--- a/data/oer-catalog-2024-2025.xlsx
+++ b/data/oer-catalog-2024-2025.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{90FC14C2-9307-4042-9F44-A914F38F6FA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2970" documentId="11_DA57C2A605D271CF30FAF17FC8BCF4206AC7672E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E79DD36E-F27C-42B5-B6FE-018453EEC2F2}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14,7 +14,7 @@
     <sheet name="OER type stats" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Catalog!$A$1:$F$269</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Catalog!$A$1:$F$270</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -41,10 +41,8 @@
   <authors>
     <author>tc={EF2E148D-555A-4E50-8DD5-A09F00C654B8}</author>
     <author>tc={AAE805E9-9988-450C-8A0E-4FC2EB2FEDE2}</author>
-    <author>tc={024D88D5-E440-4947-8942-080E6C53720C}</author>
     <author>tc={316FD03D-FBA8-46BE-9B13-BDBF824B02A3}</author>
     <author>tc={AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}</author>
-    <author>tc={747DFCD0-8BE0-4115-8F30-19A4905FD368}</author>
     <author>tc={EF7DB6F4-CF1E-46D8-AD38-559F06874760}</author>
   </authors>
   <commentList>
@@ -64,15 +62,7 @@
     This link immediately prompts file download instead of leading to a website with the file</t>
       </text>
     </comment>
-    <comment ref="C94" authorId="2" shapeId="0" xr:uid="{024D88D5-E440-4947-8942-080E6C53720C}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    this item is meant to replace textbook-- can we mark is as a textbook</t>
-      </text>
-    </comment>
-    <comment ref="G98" authorId="3" shapeId="0" xr:uid="{316FD03D-FBA8-46BE-9B13-BDBF824B02A3}">
+    <comment ref="G98" authorId="2" shapeId="0" xr:uid="{316FD03D-FBA8-46BE-9B13-BDBF824B02A3}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -80,7 +70,7 @@
     Links to a Google Form that isn't open</t>
       </text>
     </comment>
-    <comment ref="E121" authorId="4" shapeId="0" xr:uid="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
+    <comment ref="E121" authorId="3" shapeId="0" xr:uid="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -88,15 +78,7 @@
     for group authored works -- cite the authoring entity described in the work</t>
       </text>
     </comment>
-    <comment ref="C152" authorId="5" shapeId="0" xr:uid="{747DFCD0-8BE0-4115-8F30-19A4905FD368}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    Video?</t>
-      </text>
-    </comment>
-    <comment ref="B154" authorId="6" shapeId="0" xr:uid="{EF7DB6F4-CF1E-46D8-AD38-559F06874760}">
+    <comment ref="B154" authorId="4" shapeId="0" xr:uid="{EF7DB6F4-CF1E-46D8-AD38-559F06874760}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -109,7 +91,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="500">
   <si>
     <t>Campus </t>
   </si>
@@ -172,9 +154,6 @@
   </si>
   <si>
     <t>Adam Kocurek</t>
-  </si>
-  <si>
-    <t>CUNY Academic Commons</t>
   </si>
   <si>
     <t>https://academicworks.cuny.edu/gc_oers/9/</t>
@@ -294,7 +273,7 @@
     <t>https://academicworks.cuny.edu/bb_oers/128/</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>Zero Textbook Cost Syllabus for POL 1101 (American Government: Practices and Values)</t>
   </si>
   <si>
     <t>Michael Villanova</t>
@@ -482,7 +461,7 @@
     <t>https://academicworks.cuny.edu/si_oers/109/</t>
   </si>
   <si>
-    <t>SPS</t>
+    <t>CUNY SPS</t>
   </si>
   <si>
     <t>Open for All Workshop</t>
@@ -667,7 +646,7 @@
     <t>https://www.youtube.com/@DanielCapic/videos</t>
   </si>
   <si>
-    <t>NYCCT</t>
+    <t>City Tech</t>
   </si>
   <si>
     <t>Demos for MTEC 1201 Computer Programming for Interactive Media I</t>
@@ -1661,6 +1640,12 @@
   </si>
   <si>
     <t>Number of OERs</t>
+  </si>
+  <si>
+    <t>NYCCT</t>
+  </si>
+  <si>
+    <t>SPS</t>
   </si>
   <si>
     <t>Grand Total</t>
@@ -1752,7 +1737,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1798,12 +1783,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2012,9 +1991,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2351,17 +2328,11 @@
   <threadedComment ref="G9" dT="2026-03-26T16:01:07.62" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{AAE805E9-9988-450C-8A0E-4FC2EB2FEDE2}">
     <text>This link immediately prompts file download instead of leading to a website with the file</text>
   </threadedComment>
-  <threadedComment ref="C94" dT="2026-03-05T18:48:55.66" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{024D88D5-E440-4947-8942-080E6C53720C}">
-    <text>this item is meant to replace textbook-- can we mark is as a textbook</text>
-  </threadedComment>
   <threadedComment ref="G98" dT="2026-03-19T14:52:17.13" personId="{657B7818-16BF-47BC-A894-BA53C86E21EC}" id="{316FD03D-FBA8-46BE-9B13-BDBF824B02A3}">
     <text>Links to a Google Form that isn't open</text>
   </threadedComment>
   <threadedComment ref="E121" dT="2026-03-19T21:24:38.22" personId="{ABB89055-104B-4067-BC1F-C93E3E956FFD}" id="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
     <text>for group authored works -- cite the authoring entity described in the work</text>
-  </threadedComment>
-  <threadedComment ref="C152" dT="2026-03-19T16:56:22.37" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{747DFCD0-8BE0-4115-8F30-19A4905FD368}">
-    <text>Video?</text>
   </threadedComment>
   <threadedComment ref="B154" dT="2026-03-22T21:31:03.50" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{EF7DB6F4-CF1E-46D8-AD38-559F06874760}">
     <text>For "ENG 210: Journalism: Its Scope and Use" Course</text>
@@ -2468,11 +2439,11 @@
       <c r="E4" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="47" t="s">
+      <c r="F4" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="36" t="s">
         <v>21</v>
-      </c>
-      <c r="G4" s="36" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:7" s="11" customFormat="1" ht="24">
@@ -2480,22 +2451,22 @@
         <v>7</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="F5" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="36" t="s">
         <v>25</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>21</v>
-      </c>
-      <c r="G5" s="36" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="24">
@@ -2503,22 +2474,22 @@
         <v>7</v>
       </c>
       <c r="B6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="D6" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="E6" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="F6" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="36" t="s">
         <v>30</v>
-      </c>
-      <c r="F6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="36" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="24">
@@ -2526,22 +2497,22 @@
         <v>7</v>
       </c>
       <c r="B7" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="17" t="s">
+      <c r="F7" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="36" t="s">
         <v>33</v>
-      </c>
-      <c r="F7" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="234" customHeight="1">
@@ -2549,1318 +2520,1318 @@
         <v>7</v>
       </c>
       <c r="B8" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D8" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="E8" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="F8" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="36" t="s">
         <v>37</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>39</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>40</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>9</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E9" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="23" t="s">
         <v>41</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="23" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="24">
       <c r="A10" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="D10" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="F10" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="23" t="s">
         <v>44</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="23" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="24">
       <c r="A11" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="24" t="s">
         <v>46</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>47</v>
       </c>
       <c r="C11" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D11" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="25" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="F11" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="26" t="s">
         <v>49</v>
-      </c>
-      <c r="F11" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="26" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="24">
       <c r="A12" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B12" s="24" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C12" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D12" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="25" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="F12" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="26" t="s">
         <v>53</v>
-      </c>
-      <c r="F12" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="26" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="24">
       <c r="A13" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B13" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="24" t="s">
+      <c r="F13" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="27" t="s">
+    </row>
+    <row r="14" spans="1:7" ht="36">
+      <c r="A14" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>57</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>58</v>
       </c>
       <c r="C14" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="27" t="s">
         <v>59</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="24">
       <c r="A15" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="24" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C15" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="F15" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="28" t="s">
         <v>63</v>
-      </c>
-      <c r="F15" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="28" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="24">
       <c r="A16" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B16" s="24" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C16" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E16" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="27" t="s">
         <v>66</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:7" ht="24">
       <c r="A17" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B17" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="24" t="s">
         <v>68</v>
-      </c>
-      <c r="C17" s="24" t="s">
-        <v>69</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E17" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="27" t="s">
         <v>70</v>
-      </c>
-      <c r="F17" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="18" spans="1:7" ht="24">
       <c r="A18" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B18" s="24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E18" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="27" t="s">
         <v>73</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:7" ht="24">
       <c r="A19" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B19" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="D19" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="D19" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="24" t="s">
+      <c r="F19" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="27" t="s">
         <v>77</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="24">
       <c r="A20" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" s="24" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C20" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D20" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E20" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="27" t="s">
         <v>80</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="24">
       <c r="A21" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B21" s="24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C21" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E21" s="24" t="s">
+        <v>82</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>83</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="24">
       <c r="A22" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B22" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E22" s="24" t="s">
         <v>85</v>
       </c>
-      <c r="C22" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E22" s="24" t="s">
+      <c r="F22" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="27" t="s">
         <v>86</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="36">
       <c r="A23" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>88</v>
       </c>
-      <c r="C23" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E23" s="24" t="s">
+      <c r="F23" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="27" t="s">
         <v>89</v>
-      </c>
-      <c r="F23" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="36">
       <c r="A24" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E24" s="24" t="s">
         <v>91</v>
       </c>
-      <c r="C24" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="24" t="s">
+      <c r="F24" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="27" t="s">
         <v>92</v>
-      </c>
-      <c r="F24" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="24">
       <c r="A25" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B25" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="24" t="s">
         <v>94</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="D25" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E25" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="D25" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E25" s="24" t="s">
+      <c r="F25" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="G25" s="27" t="s">
         <v>97</v>
-      </c>
-      <c r="G25" s="27" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="26" spans="1:7" ht="24">
       <c r="A26" s="24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B26" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="E26" s="24" t="s">
         <v>99</v>
       </c>
-      <c r="C26" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E26" s="24" t="s">
+      <c r="F26" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="27" t="s">
         <v>100</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="B27" s="24" t="s">
         <v>102</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>103</v>
       </c>
       <c r="C27" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E27" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="F27" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="27" t="s">
         <v>105</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:7" ht="24">
       <c r="A28" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B28" s="24" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C28" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E28" s="24" t="s">
+        <v>107</v>
+      </c>
+      <c r="F28" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="27" t="s">
         <v>108</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:7" ht="24">
       <c r="A29" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B29" s="24" t="s">
+        <v>109</v>
+      </c>
+      <c r="C29" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D29" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D29" s="18" t="s">
+      <c r="E29" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="F29" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="27" t="s">
         <v>112</v>
-      </c>
-      <c r="F29" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="42" customHeight="1">
       <c r="A30" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B30" s="24" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D30" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E30" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="C30" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="24" t="s">
+      <c r="F30" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="27" t="s">
         <v>115</v>
-      </c>
-      <c r="F30" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="24">
       <c r="A31" s="24" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B31" s="24" t="s">
+        <v>116</v>
+      </c>
+      <c r="C31" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D31" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E31" s="24" t="s">
+      <c r="F31" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="27" t="s">
         <v>118</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="24">
       <c r="A32" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B32" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="C32" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="D32" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" s="24" t="s">
         <v>122</v>
       </c>
-      <c r="D32" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E32" s="24" t="s">
+      <c r="F32" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="G32" s="27" t="s">
         <v>124</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="24">
       <c r="A33" s="24" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B33" s="24" t="s">
+        <v>125</v>
+      </c>
+      <c r="C33" s="24" t="s">
+        <v>121</v>
+      </c>
+      <c r="D33" s="29" t="s">
+        <v>28</v>
+      </c>
+      <c r="E33" s="24" t="s">
         <v>126</v>
       </c>
-      <c r="C33" s="24" t="s">
-        <v>122</v>
-      </c>
-      <c r="D33" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="E33" s="24" t="s">
+      <c r="F33" s="24" t="s">
+        <v>123</v>
+      </c>
+      <c r="G33" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="F33" s="24" t="s">
-        <v>124</v>
-      </c>
-      <c r="G33" s="30" t="s">
+    </row>
+    <row r="34" spans="1:7" s="9" customFormat="1" ht="36">
+      <c r="A34" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B34" s="17" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" s="9" customFormat="1" ht="36">
-      <c r="A34" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="B34" s="17" t="s">
+      <c r="C34" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D34" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E34" s="17" t="s">
         <v>129</v>
       </c>
-      <c r="C34" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D34" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E34" s="17" t="s">
+      <c r="F34" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="19" t="s">
         <v>130</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="19" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="35" spans="1:7" ht="24">
       <c r="A35" s="24" t="s">
+        <v>131</v>
+      </c>
+      <c r="B35" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="C35" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D35" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="C35" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D35" s="18" t="s">
+      <c r="E35" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="F35" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G35" s="27" t="s">
         <v>135</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G35" s="27" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="36" spans="1:7" ht="24">
       <c r="A36" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B36" s="24" t="s">
+        <v>136</v>
+      </c>
+      <c r="C36" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="D36" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="D36" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E36" s="24" t="s">
+      <c r="F36" s="17" t="s">
         <v>139</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="G36" s="27" t="s">
         <v>140</v>
-      </c>
-      <c r="G36" s="27" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="37" spans="1:7" ht="24">
       <c r="A37" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B37" s="24" t="s">
+        <v>141</v>
+      </c>
+      <c r="C37" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="C37" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="18" t="s">
+      <c r="E37" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="F37" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G37" s="27" t="s">
         <v>144</v>
-      </c>
-      <c r="F37" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G37" s="27" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:7" ht="24">
       <c r="A38" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="24" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D38" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="C38" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E38" s="24" t="s">
+      <c r="F38" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G38" s="27" t="s">
         <v>147</v>
-      </c>
-      <c r="F38" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G38" s="27" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="33" customHeight="1">
       <c r="A39" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B39" s="24" t="s">
+        <v>148</v>
+      </c>
+      <c r="C39" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G39" s="27" t="s">
         <v>149</v>
-      </c>
-      <c r="C39" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E39" s="24" t="s">
-        <v>147</v>
-      </c>
-      <c r="F39" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="40" spans="1:7" ht="104.25" customHeight="1">
       <c r="A40" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B40" s="24" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E40" s="24" t="s">
         <v>151</v>
       </c>
-      <c r="C40" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D40" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E40" s="24" t="s">
+      <c r="F40" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G40" s="26" t="s">
         <v>152</v>
-      </c>
-      <c r="F40" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G40" s="26" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="41" spans="1:7" ht="27" customHeight="1">
       <c r="A41" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B41" s="24" t="s">
+        <v>153</v>
+      </c>
+      <c r="C41" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E41" s="25" t="s">
         <v>154</v>
       </c>
-      <c r="C41" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D41" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E41" s="25" t="s">
+      <c r="F41" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="26" t="s">
         <v>155</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="26" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="42" spans="1:7" ht="41.25" customHeight="1">
       <c r="A42" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B42" s="24" t="s">
+        <v>156</v>
+      </c>
+      <c r="C42" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E42" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="C42" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D42" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E42" s="24" t="s">
+      <c r="F42" s="17" t="s">
         <v>158</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="G42" s="26" t="s">
         <v>159</v>
-      </c>
-      <c r="G42" s="26" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:7" ht="24">
       <c r="A43" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B43" s="24" t="s">
+        <v>160</v>
+      </c>
+      <c r="C43" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E43" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="C43" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D43" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="25" t="s">
+      <c r="F43" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="26" t="s">
         <v>162</v>
-      </c>
-      <c r="F43" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="26" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="44" spans="1:7" ht="24">
       <c r="A44" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B44" s="24" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D44" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E44" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="C44" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D44" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E44" s="25" t="s">
+      <c r="F44" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="27" t="s">
         <v>165</v>
-      </c>
-      <c r="F44" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="27" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:7" ht="41.25" customHeight="1">
       <c r="A45" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B45" s="24" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D45" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C45" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D45" s="18" t="s">
+      <c r="E45" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="F45" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="27" t="s">
         <v>169</v>
-      </c>
-      <c r="F45" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="27" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="28.5" customHeight="1">
       <c r="A46" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B46" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="C46" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="25" t="s">
         <v>171</v>
       </c>
-      <c r="C46" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D46" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="25" t="s">
+      <c r="F46" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="27" t="s">
         <v>172</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="27" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B47" s="17" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="F47" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G47" s="27" t="s">
         <v>174</v>
-      </c>
-      <c r="C47" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E47" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="F47" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="G47" s="27" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="48" spans="1:7" ht="24">
       <c r="A48" s="24" t="s">
+        <v>175</v>
+      </c>
+      <c r="B48" s="24" t="s">
         <v>176</v>
       </c>
-      <c r="B48" s="24" t="s">
+      <c r="C48" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E48" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="C48" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E48" s="24" t="s">
+      <c r="F48" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="G48" s="27" t="s">
         <v>179</v>
-      </c>
-      <c r="G48" s="27" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="24">
       <c r="A49" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B49" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E49" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="C49" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D49" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E49" s="24" t="s">
+      <c r="F49" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G49" s="27" t="s">
         <v>182</v>
-      </c>
-      <c r="F49" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" s="27" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="50" spans="1:7" s="9" customFormat="1" ht="36">
       <c r="A50" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B50" s="41" t="s">
+        <v>183</v>
+      </c>
+      <c r="C50" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E50" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="C50" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E50" s="20" t="s">
+      <c r="F50" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="31" t="s">
         <v>185</v>
-      </c>
-      <c r="F50" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="31" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:7" ht="24">
       <c r="A51" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="D51" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E51" s="25" t="s">
         <v>187</v>
       </c>
-      <c r="C51" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E51" s="25" t="s">
+      <c r="F51" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G51" s="27" t="s">
         <v>188</v>
-      </c>
-      <c r="F51" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G51" s="27" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="52" spans="1:7" ht="24">
       <c r="A52" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B52" s="24" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C52" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E52" s="24" t="s">
+        <v>190</v>
+      </c>
+      <c r="F52" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="27" t="s">
         <v>191</v>
-      </c>
-      <c r="F52" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="27" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="53" spans="1:7" s="9" customFormat="1" ht="36">
       <c r="A53" s="17" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B53" s="17" t="s">
+        <v>192</v>
+      </c>
+      <c r="C53" s="17" t="s">
         <v>193</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="D53" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="D53" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E53" s="17" t="s">
+      <c r="F53" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="40" t="s">
         <v>195</v>
-      </c>
-      <c r="F53" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" s="40" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:7" ht="41.25" customHeight="1">
       <c r="A54" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B54" s="24" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C54" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E54" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="27" t="s">
         <v>198</v>
-      </c>
-      <c r="F54" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" s="27" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="24">
       <c r="A55" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B55" s="24" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E55" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="C55" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E55" s="24" t="s">
+      <c r="F55" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="27" t="s">
         <v>201</v>
-      </c>
-      <c r="F55" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="27" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="56" spans="1:7" ht="36">
       <c r="A56" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B56" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D56" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E56" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="C56" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D56" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E56" s="24" t="s">
+      <c r="F56" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="27" t="s">
         <v>204</v>
-      </c>
-      <c r="F56" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="27" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="57" spans="1:7" ht="53.25" customHeight="1">
       <c r="A57" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B57" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D57" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E57" s="24" t="s">
         <v>206</v>
       </c>
-      <c r="C57" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D57" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" s="24" t="s">
+      <c r="F57" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" s="27" t="s">
         <v>207</v>
-      </c>
-      <c r="F57" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" s="27" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="72">
       <c r="A58" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B58" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E58" s="24" t="s">
         <v>209</v>
       </c>
-      <c r="C58" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D58" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E58" s="24" t="s">
+      <c r="F58" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G58" s="27" t="s">
         <v>210</v>
-      </c>
-      <c r="F58" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G58" s="27" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="59" spans="1:7" ht="31.5" customHeight="1">
       <c r="A59" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B59" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D59" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E59" s="24" t="s">
+        <v>197</v>
+      </c>
+      <c r="F59" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D59" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E59" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="F59" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" s="27" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="24">
       <c r="A60" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B60" s="24" t="s">
         <v>214</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>215</v>
       </c>
       <c r="C60" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E60" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="F60" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="27" t="s">
         <v>216</v>
-      </c>
-      <c r="F60" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="27" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="24">
       <c r="A61" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B61" s="24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C61" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E61" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="27" t="s">
         <v>219</v>
-      </c>
-      <c r="F61" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" s="27" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="24">
       <c r="A62" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B62" s="24" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C62" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E62" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="F62" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="27" t="s">
         <v>222</v>
-      </c>
-      <c r="F62" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="27" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="24">
       <c r="A63" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B63" s="24" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C63" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E63" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="27" t="s">
         <v>225</v>
-      </c>
-      <c r="F63" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G63" s="27" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="24">
       <c r="A64" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B64" s="24" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C64" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E64" s="24" t="s">
+        <v>227</v>
+      </c>
+      <c r="F64" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="27" t="s">
         <v>228</v>
-      </c>
-      <c r="F64" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" s="27" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:7">
       <c r="A65" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B65" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C65" s="24" t="s">
         <v>9</v>
@@ -3869,67 +3840,67 @@
         <v>19</v>
       </c>
       <c r="E65" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="F65" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="27" t="s">
         <v>231</v>
-      </c>
-      <c r="F65" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="27" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="66" spans="1:7">
       <c r="A66" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B66" s="24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C66" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E66" s="24" t="s">
+        <v>233</v>
+      </c>
+      <c r="F66" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="27" t="s">
         <v>234</v>
-      </c>
-      <c r="F66" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G66" s="27" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="42.75" customHeight="1">
       <c r="A67" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B67" s="24" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C67" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D67" s="18" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E67" s="24" t="s">
+        <v>236</v>
+      </c>
+      <c r="F67" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" s="26" t="s">
         <v>237</v>
-      </c>
-      <c r="F67" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" s="26" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:7" ht="24">
       <c r="A68" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B68" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C68" s="24" t="s">
         <v>9</v>
@@ -3938,2014 +3909,2014 @@
         <v>10</v>
       </c>
       <c r="E68" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="27" t="s">
         <v>240</v>
-      </c>
-      <c r="F68" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G68" s="27" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="69" spans="1:7" ht="29.25" customHeight="1">
       <c r="A69" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B69" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C69" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D69" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E69" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="F69" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="27" t="s">
         <v>243</v>
-      </c>
-      <c r="F69" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="27" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="24">
       <c r="A70" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B70" s="24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C70" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D70" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E70" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" s="27" t="s">
         <v>246</v>
-      </c>
-      <c r="F70" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G70" s="27" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="71" spans="1:7" ht="24">
       <c r="A71" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B71" s="24" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C71" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="18" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E71" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="F71" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71" s="27" t="s">
         <v>249</v>
-      </c>
-      <c r="F71" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G71" s="27" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="72" spans="1:7" ht="24">
       <c r="A72" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B72" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C72" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D72" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E72" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F72" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="27" t="s">
         <v>252</v>
-      </c>
-      <c r="F72" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" s="27" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="73" spans="1:7" ht="24">
       <c r="A73" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B73" s="24" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C73" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E73" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" s="27" t="s">
         <v>255</v>
-      </c>
-      <c r="F73" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" s="27" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="74" spans="1:7" ht="24">
       <c r="A74" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B74" s="24" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C74" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D74" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E74" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="F74" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="26" t="s">
         <v>258</v>
-      </c>
-      <c r="F74" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G74" s="26" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="75" spans="1:7" ht="24">
       <c r="A75" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B75" s="24" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C75" s="25" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E75" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="F75" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" s="27" t="s">
         <v>261</v>
-      </c>
-      <c r="F75" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="27" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="76" spans="1:7" ht="24">
       <c r="A76" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B76" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="C76" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D76" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E76" s="25" t="s">
         <v>263</v>
       </c>
-      <c r="C76" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D76" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E76" s="25" t="s">
+      <c r="F76" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="27" t="s">
         <v>264</v>
-      </c>
-      <c r="F76" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="27" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="77" spans="1:7" s="9" customFormat="1" ht="24">
       <c r="A77" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B77" s="17" t="s">
+        <v>265</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="D77" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E77" s="17" t="s">
         <v>266</v>
       </c>
-      <c r="C77" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E77" s="17" t="s">
+      <c r="F77" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="19" t="s">
         <v>267</v>
-      </c>
-      <c r="F77" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="19" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="24">
       <c r="A78" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B78" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="C78" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D78" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E78" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="C78" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D78" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E78" s="25" t="s">
+      <c r="F78" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G78" s="27" t="s">
         <v>270</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G78" s="27" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="24">
       <c r="A79" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B79" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="C79" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D79" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E79" s="25" t="s">
         <v>272</v>
       </c>
-      <c r="C79" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D79" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E79" s="25" t="s">
+      <c r="F79" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="27" t="s">
         <v>273</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="27" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="80" spans="1:7">
       <c r="A80" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B80" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="C80" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D80" s="18" t="s">
         <v>275</v>
       </c>
-      <c r="C80" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D80" s="18" t="s">
+      <c r="E80" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="E80" s="24" t="s">
+      <c r="F80" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="27" t="s">
         <v>277</v>
-      </c>
-      <c r="F80" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G80" s="27" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="81" spans="1:7">
       <c r="A81" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B81" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C81" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D81" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="E81" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="F81" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="G81" s="27" t="s">
         <v>279</v>
-      </c>
-      <c r="C81" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="D81" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="E81" s="24" t="s">
-        <v>277</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>140</v>
-      </c>
-      <c r="G81" s="27" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="24">
       <c r="A82" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B82" s="24" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C82" s="24" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D82" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="E82" s="24" t="s">
         <v>276</v>
       </c>
-      <c r="E82" s="24" t="s">
-        <v>277</v>
-      </c>
       <c r="F82" s="17" t="s">
+        <v>280</v>
+      </c>
+      <c r="G82" s="27" t="s">
         <v>281</v>
-      </c>
-      <c r="G82" s="27" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="24">
       <c r="A83" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B83" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D83" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E83" s="24" t="s">
         <v>283</v>
       </c>
-      <c r="C83" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D83" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E83" s="24" t="s">
+      <c r="F83" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="27" t="s">
         <v>284</v>
-      </c>
-      <c r="F83" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G83" s="27" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="36">
       <c r="A84" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B84" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D84" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E84" s="24" t="s">
         <v>286</v>
       </c>
-      <c r="C84" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E84" s="24" t="s">
+      <c r="F84" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="27" t="s">
         <v>287</v>
-      </c>
-      <c r="F84" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G84" s="27" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="36">
       <c r="A85" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B85" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D85" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E85" s="24" t="s">
         <v>289</v>
       </c>
-      <c r="C85" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D85" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E85" s="24" t="s">
+      <c r="F85" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="27" t="s">
         <v>290</v>
-      </c>
-      <c r="F85" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="27" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="24">
       <c r="A86" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B86" s="24" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C86" s="24" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D86" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E86" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="27" t="s">
         <v>293</v>
-      </c>
-      <c r="F86" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" s="27" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="87" spans="1:7" ht="24">
       <c r="A87" s="24" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B87" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E87" s="24" t="s">
         <v>295</v>
       </c>
-      <c r="C87" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D87" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E87" s="24" t="s">
+      <c r="F87" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="27" t="s">
         <v>296</v>
-      </c>
-      <c r="F87" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="27" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="88" spans="1:7" ht="24">
       <c r="A88" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B88" s="24" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C88" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D88" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E88" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="F88" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="27" t="s">
         <v>299</v>
-      </c>
-      <c r="F88" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G88" s="27" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="89" spans="1:7" ht="24">
       <c r="A89" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B89" s="24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C89" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D89" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E89" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="F89" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="27" t="s">
         <v>302</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="27" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="90" spans="1:7" ht="24">
       <c r="A90" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B90" s="24" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C90" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D90" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E90" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="F90" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" s="27" t="s">
         <v>305</v>
-      </c>
-      <c r="F90" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" s="27" t="s">
-        <v>306</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="33" customHeight="1">
       <c r="A91" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B91" s="24" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C91" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D91" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E91" s="24" t="s">
+        <v>307</v>
+      </c>
+      <c r="F91" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="27" t="s">
         <v>308</v>
-      </c>
-      <c r="F91" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" s="27" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="28.5" customHeight="1">
       <c r="A92" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B92" s="24" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C92" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D92" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E92" s="24" t="s">
+        <v>310</v>
+      </c>
+      <c r="F92" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="27" t="s">
         <v>311</v>
-      </c>
-      <c r="F92" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" s="27" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="24">
       <c r="A93" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B93" s="24" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="C93" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D93" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E93" s="24" t="s">
+        <v>313</v>
+      </c>
+      <c r="F93" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="F93" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" s="27" t="s">
+    </row>
+    <row r="94" spans="1:7" ht="24">
+      <c r="A94" s="24" t="s">
+        <v>38</v>
+      </c>
+      <c r="B94" s="24" t="s">
         <v>315</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" s="11" customFormat="1" ht="24">
-      <c r="A94" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B94" s="32" t="s">
+      <c r="C94" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D94" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="E94" s="24" t="s">
         <v>316</v>
       </c>
-      <c r="C94" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D94" s="33" t="s">
-        <v>276</v>
-      </c>
-      <c r="E94" s="32" t="s">
+      <c r="F94" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G94" s="47" t="s">
         <v>317</v>
-      </c>
-      <c r="F94" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="G94" s="34" t="s">
-        <v>318</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="48">
       <c r="A95" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B95" s="24" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C95" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D95" s="18" t="s">
         <v>10</v>
       </c>
       <c r="E95" s="24" t="s">
+        <v>319</v>
+      </c>
+      <c r="F95" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G95" s="27" t="s">
         <v>320</v>
-      </c>
-      <c r="F95" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G95" s="27" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="96" spans="1:7" ht="24">
       <c r="A96" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B96" s="24" t="s">
+        <v>321</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D96" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="E96" s="24" t="s">
         <v>322</v>
       </c>
-      <c r="C96" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D96" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="E96" s="24" t="s">
+      <c r="F96" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="27" t="s">
         <v>323</v>
-      </c>
-      <c r="F96" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" s="27" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="24">
       <c r="A97" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B97" s="24" t="s">
+        <v>324</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D97" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E97" s="24" t="s">
         <v>325</v>
       </c>
-      <c r="C97" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D97" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E97" s="24" t="s">
+      <c r="F97" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" s="27" t="s">
         <v>326</v>
-      </c>
-      <c r="F97" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" s="27" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="98" spans="1:7" s="11" customFormat="1" ht="36">
       <c r="A98" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B98" s="32" t="s">
+        <v>327</v>
+      </c>
+      <c r="C98" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="D98" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="E98" s="32" t="s">
         <v>328</v>
       </c>
-      <c r="C98" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="D98" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="E98" s="32" t="s">
+      <c r="F98" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="34" t="s">
         <v>329</v>
-      </c>
-      <c r="F98" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" s="34" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="99" spans="1:7" ht="41.25" customHeight="1">
       <c r="A99" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B99" s="24" t="s">
+        <v>330</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D99" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E99" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="F99" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" s="27" t="s">
         <v>331</v>
-      </c>
-      <c r="C99" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D99" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E99" s="24" t="s">
-        <v>299</v>
-      </c>
-      <c r="F99" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" s="27" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="100" spans="1:7" ht="42" customHeight="1">
       <c r="A100" s="24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B100" s="24" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C100" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D100" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E100" s="24" t="s">
+        <v>333</v>
+      </c>
+      <c r="F100" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="27" t="s">
         <v>334</v>
-      </c>
-      <c r="F100" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="27" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="101" spans="1:7" ht="24">
       <c r="A101" s="24" t="s">
+        <v>335</v>
+      </c>
+      <c r="B101" s="24" t="s">
         <v>336</v>
       </c>
-      <c r="B101" s="24" t="s">
+      <c r="C101" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D101" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="C101" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D101" s="18" t="s">
+      <c r="E101" s="24" t="s">
         <v>338</v>
       </c>
-      <c r="E101" s="24" t="s">
+      <c r="F101" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G101" s="27" t="s">
         <v>339</v>
-      </c>
-      <c r="F101" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G101" s="27" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="102" spans="1:7">
       <c r="A102" s="24" t="s">
+        <v>340</v>
+      </c>
+      <c r="B102" s="24" t="s">
         <v>341</v>
-      </c>
-      <c r="B102" s="24" t="s">
-        <v>342</v>
       </c>
       <c r="C102" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D102" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E102" s="24" t="s">
+        <v>342</v>
+      </c>
+      <c r="F102" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="27" t="s">
         <v>343</v>
-      </c>
-      <c r="F102" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G102" s="27" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="103" spans="1:7">
       <c r="A103" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B103" s="24" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C103" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D103" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E103" s="24" t="s">
+        <v>345</v>
+      </c>
+      <c r="F103" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" s="27" t="s">
         <v>346</v>
-      </c>
-      <c r="F103" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G103" s="27" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="104" spans="1:7" ht="24">
       <c r="A104" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B104" s="24" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C104" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D104" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E104" s="24" t="s">
+        <v>348</v>
+      </c>
+      <c r="F104" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="27" t="s">
         <v>349</v>
-      </c>
-      <c r="F104" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G104" s="27" t="s">
-        <v>350</v>
       </c>
     </row>
     <row r="105" spans="1:7" ht="48">
       <c r="A105" s="24" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B105" s="24" t="s">
+        <v>350</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" s="24" t="s">
         <v>351</v>
       </c>
-      <c r="C105" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="D105" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E105" s="24" t="s">
+      <c r="F105" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="27" t="s">
         <v>352</v>
-      </c>
-      <c r="F105" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="27" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:7" ht="36">
       <c r="A106" s="24" t="s">
+        <v>353</v>
+      </c>
+      <c r="B106" s="24" t="s">
         <v>354</v>
       </c>
-      <c r="B106" s="24" t="s">
+      <c r="C106" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D106" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" s="24" t="s">
         <v>355</v>
       </c>
-      <c r="C106" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D106" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E106" s="24" t="s">
+      <c r="F106" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="27" t="s">
         <v>356</v>
-      </c>
-      <c r="F106" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" s="27" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:7" ht="24">
       <c r="A107" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B107" s="24" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C107" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D107" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E107" s="24" t="s">
+        <v>358</v>
+      </c>
+      <c r="F107" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" s="27" t="s">
         <v>359</v>
-      </c>
-      <c r="F107" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" s="27" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="108" spans="1:7" ht="24">
       <c r="A108" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B108" s="24" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C108" s="24" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D108" s="18" t="s">
         <v>19</v>
       </c>
       <c r="E108" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="F108" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" s="27" t="s">
         <v>362</v>
-      </c>
-      <c r="F108" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G108" s="27" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:7" ht="48">
       <c r="A109" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B109" s="24" t="s">
+        <v>363</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D109" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E109" s="24" t="s">
         <v>364</v>
       </c>
-      <c r="C109" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D109" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E109" s="24" t="s">
+      <c r="F109" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="27" t="s">
         <v>365</v>
-      </c>
-      <c r="F109" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" s="27" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="110" spans="1:7" ht="24">
       <c r="A110" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B110" s="24" t="s">
+        <v>366</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="E110" s="24" t="s">
         <v>367</v>
       </c>
-      <c r="C110" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="D110" s="18" t="s">
-        <v>134</v>
-      </c>
-      <c r="E110" s="24" t="s">
+      <c r="F110" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="27" t="s">
         <v>368</v>
-      </c>
-      <c r="F110" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G110" s="27" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="111" spans="1:7" ht="24">
       <c r="A111" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B111" s="24" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D111" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="E111" s="24" t="s">
         <v>370</v>
       </c>
-      <c r="C111" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>104</v>
-      </c>
-      <c r="E111" s="24" t="s">
+      <c r="F111" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" s="27" t="s">
         <v>371</v>
-      </c>
-      <c r="F111" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G111" s="27" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="112" spans="1:7" ht="108.75" customHeight="1">
       <c r="A112" s="24" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B112" s="24" t="s">
+        <v>372</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D112" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112" s="24" t="s">
         <v>373</v>
       </c>
-      <c r="C112" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E112" s="24" t="s">
+      <c r="F112" s="17" t="s">
+        <v>158</v>
+      </c>
+      <c r="G112" s="27" t="s">
         <v>374</v>
-      </c>
-      <c r="F112" s="17" t="s">
-        <v>159</v>
-      </c>
-      <c r="G112" s="27" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="83.25" customHeight="1">
       <c r="A113" s="24" t="s">
+        <v>375</v>
+      </c>
+      <c r="B113" s="24" t="s">
         <v>376</v>
       </c>
-      <c r="B113" s="24" t="s">
+      <c r="C113" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D113" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E113" s="24" t="s">
         <v>377</v>
       </c>
-      <c r="C113" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D113" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E113" s="24" t="s">
+      <c r="F113" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" s="27" t="s">
         <v>378</v>
-      </c>
-      <c r="F113" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" s="27" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="24">
       <c r="A114" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B114" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D114" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="24" t="s">
         <v>380</v>
       </c>
-      <c r="C114" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D114" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E114" s="24" t="s">
+      <c r="F114" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="27" t="s">
         <v>381</v>
-      </c>
-      <c r="F114" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G114" s="27" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="115" spans="1:7" ht="24">
       <c r="A115" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B115" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D115" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" s="24" t="s">
         <v>383</v>
       </c>
-      <c r="C115" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D115" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="E115" s="24" t="s">
+      <c r="F115" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="27" t="s">
         <v>384</v>
-      </c>
-      <c r="F115" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="27" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="116" spans="1:7" ht="34.5" customHeight="1">
       <c r="A116" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B116" s="24" t="s">
+        <v>385</v>
+      </c>
+      <c r="C116" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D116" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="24" t="s">
         <v>386</v>
       </c>
-      <c r="C116" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D116" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E116" s="24" t="s">
+      <c r="F116" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" s="27" t="s">
         <v>387</v>
-      </c>
-      <c r="F116" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G116" s="27" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="117" spans="1:7" ht="24">
       <c r="A117" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B117" s="24" t="s">
+        <v>388</v>
+      </c>
+      <c r="C117" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D117" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="24" t="s">
         <v>389</v>
       </c>
-      <c r="C117" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D117" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E117" s="24" t="s">
+      <c r="F117" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" s="27" t="s">
         <v>390</v>
-      </c>
-      <c r="F117" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" s="27" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="118" spans="1:7" ht="24">
       <c r="A118" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B118" s="24" t="s">
+        <v>391</v>
+      </c>
+      <c r="C118" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="D118" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118" s="24" t="s">
         <v>392</v>
       </c>
-      <c r="C118" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D118" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E118" s="24" t="s">
+      <c r="F118" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" s="27" t="s">
         <v>393</v>
-      </c>
-      <c r="F118" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" s="27" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="119" spans="1:7" ht="24">
       <c r="A119" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B119" s="24" t="s">
+        <v>394</v>
+      </c>
+      <c r="C119" s="24" t="s">
+        <v>193</v>
+      </c>
+      <c r="D119" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="E119" s="24" t="s">
         <v>395</v>
       </c>
-      <c r="C119" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D119" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E119" s="24" t="s">
+      <c r="F119" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G119" s="27" t="s">
         <v>396</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G119" s="27" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="120" spans="1:7" ht="24">
       <c r="A120" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B120" s="24" t="s">
+        <v>397</v>
+      </c>
+      <c r="C120" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D120" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" s="24" t="s">
         <v>398</v>
       </c>
-      <c r="C120" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D120" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E120" s="24" t="s">
+      <c r="F120" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G120" s="27" t="s">
         <v>399</v>
-      </c>
-      <c r="F120" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G120" s="27" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="121" spans="1:7" s="10" customFormat="1" ht="36">
       <c r="A121" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B121" s="17" t="s">
+        <v>400</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D121" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121" s="35" t="s">
         <v>401</v>
       </c>
-      <c r="C121" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D121" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E121" s="35" t="s">
+      <c r="F121" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G121" s="36" t="s">
         <v>402</v>
-      </c>
-      <c r="F121" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G121" s="36" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="122" spans="1:7" s="10" customFormat="1" ht="36">
       <c r="A122" s="17" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B122" s="17" t="s">
+        <v>403</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="D122" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122" s="35" t="s">
+        <v>401</v>
+      </c>
+      <c r="F122" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G122" s="36" t="s">
         <v>404</v>
-      </c>
-      <c r="C122" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="D122" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E122" s="35" t="s">
-        <v>402</v>
-      </c>
-      <c r="F122" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G122" s="36" t="s">
-        <v>405</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="24">
       <c r="A123" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B123" s="24" t="s">
+        <v>405</v>
+      </c>
+      <c r="C123" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D123" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="E123" s="24" t="s">
         <v>406</v>
       </c>
-      <c r="C123" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D123" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="E123" s="24" t="s">
+      <c r="F123" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G123" s="27" t="s">
         <v>407</v>
-      </c>
-      <c r="F123" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G123" s="27" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="24">
       <c r="A124" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B124" s="24" t="s">
+        <v>408</v>
+      </c>
+      <c r="C124" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D124" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="E124" s="24" t="s">
         <v>409</v>
       </c>
-      <c r="C124" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D124" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="E124" s="24" t="s">
+      <c r="F124" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G124" s="27" t="s">
         <v>410</v>
-      </c>
-      <c r="F124" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G124" s="27" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="125" spans="1:7" ht="24">
       <c r="A125" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B125" s="24" t="s">
+        <v>411</v>
+      </c>
+      <c r="C125" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D125" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="24" t="s">
         <v>412</v>
       </c>
-      <c r="C125" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D125" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E125" s="24" t="s">
+      <c r="F125" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G125" s="27" t="s">
         <v>413</v>
-      </c>
-      <c r="F125" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G125" s="27" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="126" spans="1:7" ht="24">
       <c r="A126" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B126" s="24" t="s">
+        <v>414</v>
+      </c>
+      <c r="C126" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D126" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="24" t="s">
         <v>415</v>
       </c>
-      <c r="C126" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D126" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E126" s="24" t="s">
+      <c r="F126" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G126" s="27" t="s">
         <v>416</v>
-      </c>
-      <c r="F126" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G126" s="27" t="s">
-        <v>417</v>
       </c>
     </row>
     <row r="127" spans="1:7" ht="24">
       <c r="A127" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B127" s="24" t="s">
+        <v>417</v>
+      </c>
+      <c r="C127" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D127" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="E127" s="24" t="s">
         <v>418</v>
       </c>
-      <c r="C127" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D127" s="18" t="s">
-        <v>338</v>
-      </c>
-      <c r="E127" s="24" t="s">
+      <c r="F127" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G127" s="27" t="s">
         <v>419</v>
-      </c>
-      <c r="F127" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G127" s="27" t="s">
-        <v>420</v>
       </c>
     </row>
     <row r="128" spans="1:7" ht="24">
       <c r="A128" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B128" s="24" t="s">
+        <v>420</v>
+      </c>
+      <c r="C128" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D128" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="24" t="s">
         <v>421</v>
       </c>
-      <c r="C128" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E128" s="24" t="s">
+      <c r="F128" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G128" s="27" t="s">
         <v>422</v>
-      </c>
-      <c r="F128" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G128" s="27" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="129" spans="1:7" ht="24">
       <c r="A129" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B129" s="24" t="s">
+        <v>423</v>
+      </c>
+      <c r="C129" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D129" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" s="24" t="s">
+        <v>415</v>
+      </c>
+      <c r="F129" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G129" s="27" t="s">
         <v>424</v>
-      </c>
-      <c r="C129" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E129" s="24" t="s">
-        <v>416</v>
-      </c>
-      <c r="F129" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G129" s="27" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="130" spans="1:7" ht="24">
       <c r="A130" s="24" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B130" s="24" t="s">
+        <v>425</v>
+      </c>
+      <c r="C130" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D130" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" s="24" t="s">
         <v>426</v>
       </c>
-      <c r="C130" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E130" s="24" t="s">
+      <c r="F130" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G130" s="27" t="s">
         <v>427</v>
-      </c>
-      <c r="F130" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G130" s="27" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="24">
       <c r="A131" s="24" t="s">
+        <v>428</v>
+      </c>
+      <c r="B131" s="24" t="s">
         <v>429</v>
-      </c>
-      <c r="B131" s="24" t="s">
-        <v>430</v>
       </c>
       <c r="C131" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D131" s="18" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E131" s="25" t="s">
+        <v>430</v>
+      </c>
+      <c r="F131" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G131" s="27" t="s">
         <v>431</v>
-      </c>
-      <c r="F131" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G131" s="27" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="132" spans="1:7">
       <c r="A132" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B132" s="24" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C132" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D132" s="18" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E132" s="25" t="s">
+        <v>433</v>
+      </c>
+      <c r="F132" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G132" s="27" t="s">
         <v>434</v>
-      </c>
-      <c r="F132" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G132" s="27" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="133" spans="1:7">
       <c r="A133" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B133" s="24" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C133" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D133" s="18" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E133" s="24" t="s">
+        <v>436</v>
+      </c>
+      <c r="F133" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G133" s="27" t="s">
         <v>437</v>
-      </c>
-      <c r="F133" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G133" s="27" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="134" spans="1:7" ht="48">
       <c r="A134" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B134" s="24" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C134" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D134" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E134" s="25" t="s">
+        <v>439</v>
+      </c>
+      <c r="F134" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G134" s="27" t="s">
         <v>440</v>
-      </c>
-      <c r="F134" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G134" s="27" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="24">
       <c r="A135" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B135" s="24" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C135" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D135" s="18" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E135" s="25" t="s">
+        <v>442</v>
+      </c>
+      <c r="F135" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G135" s="27" t="s">
         <v>443</v>
-      </c>
-      <c r="F135" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G135" s="27" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="136" spans="1:7" ht="24">
       <c r="A136" s="24" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B136" s="24" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C136" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D136" s="18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E136" s="25" t="s">
+        <v>445</v>
+      </c>
+      <c r="F136" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G136" s="27" t="s">
         <v>446</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G136" s="27" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="137" spans="1:7" ht="61.5" customHeight="1">
       <c r="A137" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="B137" s="24" t="s">
         <v>448</v>
       </c>
-      <c r="B137" s="24" t="s">
+      <c r="C137" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D137" s="18" t="s">
+        <v>275</v>
+      </c>
+      <c r="E137" s="24" t="s">
         <v>449</v>
       </c>
-      <c r="C137" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="E137" s="24" t="s">
+      <c r="F137" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G137" s="27" t="s">
         <v>450</v>
-      </c>
-      <c r="F137" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G137" s="27" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="138" spans="1:7" ht="36">
       <c r="A138" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B138" s="24" t="s">
+        <v>451</v>
+      </c>
+      <c r="C138" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D138" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E138" s="24" t="s">
         <v>452</v>
       </c>
-      <c r="C138" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E138" s="24" t="s">
+      <c r="F138" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G138" s="27" t="s">
         <v>453</v>
-      </c>
-      <c r="F138" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G138" s="27" t="s">
-        <v>454</v>
       </c>
     </row>
     <row r="139" spans="1:7" ht="24">
       <c r="A139" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B139" s="24" t="s">
+        <v>454</v>
+      </c>
+      <c r="C139" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E139" s="24" t="s">
         <v>455</v>
       </c>
-      <c r="C139" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D139" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E139" s="24" t="s">
+      <c r="F139" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139" s="27" t="s">
         <v>456</v>
-      </c>
-      <c r="F139" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G139" s="27" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="140" spans="1:7" ht="24">
       <c r="A140" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B140" s="24" t="s">
+        <v>457</v>
+      </c>
+      <c r="C140" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D140" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F140" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G140" s="27" t="s">
         <v>458</v>
-      </c>
-      <c r="C140" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D140" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E140" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="27" t="s">
-        <v>459</v>
       </c>
     </row>
     <row r="141" spans="1:7" ht="24">
       <c r="A141" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B141" s="24" t="s">
+        <v>459</v>
+      </c>
+      <c r="C141" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D141" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F141" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G141" s="27" t="s">
         <v>460</v>
-      </c>
-      <c r="C141" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D141" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E141" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F141" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G141" s="27" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="142" spans="1:7" ht="24">
       <c r="A142" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B142" s="24" t="s">
+        <v>461</v>
+      </c>
+      <c r="C142" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D142" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F142" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G142" s="27" t="s">
         <v>462</v>
-      </c>
-      <c r="C142" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D142" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E142" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F142" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G142" s="27" t="s">
-        <v>463</v>
       </c>
     </row>
     <row r="143" spans="1:7" ht="24">
       <c r="A143" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B143" s="24" t="s">
+        <v>463</v>
+      </c>
+      <c r="C143" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D143" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F143" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G143" s="27" t="s">
         <v>464</v>
-      </c>
-      <c r="C143" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D143" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E143" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F143" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G143" s="27" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="144" spans="1:7" ht="24">
       <c r="A144" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B144" s="24" t="s">
+        <v>465</v>
+      </c>
+      <c r="C144" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D144" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F144" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G144" s="27" t="s">
         <v>466</v>
-      </c>
-      <c r="C144" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D144" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E144" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F144" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G144" s="27" t="s">
-        <v>467</v>
       </c>
     </row>
     <row r="145" spans="1:7" ht="24">
       <c r="A145" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B145" s="24" t="s">
+        <v>467</v>
+      </c>
+      <c r="C145" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D145" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F145" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G145" s="27" t="s">
         <v>468</v>
-      </c>
-      <c r="C145" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D145" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E145" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F145" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G145" s="27" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="146" spans="1:7" ht="24">
       <c r="A146" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B146" s="24" t="s">
+        <v>469</v>
+      </c>
+      <c r="C146" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D146" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F146" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G146" s="27" t="s">
         <v>470</v>
-      </c>
-      <c r="C146" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D146" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E146" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F146" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G146" s="27" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="147" spans="1:7" ht="24">
       <c r="A147" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B147" s="24" t="s">
+        <v>471</v>
+      </c>
+      <c r="C147" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D147" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F147" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147" s="27" t="s">
         <v>472</v>
-      </c>
-      <c r="C147" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D147" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E147" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F147" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G147" s="27" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="148" spans="1:7" ht="24">
       <c r="A148" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B148" s="24" t="s">
+        <v>473</v>
+      </c>
+      <c r="C148" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D148" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F148" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="27" t="s">
         <v>474</v>
-      </c>
-      <c r="C148" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D148" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E148" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F148" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G148" s="27" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="149" spans="1:7" ht="24">
       <c r="A149" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B149" s="24" t="s">
+        <v>475</v>
+      </c>
+      <c r="C149" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D149" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F149" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" s="27" t="s">
         <v>476</v>
-      </c>
-      <c r="C149" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D149" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E149" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F149" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G149" s="27" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="150" spans="1:7" ht="24">
       <c r="A150" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B150" s="24" t="s">
+        <v>477</v>
+      </c>
+      <c r="C150" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D150" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E150" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F150" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="27" t="s">
         <v>478</v>
-      </c>
-      <c r="C150" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D150" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E150" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F150" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="27" t="s">
-        <v>479</v>
       </c>
     </row>
     <row r="151" spans="1:7" ht="24">
       <c r="A151" s="24" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B151" s="24" t="s">
+        <v>479</v>
+      </c>
+      <c r="C151" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D151" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F151" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" s="27" t="s">
         <v>480</v>
       </c>
-      <c r="C151" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D151" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="E151" s="24" t="s">
-        <v>456</v>
-      </c>
-      <c r="F151" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G151" s="27" t="s">
+    </row>
+    <row r="152" spans="1:7">
+      <c r="A152" s="24" t="s">
+        <v>447</v>
+      </c>
+      <c r="B152" s="24" t="s">
         <v>481</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" s="11" customFormat="1" ht="24">
-      <c r="A152" s="32" t="s">
-        <v>448</v>
-      </c>
-      <c r="B152" s="32" t="s">
+      <c r="C152" s="24" t="s">
+        <v>137</v>
+      </c>
+      <c r="D152" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152" s="24" t="s">
+        <v>455</v>
+      </c>
+      <c r="F152" s="24" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="30" t="s">
         <v>482</v>
-      </c>
-      <c r="C152" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="D152" s="33" t="s">
-        <v>24</v>
-      </c>
-      <c r="E152" s="32" t="s">
-        <v>456</v>
-      </c>
-      <c r="F152" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G152" s="34" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="153" spans="1:7" ht="39" customHeight="1">
       <c r="A153" s="24" t="s">
+        <v>483</v>
+      </c>
+      <c r="B153" s="37" t="s">
         <v>484</v>
       </c>
-      <c r="B153" s="37" t="s">
+      <c r="C153" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D153" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E153" s="24" t="s">
         <v>485</v>
       </c>
-      <c r="C153" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D153" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E153" s="24" t="s">
+      <c r="F153" s="17" t="s">
+        <v>96</v>
+      </c>
+      <c r="G153" s="27" t="s">
         <v>486</v>
-      </c>
-      <c r="F153" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="G153" s="27" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="154" spans="1:7" s="12" customFormat="1" ht="24">
       <c r="A154" s="24" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B154" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="C154" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="D154" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="E154" s="24" t="s">
         <v>488</v>
       </c>
-      <c r="C154" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D154" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E154" s="24" t="s">
+      <c r="F154" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G154" s="27" t="s">
         <v>489</v>
-      </c>
-      <c r="F154" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="G154" s="27" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="155" spans="1:7">
       <c r="A155" s="24" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B155" s="24" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C155" s="24" t="s">
         <v>9</v>
       </c>
       <c r="D155" s="17" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E155" s="38" t="s">
+        <v>491</v>
+      </c>
+      <c r="F155" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="G155" s="39" t="s">
         <v>492</v>
-      </c>
-      <c r="F155" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="G155" s="39" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="156" spans="1:7">
@@ -6483,15 +6454,15 @@
   <sheetData>
     <row r="1" spans="1:5" ht="30.75">
       <c r="A1" s="44" t="s">
+        <v>493</v>
+      </c>
+      <c r="B1" s="45" t="s">
         <v>494</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>495</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="42">
         <v>16</v>
@@ -6499,7 +6470,7 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="5" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B3" s="42">
         <v>4</v>
@@ -6507,7 +6478,7 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B4" s="42">
         <v>1</v>
@@ -6515,7 +6486,7 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B5" s="42">
         <v>2</v>
@@ -6524,7 +6495,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B6" s="42">
         <v>5</v>
@@ -6542,7 +6513,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="5" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B8" s="42">
         <v>7</v>
@@ -6551,7 +6522,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B9" s="42">
         <v>18</v>
@@ -6560,7 +6531,7 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="42">
         <v>15</v>
@@ -6569,7 +6540,7 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B11" s="42">
         <v>14</v>
@@ -6578,7 +6549,7 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12" s="5" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B12" s="42">
         <v>6</v>
@@ -6587,7 +6558,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>176</v>
+        <v>495</v>
       </c>
       <c r="B13" s="42">
         <v>12</v>
@@ -6596,7 +6567,7 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14" s="5" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B14" s="42">
         <v>16</v>
@@ -6605,7 +6576,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B15" s="42">
         <v>28</v>
@@ -6614,7 +6585,7 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
-        <v>120</v>
+        <v>496</v>
       </c>
       <c r="B16" s="42">
         <v>3</v>
@@ -6623,7 +6594,7 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B17" s="43">
         <f>SUM(B2:B16)</f>
@@ -6664,15 +6635,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75">
       <c r="A1" s="3" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2">
         <v>13</v>
@@ -6688,7 +6659,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -6696,7 +6667,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B5">
         <v>7</v>
@@ -6712,7 +6683,7 @@
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B7">
         <v>18</v>
@@ -6720,7 +6691,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B8">
         <v>2</v>
@@ -6728,7 +6699,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="5" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -6736,7 +6707,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -6744,7 +6715,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B11">
         <v>4</v>
@@ -6752,7 +6723,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B12">
         <v>10</v>
@@ -6760,7 +6731,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B13">
         <v>5</v>
@@ -6768,7 +6739,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B14">
         <v>4</v>
@@ -6776,7 +6747,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B15">
         <v>41</v>
@@ -6792,7 +6763,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B17">
         <v>17</v>
@@ -6800,7 +6771,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B18" s="4">
         <f>SUM(B2:B17)</f>
@@ -6841,15 +6812,15 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75">
       <c r="A1" s="46" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B1" s="46" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
       <c r="A2" s="42" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>24</v>
@@ -6857,7 +6828,7 @@
     </row>
     <row r="3" spans="1:2" ht="30.75">
       <c r="A3" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3">
         <v>10</v>
@@ -6865,7 +6836,7 @@
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1">
       <c r="A4" s="42" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4">
         <v>7</v>
@@ -6873,7 +6844,7 @@
     </row>
     <row r="5" spans="1:2" ht="30.75">
       <c r="A5" s="42" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>14</v>
@@ -6889,7 +6860,7 @@
     </row>
     <row r="7" spans="1:2" ht="30.75">
       <c r="A7" s="42" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B7">
         <v>45</v>
@@ -6897,7 +6868,7 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B8">
         <v>4</v>
@@ -6905,7 +6876,7 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="42" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B9">
         <v>2</v>
@@ -6913,7 +6884,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="43" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B10" s="4">
         <f>SUM(B2:B9)</f>

--- a/data/oer-catalog-2024-2025.xlsx
+++ b/data/oer-catalog-2024-2025.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="2970" documentId="11_DA57C2A605D271CF30FAF17FC8BCF4206AC7672E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E79DD36E-F27C-42B5-B6FE-018453EEC2F2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{27D11BC1-35FF-4E43-9830-75048CA005DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,6 @@
     <author>tc={AAE805E9-9988-450C-8A0E-4FC2EB2FEDE2}</author>
     <author>tc={316FD03D-FBA8-46BE-9B13-BDBF824B02A3}</author>
     <author>tc={AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}</author>
-    <author>tc={EF7DB6F4-CF1E-46D8-AD38-559F06874760}</author>
   </authors>
   <commentList>
     <comment ref="A9" authorId="0" shapeId="0" xr:uid="{EF2E148D-555A-4E50-8DD5-A09F00C654B8}">
@@ -78,20 +77,12 @@
     for group authored works -- cite the authoring entity described in the work</t>
       </text>
     </comment>
-    <comment ref="B154" authorId="4" shapeId="0" xr:uid="{EF7DB6F4-CF1E-46D8-AD38-559F06874760}">
-      <text>
-        <t>[Threaded comment]
-Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
-Comment:
-    For "ENG 210: Journalism: Its Scope and Use" Course</t>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="533">
   <si>
     <t>Campus </t>
   </si>
@@ -215,7 +206,7 @@
     <t>https://academicworks.cuny.edu/gc_oers/12/</t>
   </si>
   <si>
-    <t>Kingsborough</t>
+    <t>KCC</t>
   </si>
   <si>
     <t>SOC 38: Sociology of Gender</t>
@@ -233,7 +224,7 @@
     <t>Shawna M. Brandle</t>
   </si>
   <si>
-    <t>https://docs.google.com/presentation/d/1RhPfLiMuaOEO-jaH6pfVOz3IugtC4CozsyQ8ZLcF4v4/edit?usp=sharing</t>
+    <t>https://academicworks.cuny.edu/kb_oers/90/</t>
   </si>
   <si>
     <t>Baruch</t>
@@ -1636,10 +1627,110 @@
     <t>https://www.myopenmath.com/course/public.php?cid=107664</t>
   </si>
   <si>
+    <t>Principles of Marketing</t>
+  </si>
+  <si>
+    <t>Ngoc Pham</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/35</t>
+  </si>
+  <si>
+    <t>Course Conversion</t>
+  </si>
+  <si>
+    <t>Business 3100 Principles of Marketing</t>
+  </si>
+  <si>
+    <t>Consumer Behavior</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/24</t>
+  </si>
+  <si>
+    <t>BUSN 3140: Consumer Behavior</t>
+  </si>
+  <si>
+    <t>Principles of Selling</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/33</t>
+  </si>
+  <si>
+    <t>BUSN 3125: Principles of Selling</t>
+  </si>
+  <si>
+    <t>Principles of Computer Architecture</t>
+  </si>
+  <si>
+    <t>Miriam Briskman</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/31/</t>
+  </si>
+  <si>
+    <t>CISC 3310 Principles of Computer Architecture</t>
+  </si>
+  <si>
+    <t>Introduction to Digital Art</t>
+  </si>
+  <si>
+    <t>Matthew Mottel</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/30</t>
+  </si>
+  <si>
+    <t>ARTD 2811: Introduction to Digital Art</t>
+  </si>
+  <si>
+    <t>Digital Life Stories: Chicana/Latina Testimonio</t>
+  </si>
+  <si>
+    <t>Jasmine Mitchell</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+PRLS 2250 Digital Life Stories: Chicana/Latina Testimonio</t>
+  </si>
+  <si>
+    <t>Museum Anthropology</t>
+  </si>
+  <si>
+    <t>Kelly Britt</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/25/</t>
+  </si>
+  <si>
+    <t>Introduction to communication disorders</t>
+  </si>
+  <si>
+    <t>Anne Frederiksen</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/26</t>
+  </si>
+  <si>
+    <t>Latin American Culture</t>
+  </si>
+  <si>
+    <t>Berndardita Llanos</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/27</t>
+  </si>
+  <si>
     <t>CUNY Campus</t>
   </si>
   <si>
     <t>Number of OERs</t>
+  </si>
+  <si>
+    <t>Kingsborough</t>
   </si>
   <si>
     <t>NYCCT</t>
@@ -1661,7 +1752,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1736,6 +1827,24 @@
       <color theme="10"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0F374F"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1787,7 +1896,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -1878,12 +1987,60 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1966,10 +2123,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1992,6 +2145,65 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2334,15 +2546,12 @@
   <threadedComment ref="E121" dT="2026-03-19T21:24:38.22" personId="{ABB89055-104B-4067-BC1F-C93E3E956FFD}" id="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
     <text>for group authored works -- cite the authoring entity described in the work</text>
   </threadedComment>
-  <threadedComment ref="B154" dT="2026-03-22T21:31:03.50" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{EF7DB6F4-CF1E-46D8-AD38-559F06874760}">
-    <text>For "ENG 210: Journalism: Its Scope and Use" Course</text>
-  </threadedComment>
 </ThreadedComments>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C78B0D9-715E-4EDD-989F-8CB33D4C8A77}">
-  <dimension ref="A1:G271"/>
+  <dimension ref="A1:L271"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" style="7" customWidth="1"/>
@@ -2538,7 +2747,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" hidden="1">
       <c r="A9" s="21" t="s">
         <v>38</v>
       </c>
@@ -2562,25 +2771,25 @@
       </c>
     </row>
     <row r="10" spans="1:7" ht="24">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="23" t="s">
+      <c r="F10" s="17" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="76" t="s">
         <v>44</v>
       </c>
     </row>
@@ -3485,7 +3694,7 @@
       <c r="A50" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="41" t="s">
+      <c r="B50" s="39" t="s">
         <v>183</v>
       </c>
       <c r="C50" s="17" t="s">
@@ -3569,7 +3778,7 @@
       <c r="F53" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="G53" s="40" t="s">
+      <c r="G53" s="38" t="s">
         <v>195</v>
       </c>
     </row>
@@ -4356,7 +4565,7 @@
       </c>
     </row>
     <row r="88" spans="1:7" ht="24">
-      <c r="A88" s="24" t="s">
+      <c r="A88" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B88" s="24" t="s">
@@ -4379,7 +4588,7 @@
       </c>
     </row>
     <row r="89" spans="1:7" ht="24">
-      <c r="A89" s="24" t="s">
+      <c r="A89" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B89" s="24" t="s">
@@ -4402,7 +4611,7 @@
       </c>
     </row>
     <row r="90" spans="1:7" ht="24">
-      <c r="A90" s="24" t="s">
+      <c r="A90" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B90" s="24" t="s">
@@ -4425,7 +4634,7 @@
       </c>
     </row>
     <row r="91" spans="1:7" ht="33" customHeight="1">
-      <c r="A91" s="24" t="s">
+      <c r="A91" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B91" s="24" t="s">
@@ -4448,7 +4657,7 @@
       </c>
     </row>
     <row r="92" spans="1:7" ht="28.5" customHeight="1">
-      <c r="A92" s="24" t="s">
+      <c r="A92" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B92" s="24" t="s">
@@ -4471,7 +4680,7 @@
       </c>
     </row>
     <row r="93" spans="1:7" ht="24">
-      <c r="A93" s="24" t="s">
+      <c r="A93" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B93" s="24" t="s">
@@ -4494,7 +4703,7 @@
       </c>
     </row>
     <row r="94" spans="1:7" ht="24">
-      <c r="A94" s="24" t="s">
+      <c r="A94" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B94" s="24" t="s">
@@ -4512,12 +4721,12 @@
       <c r="F94" s="24" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="47" t="s">
+      <c r="G94" s="45" t="s">
         <v>317</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="48">
-      <c r="A95" s="24" t="s">
+      <c r="A95" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B95" s="24" t="s">
@@ -4540,7 +4749,7 @@
       </c>
     </row>
     <row r="96" spans="1:7" ht="24">
-      <c r="A96" s="24" t="s">
+      <c r="A96" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B96" s="24" t="s">
@@ -4563,7 +4772,7 @@
       </c>
     </row>
     <row r="97" spans="1:7" ht="24">
-      <c r="A97" s="24" t="s">
+      <c r="A97" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B97" s="24" t="s">
@@ -4585,8 +4794,8 @@
         <v>326</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="11" customFormat="1" ht="36">
-      <c r="A98" s="32" t="s">
+    <row r="98" spans="1:7" s="11" customFormat="1" ht="36" hidden="1">
+      <c r="A98" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B98" s="32" t="s">
@@ -4609,7 +4818,7 @@
       </c>
     </row>
     <row r="99" spans="1:7" ht="41.25" customHeight="1">
-      <c r="A99" s="24" t="s">
+      <c r="A99" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B99" s="24" t="s">
@@ -4632,7 +4841,7 @@
       </c>
     </row>
     <row r="100" spans="1:7" ht="42" customHeight="1">
-      <c r="A100" s="24" t="s">
+      <c r="A100" s="17" t="s">
         <v>38</v>
       </c>
       <c r="B100" s="24" t="s">
@@ -5666,7 +5875,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="145" spans="1:7" ht="24">
+    <row r="145" spans="1:12" ht="24">
       <c r="A145" s="24" t="s">
         <v>447</v>
       </c>
@@ -5689,7 +5898,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="146" spans="1:7" ht="24">
+    <row r="146" spans="1:12" ht="24">
       <c r="A146" s="24" t="s">
         <v>447</v>
       </c>
@@ -5712,7 +5921,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="147" spans="1:7" ht="24">
+    <row r="147" spans="1:12" ht="24">
       <c r="A147" s="24" t="s">
         <v>447</v>
       </c>
@@ -5735,7 +5944,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="24">
+    <row r="148" spans="1:12" ht="24">
       <c r="A148" s="24" t="s">
         <v>447</v>
       </c>
@@ -5758,7 +5967,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="149" spans="1:7" ht="24">
+    <row r="149" spans="1:12" ht="24">
       <c r="A149" s="24" t="s">
         <v>447</v>
       </c>
@@ -5781,7 +5990,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="24">
+    <row r="150" spans="1:12" ht="24">
       <c r="A150" s="24" t="s">
         <v>447</v>
       </c>
@@ -5804,7 +6013,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="24">
+    <row r="151" spans="1:12" ht="24">
       <c r="A151" s="24" t="s">
         <v>447</v>
       </c>
@@ -5827,7 +6036,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:12">
       <c r="A152" s="24" t="s">
         <v>447</v>
       </c>
@@ -5850,7 +6059,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="39" customHeight="1">
+    <row r="153" spans="1:12" ht="39" customHeight="1">
       <c r="A153" s="24" t="s">
         <v>483</v>
       </c>
@@ -5873,193 +6082,454 @@
         <v>486</v>
       </c>
     </row>
-    <row r="154" spans="1:7" s="12" customFormat="1" ht="24">
-      <c r="A154" s="24" t="s">
+    <row r="154" spans="1:12" s="12" customFormat="1" ht="24">
+      <c r="A154" s="63" t="s">
         <v>131</v>
       </c>
-      <c r="B154" s="25" t="s">
+      <c r="B154" s="72" t="s">
         <v>487</v>
       </c>
-      <c r="C154" s="24" t="s">
+      <c r="C154" s="63" t="s">
         <v>94</v>
       </c>
-      <c r="D154" s="18" t="s">
+      <c r="D154" s="73" t="s">
         <v>61</v>
       </c>
-      <c r="E154" s="24" t="s">
+      <c r="E154" s="63" t="s">
         <v>488</v>
       </c>
-      <c r="F154" s="24" t="s">
+      <c r="F154" s="63" t="s">
         <v>96</v>
       </c>
-      <c r="G154" s="27" t="s">
+      <c r="G154" s="74" t="s">
         <v>489</v>
       </c>
     </row>
-    <row r="155" spans="1:7">
-      <c r="A155" s="24" t="s">
+    <row r="155" spans="1:12">
+      <c r="A155" s="64" t="s">
         <v>483</v>
       </c>
-      <c r="B155" s="24" t="s">
+      <c r="B155" s="64" t="s">
         <v>490</v>
       </c>
-      <c r="C155" s="24" t="s">
+      <c r="C155" s="64" t="s">
         <v>9</v>
       </c>
-      <c r="D155" s="17" t="s">
+      <c r="D155" s="65" t="s">
         <v>275</v>
       </c>
-      <c r="E155" s="38" t="s">
+      <c r="E155" s="66" t="s">
         <v>491</v>
       </c>
-      <c r="F155" s="24" t="s">
+      <c r="F155" s="64" t="s">
         <v>280</v>
       </c>
-      <c r="G155" s="39" t="s">
+      <c r="G155" s="67" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="156" spans="1:7">
-      <c r="A156" s="8"/>
-      <c r="B156" s="8"/>
-      <c r="C156" s="8"/>
-      <c r="D156" s="8"/>
-      <c r="E156" s="8"/>
-    </row>
-    <row r="157" spans="1:7">
-      <c r="A157" s="8"/>
-      <c r="B157" s="8"/>
-      <c r="C157" s="8"/>
-      <c r="D157" s="8"/>
-      <c r="E157" s="8"/>
-    </row>
-    <row r="158" spans="1:7">
-      <c r="A158" s="8"/>
-      <c r="B158" s="8"/>
-      <c r="C158" s="8"/>
-      <c r="D158" s="8"/>
-      <c r="E158" s="8"/>
-    </row>
-    <row r="159" spans="1:7">
-      <c r="A159" s="8"/>
-      <c r="B159" s="8"/>
-      <c r="C159" s="8"/>
-      <c r="D159" s="8"/>
-      <c r="E159" s="8"/>
-    </row>
-    <row r="160" spans="1:7">
-      <c r="A160" s="8"/>
-      <c r="B160" s="8"/>
-      <c r="C160" s="8"/>
-      <c r="D160" s="8"/>
-      <c r="E160" s="8"/>
-    </row>
-    <row r="161" spans="1:5">
-      <c r="A161" s="8"/>
-      <c r="B161" s="8"/>
-      <c r="C161" s="8"/>
-      <c r="D161" s="8"/>
-      <c r="E161" s="8"/>
-    </row>
-    <row r="162" spans="1:5">
-      <c r="A162" s="8"/>
-      <c r="B162" s="8"/>
-      <c r="C162" s="8"/>
-      <c r="D162" s="8"/>
-      <c r="E162" s="8"/>
-    </row>
-    <row r="163" spans="1:5">
-      <c r="A163" s="8"/>
-      <c r="B163" s="8"/>
-      <c r="C163" s="8"/>
-      <c r="D163" s="8"/>
-      <c r="E163" s="8"/>
-    </row>
-    <row r="164" spans="1:5">
-      <c r="A164" s="8"/>
-      <c r="B164" s="8"/>
-      <c r="C164" s="8"/>
-      <c r="D164" s="8"/>
-      <c r="E164" s="8"/>
-    </row>
-    <row r="165" spans="1:5">
+    <row r="156" spans="1:12" ht="30.75">
+      <c r="A156" t="s">
+        <v>483</v>
+      </c>
+      <c r="B156" t="s">
+        <v>493</v>
+      </c>
+      <c r="C156" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" t="s">
+        <v>494</v>
+      </c>
+      <c r="F156" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" s="68" t="s">
+        <v>495</v>
+      </c>
+      <c r="H156" s="59" t="s">
+        <v>496</v>
+      </c>
+      <c r="I156" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J156" s="46" t="s">
+        <v>497</v>
+      </c>
+      <c r="K156" s="48" t="s">
+        <v>495</v>
+      </c>
+      <c r="L156" s="46"/>
+    </row>
+    <row r="157" spans="1:12" ht="30.75">
+      <c r="A157" t="s">
+        <v>483</v>
+      </c>
+      <c r="B157" t="s">
+        <v>498</v>
+      </c>
+      <c r="C157" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" t="s">
+        <v>494</v>
+      </c>
+      <c r="F157" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="68" t="s">
+        <v>499</v>
+      </c>
+      <c r="H157" s="60" t="s">
+        <v>496</v>
+      </c>
+      <c r="I157" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J157" s="49" t="s">
+        <v>500</v>
+      </c>
+      <c r="K157" s="48" t="s">
+        <v>499</v>
+      </c>
+      <c r="L157" s="49"/>
+    </row>
+    <row r="158" spans="1:12" ht="30.75">
+      <c r="A158" t="s">
+        <v>483</v>
+      </c>
+      <c r="B158" t="s">
+        <v>501</v>
+      </c>
+      <c r="C158" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="40" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" t="s">
+        <v>494</v>
+      </c>
+      <c r="F158" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="68" t="s">
+        <v>502</v>
+      </c>
+      <c r="H158" s="60" t="s">
+        <v>496</v>
+      </c>
+      <c r="I158" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="J158" s="49" t="s">
+        <v>503</v>
+      </c>
+      <c r="K158" s="48" t="s">
+        <v>502</v>
+      </c>
+      <c r="L158" s="49"/>
+    </row>
+    <row r="159" spans="1:12" ht="30.75">
+      <c r="A159" t="s">
+        <v>483</v>
+      </c>
+      <c r="B159" t="s">
+        <v>504</v>
+      </c>
+      <c r="C159" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="40" t="s">
+        <v>47</v>
+      </c>
+      <c r="E159" t="s">
+        <v>505</v>
+      </c>
+      <c r="F159" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159" s="68" t="s">
+        <v>506</v>
+      </c>
+      <c r="H159" s="61" t="s">
+        <v>496</v>
+      </c>
+      <c r="I159" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="J159" s="50" t="s">
+        <v>507</v>
+      </c>
+      <c r="K159" s="52" t="s">
+        <v>506</v>
+      </c>
+      <c r="L159" s="50"/>
+    </row>
+    <row r="160" spans="1:12" ht="29.25">
+      <c r="A160" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B160" s="69" t="s">
+        <v>508</v>
+      </c>
+      <c r="C160" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="69" t="s">
+        <v>142</v>
+      </c>
+      <c r="E160" s="70" t="s">
+        <v>509</v>
+      </c>
+      <c r="F160" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="71" t="s">
+        <v>510</v>
+      </c>
+      <c r="H160" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="I160" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J160" s="55" t="s">
+        <v>511</v>
+      </c>
+      <c r="K160" s="56" t="s">
+        <v>510</v>
+      </c>
+      <c r="L160" s="53"/>
+    </row>
+    <row r="161" spans="1:12" ht="29.25">
+      <c r="A161" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B161" s="69" t="s">
+        <v>512</v>
+      </c>
+      <c r="C161" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="69" t="s">
+        <v>61</v>
+      </c>
+      <c r="E161" s="70" t="s">
+        <v>513</v>
+      </c>
+      <c r="F161" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G161" s="71" t="s">
+        <v>514</v>
+      </c>
+      <c r="H161" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="I161" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J161" s="57" t="s">
+        <v>515</v>
+      </c>
+      <c r="K161" s="56" t="s">
+        <v>514</v>
+      </c>
+      <c r="L161" s="53"/>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B162" s="69" t="s">
+        <v>516</v>
+      </c>
+      <c r="C162" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162" s="70" t="s">
+        <v>517</v>
+      </c>
+      <c r="F162" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="71" t="s">
+        <v>518</v>
+      </c>
+      <c r="H162" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="I162" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J162" s="53" t="s">
+        <v>516</v>
+      </c>
+      <c r="K162" s="56" t="s">
+        <v>518</v>
+      </c>
+      <c r="L162" s="58"/>
+    </row>
+    <row r="163" spans="1:12" ht="29.25">
+      <c r="A163" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B163" s="69" t="s">
+        <v>519</v>
+      </c>
+      <c r="C163" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="69" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" s="70" t="s">
+        <v>520</v>
+      </c>
+      <c r="F163" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" s="71" t="s">
+        <v>521</v>
+      </c>
+      <c r="H163" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="I163" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J163" s="53" t="s">
+        <v>519</v>
+      </c>
+      <c r="K163" s="56" t="s">
+        <v>521</v>
+      </c>
+      <c r="L163" s="58"/>
+    </row>
+    <row r="164" spans="1:12" ht="24">
+      <c r="A164" s="69" t="s">
+        <v>483</v>
+      </c>
+      <c r="B164" s="69" t="s">
+        <v>522</v>
+      </c>
+      <c r="C164" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="75" t="s">
+        <v>61</v>
+      </c>
+      <c r="E164" s="70" t="s">
+        <v>523</v>
+      </c>
+      <c r="F164" s="64" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="71" t="s">
+        <v>524</v>
+      </c>
+      <c r="H164" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="I164" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="J164" s="53" t="s">
+        <v>522</v>
+      </c>
+      <c r="K164" s="56" t="s">
+        <v>524</v>
+      </c>
+      <c r="L164" s="58"/>
+    </row>
+    <row r="165" spans="1:12">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:12">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:12">
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:12">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:12">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:12">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:12">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:12">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:12">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:12">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:12">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:12">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
@@ -6411,9 +6881,27 @@
     <hyperlink ref="G77" r:id="rId152" xr:uid="{A36D9556-A422-464B-917E-B56AB2B55911}"/>
     <hyperlink ref="G155" r:id="rId153" xr:uid="{FFDBE46E-7115-4E9A-84E3-780E0A8239E2}"/>
     <hyperlink ref="G9" r:id="rId154" xr:uid="{3B27917C-C3DD-48E9-B5E8-BBEEF07D44CB}"/>
+    <hyperlink ref="K156" r:id="rId155" xr:uid="{21584492-E056-4A93-BE24-99DD5DA60F1C}"/>
+    <hyperlink ref="K157" r:id="rId156" xr:uid="{55D78088-8150-4374-AEEE-0A27983FE364}"/>
+    <hyperlink ref="K158" r:id="rId157" xr:uid="{33226C34-69A7-4175-A160-0A1F73070154}"/>
+    <hyperlink ref="K159" r:id="rId158" xr:uid="{66C7D8CB-6686-42F3-8A5F-94F3AB5C69F2}"/>
+    <hyperlink ref="K162" r:id="rId159" xr:uid="{01C48349-98A9-4A36-AA01-FC42D0B232D9}"/>
+    <hyperlink ref="K163" r:id="rId160" xr:uid="{91859E15-9B4B-4CE1-AD2D-4DFC755EC58B}"/>
+    <hyperlink ref="K164" r:id="rId161" xr:uid="{F2C7F609-7DAB-475A-B517-0D1B64281C5F}"/>
+    <hyperlink ref="K161" r:id="rId162" xr:uid="{3CE37E7A-6D4A-4AAA-BE1F-CFA90EE5BED9}"/>
+    <hyperlink ref="K160" r:id="rId163" xr:uid="{F573405B-06D8-49AD-84F1-A25CA348A467}"/>
+    <hyperlink ref="G156" r:id="rId164" xr:uid="{D5E77608-998D-48BE-96A8-6A4D3F46A02F}"/>
+    <hyperlink ref="G157" r:id="rId165" xr:uid="{200F9D4A-9AF2-4D9D-9952-9DC2C3BD2D78}"/>
+    <hyperlink ref="G158" r:id="rId166" xr:uid="{7595CFC8-7AB0-4C4E-B3BE-FB52090BB1C7}"/>
+    <hyperlink ref="G159" r:id="rId167" xr:uid="{EA203628-A8A6-4BED-B26B-C6792385937B}"/>
+    <hyperlink ref="G162" r:id="rId168" xr:uid="{5686D2E3-9F2B-499C-AE38-3F74D1A0B4AC}"/>
+    <hyperlink ref="G163" r:id="rId169" xr:uid="{6E3C40DC-DC0A-4FD8-BC45-D40202B3A66A}"/>
+    <hyperlink ref="G164" r:id="rId170" xr:uid="{66B90635-FA20-4B3A-95B5-E735EACBBB93}"/>
+    <hyperlink ref="G161" r:id="rId171" xr:uid="{058563C7-3039-464C-AAAA-5E8C55B5966B}"/>
+    <hyperlink ref="G160" r:id="rId172" xr:uid="{DCCD4AB1-6174-4770-B88D-6D9A55AC89E9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId155"/>
+  <legacyDrawing r:id="rId173"/>
 </worksheet>
 </file>
 
@@ -6423,7 +6911,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="42" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="40" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
@@ -6453,18 +6941,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30.75">
-      <c r="A1" s="44" t="s">
-        <v>493</v>
-      </c>
-      <c r="B1" s="45" t="s">
-        <v>494</v>
+      <c r="A1" s="42" t="s">
+        <v>525</v>
+      </c>
+      <c r="B1" s="43" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="42">
+      <c r="B2" s="40">
         <v>16</v>
       </c>
     </row>
@@ -6472,7 +6960,7 @@
       <c r="A3" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="B3" s="42">
+      <c r="B3" s="40">
         <v>4</v>
       </c>
     </row>
@@ -6480,7 +6968,7 @@
       <c r="A4" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="B4" s="42">
+      <c r="B4" s="40">
         <v>1</v>
       </c>
     </row>
@@ -6488,8 +6976,8 @@
       <c r="A5" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="B5" s="42">
-        <v>2</v>
+      <c r="B5" s="40">
+        <v>11</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -6497,7 +6985,7 @@
       <c r="A6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="42">
+      <c r="B6" s="40">
         <v>5</v>
       </c>
       <c r="E6" s="1"/>
@@ -6506,7 +6994,7 @@
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="42">
+      <c r="B7" s="40">
         <v>7</v>
       </c>
       <c r="E7" s="1"/>
@@ -6515,7 +7003,7 @@
       <c r="A8" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="42">
+      <c r="B8" s="40">
         <v>7</v>
       </c>
       <c r="E8" s="1"/>
@@ -6524,16 +7012,16 @@
       <c r="A9" s="5" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="42">
+      <c r="B9" s="40">
         <v>18</v>
       </c>
       <c r="E9" s="1"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10" s="42">
+        <v>527</v>
+      </c>
+      <c r="B10" s="40">
         <v>15</v>
       </c>
       <c r="E10" s="1"/>
@@ -6542,7 +7030,7 @@
       <c r="A11" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="42">
+      <c r="B11" s="40">
         <v>14</v>
       </c>
       <c r="E11" s="1"/>
@@ -6551,16 +7039,16 @@
       <c r="A12" s="5" t="s">
         <v>428</v>
       </c>
-      <c r="B12" s="42">
+      <c r="B12" s="40">
         <v>6</v>
       </c>
       <c r="E12" s="1"/>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="5" t="s">
-        <v>495</v>
-      </c>
-      <c r="B13" s="42">
+        <v>528</v>
+      </c>
+      <c r="B13" s="40">
         <v>12</v>
       </c>
       <c r="E13" s="1"/>
@@ -6569,7 +7057,7 @@
       <c r="A14" s="5" t="s">
         <v>447</v>
       </c>
-      <c r="B14" s="42">
+      <c r="B14" s="40">
         <v>16</v>
       </c>
       <c r="E14" s="1"/>
@@ -6578,27 +7066,27 @@
       <c r="A15" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B15" s="42">
+      <c r="B15" s="40">
         <v>28</v>
       </c>
       <c r="E15" s="1"/>
     </row>
     <row r="16" spans="1:5">
       <c r="A16" s="5" t="s">
-        <v>496</v>
-      </c>
-      <c r="B16" s="42">
+        <v>529</v>
+      </c>
+      <c r="B16" s="40">
         <v>3</v>
       </c>
       <c r="E16" s="1"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="B17" s="43">
+        <v>530</v>
+      </c>
+      <c r="B17" s="41">
         <f>SUM(B2:B16)</f>
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -6635,10 +7123,10 @@
   <sheetData>
     <row r="1" spans="1:2" ht="30.75">
       <c r="A1" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="B1" s="46" t="s">
-        <v>494</v>
+        <v>531</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -6646,7 +7134,7 @@
         <v>47</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -6654,7 +7142,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -6686,7 +7174,7 @@
         <v>61</v>
       </c>
       <c r="B7">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -6710,7 +7198,7 @@
         <v>142</v>
       </c>
       <c r="B10">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -6750,7 +7238,7 @@
         <v>23</v>
       </c>
       <c r="B15">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -6771,11 +7259,11 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" s="4" t="s">
-        <v>497</v>
+        <v>530</v>
       </c>
       <c r="B18" s="4">
         <f>SUM(B2:B17)</f>
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -6806,20 +7294,20 @@
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" style="42" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" style="40" customWidth="1"/>
     <col min="2" max="2" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30.75">
-      <c r="A1" s="46" t="s">
-        <v>499</v>
-      </c>
-      <c r="B1" s="46" t="s">
-        <v>494</v>
+      <c r="A1" s="44" t="s">
+        <v>532</v>
+      </c>
+      <c r="B1" s="44" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="30.75">
-      <c r="A2" s="42" t="s">
+      <c r="A2" s="40" t="s">
         <v>75</v>
       </c>
       <c r="B2">
@@ -6827,15 +7315,15 @@
       </c>
     </row>
     <row r="3" spans="1:2" ht="30.75">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="40" t="s">
         <v>68</v>
       </c>
       <c r="B3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15.75" customHeight="1">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="40" t="s">
         <v>193</v>
       </c>
       <c r="B4">
@@ -6843,23 +7331,23 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="30.75">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="40" t="s">
         <v>27</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="30.75">
-      <c r="A6" s="42" t="s">
+      <c r="A6" s="40" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>48</v>
+        <v>57</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="30.75">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="40" t="s">
         <v>94</v>
       </c>
       <c r="B7">
@@ -6867,15 +7355,15 @@
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="42" t="s">
+      <c r="A8" s="40" t="s">
         <v>137</v>
       </c>
       <c r="B8">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="42" t="s">
+      <c r="A9" s="40" t="s">
         <v>121</v>
       </c>
       <c r="B9">
@@ -6883,12 +7371,12 @@
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="43" t="s">
-        <v>497</v>
+      <c r="A10" s="41" t="s">
+        <v>530</v>
       </c>
       <c r="B10" s="4">
         <f>SUM(B2:B9)</f>
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/data/oer-catalog-2024-2025.xlsx
+++ b/data/oer-catalog-2024-2025.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29930"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27D11BC1-35FF-4E43-9830-75048CA005DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elliotgalvis/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EF4B2B-B60A-3C49-8D0D-3A2CB405A5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="780" windowWidth="30200" windowHeight="20640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="6" r:id="rId1"/>
@@ -1752,7 +1757,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1830,19 +1835,19 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0F374F"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -2238,9 +2243,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2278,7 +2283,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2384,7 +2389,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2526,7 +2531,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2552,18 +2557,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C78B0D9-715E-4EDD-989F-8CB33D4C8A77}">
   <dimension ref="A1:L271"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="33.7109375" style="7" customWidth="1"/>
-    <col min="3" max="3" width="21.42578125" style="7" customWidth="1"/>
-    <col min="4" max="4" width="19.5703125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.85546875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="24.85546875" style="8" customWidth="1"/>
-    <col min="7" max="7" width="29.7109375" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" style="7" customWidth="1"/>
+    <col min="2" max="2" width="33.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="7" customWidth="1"/>
+    <col min="4" max="4" width="19.5" style="2" customWidth="1"/>
+    <col min="5" max="5" width="24.83203125" style="7" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" style="8" customWidth="1"/>
+    <col min="7" max="7" width="29.6640625" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="46.5" customHeight="1">
+    <row r="1" spans="1:7" s="6" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
@@ -2586,7 +2591,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" s="9" customFormat="1" ht="24">
+    <row r="2" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>7</v>
       </c>
@@ -2609,7 +2614,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="9" customFormat="1">
+    <row r="3" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="17" t="s">
         <v>7</v>
       </c>
@@ -2632,7 +2637,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:7" s="9" customFormat="1" ht="24">
+    <row r="4" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" s="17" t="s">
         <v>7</v>
       </c>
@@ -2655,7 +2660,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="11" customFormat="1" ht="24">
+    <row r="5" spans="1:7" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.2">
       <c r="A5" s="17" t="s">
         <v>7</v>
       </c>
@@ -2678,7 +2683,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="24">
+    <row r="6" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A6" s="17" t="s">
         <v>7</v>
       </c>
@@ -2701,7 +2706,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="24">
+    <row r="7" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A7" s="17" t="s">
         <v>7</v>
       </c>
@@ -2724,7 +2729,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="234" customHeight="1">
+    <row r="8" spans="1:7" ht="234" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="17" t="s">
         <v>7</v>
       </c>
@@ -2747,7 +2752,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:7" hidden="1">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>38</v>
       </c>
@@ -2770,7 +2775,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24">
+    <row r="10" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A10" s="17" t="s">
         <v>38</v>
       </c>
@@ -2793,7 +2798,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="24">
+    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.2">
       <c r="A11" s="24" t="s">
         <v>45</v>
       </c>
@@ -2816,7 +2821,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="24">
+    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.2">
       <c r="A12" s="24" t="s">
         <v>45</v>
       </c>
@@ -2839,7 +2844,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="24">
+    <row r="13" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A13" s="24" t="s">
         <v>45</v>
       </c>
@@ -2862,7 +2867,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="36">
+    <row r="14" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A14" s="24" t="s">
         <v>45</v>
       </c>
@@ -2885,7 +2890,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="24">
+    <row r="15" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A15" s="24" t="s">
         <v>45</v>
       </c>
@@ -2908,7 +2913,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="24">
+    <row r="16" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A16" s="24" t="s">
         <v>45</v>
       </c>
@@ -2931,7 +2936,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="24">
+    <row r="17" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A17" s="24" t="s">
         <v>45</v>
       </c>
@@ -2954,7 +2959,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="24">
+    <row r="18" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A18" s="24" t="s">
         <v>45</v>
       </c>
@@ -2977,7 +2982,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="24">
+    <row r="19" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A19" s="24" t="s">
         <v>45</v>
       </c>
@@ -3000,7 +3005,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="24">
+    <row r="20" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A20" s="24" t="s">
         <v>45</v>
       </c>
@@ -3023,7 +3028,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="24">
+    <row r="21" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A21" s="24" t="s">
         <v>45</v>
       </c>
@@ -3046,7 +3051,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="24">
+    <row r="22" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A22" s="24" t="s">
         <v>45</v>
       </c>
@@ -3069,7 +3074,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="36">
+    <row r="23" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A23" s="24" t="s">
         <v>45</v>
       </c>
@@ -3092,7 +3097,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="36">
+    <row r="24" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A24" s="24" t="s">
         <v>45</v>
       </c>
@@ -3115,7 +3120,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="24">
+    <row r="25" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A25" s="24" t="s">
         <v>45</v>
       </c>
@@ -3138,7 +3143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="24">
+    <row r="26" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A26" s="24" t="s">
         <v>45</v>
       </c>
@@ -3161,7 +3166,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="24" t="s">
         <v>101</v>
       </c>
@@ -3184,7 +3189,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="24">
+    <row r="28" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A28" s="24" t="s">
         <v>101</v>
       </c>
@@ -3207,7 +3212,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="24">
+    <row r="29" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A29" s="24" t="s">
         <v>101</v>
       </c>
@@ -3230,7 +3235,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="42" customHeight="1">
+    <row r="30" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="24" t="s">
         <v>101</v>
       </c>
@@ -3253,7 +3258,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="24">
+    <row r="31" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A31" s="24" t="s">
         <v>101</v>
       </c>
@@ -3276,7 +3281,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="24">
+    <row r="32" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A32" s="24" t="s">
         <v>119</v>
       </c>
@@ -3299,7 +3304,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="24">
+    <row r="33" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A33" s="24" t="s">
         <v>119</v>
       </c>
@@ -3322,7 +3327,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="34" spans="1:7" s="9" customFormat="1" ht="36">
+    <row r="34" spans="1:7" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A34" s="24" t="s">
         <v>119</v>
       </c>
@@ -3345,7 +3350,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="24">
+    <row r="35" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A35" s="24" t="s">
         <v>131</v>
       </c>
@@ -3368,7 +3373,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="24">
+    <row r="36" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A36" s="24" t="s">
         <v>131</v>
       </c>
@@ -3391,7 +3396,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="24">
+    <row r="37" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A37" s="24" t="s">
         <v>131</v>
       </c>
@@ -3414,7 +3419,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="24">
+    <row r="38" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A38" s="24" t="s">
         <v>131</v>
       </c>
@@ -3437,7 +3442,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="33" customHeight="1">
+    <row r="39" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="24" t="s">
         <v>131</v>
       </c>
@@ -3460,7 +3465,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="104.25" customHeight="1">
+    <row r="40" spans="1:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="24" t="s">
         <v>131</v>
       </c>
@@ -3483,7 +3488,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="27" customHeight="1">
+    <row r="41" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="24" t="s">
         <v>131</v>
       </c>
@@ -3506,7 +3511,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="41.25" customHeight="1">
+    <row r="42" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="24" t="s">
         <v>131</v>
       </c>
@@ -3529,7 +3534,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="24">
+    <row r="43" spans="1:7" ht="29" x14ac:dyDescent="0.2">
       <c r="A43" s="24" t="s">
         <v>131</v>
       </c>
@@ -3552,7 +3557,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="24">
+    <row r="44" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A44" s="24" t="s">
         <v>131</v>
       </c>
@@ -3575,7 +3580,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="41.25" customHeight="1">
+    <row r="45" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="24" t="s">
         <v>131</v>
       </c>
@@ -3598,7 +3603,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="28.5" customHeight="1">
+    <row r="46" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="24" t="s">
         <v>131</v>
       </c>
@@ -3621,7 +3626,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="24" t="s">
         <v>131</v>
       </c>
@@ -3644,7 +3649,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="24">
+    <row r="48" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A48" s="24" t="s">
         <v>175</v>
       </c>
@@ -3667,7 +3672,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="24">
+    <row r="49" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A49" s="24" t="s">
         <v>175</v>
       </c>
@@ -3690,7 +3695,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="50" spans="1:7" s="9" customFormat="1" ht="36">
+    <row r="50" spans="1:7" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A50" s="17" t="s">
         <v>175</v>
       </c>
@@ -3713,7 +3718,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="24">
+    <row r="51" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A51" s="24" t="s">
         <v>175</v>
       </c>
@@ -3736,7 +3741,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="24">
+    <row r="52" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A52" s="24" t="s">
         <v>175</v>
       </c>
@@ -3759,7 +3764,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="53" spans="1:7" s="9" customFormat="1" ht="36">
+    <row r="53" spans="1:7" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
       <c r="A53" s="17" t="s">
         <v>175</v>
       </c>
@@ -3782,7 +3787,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="41.25" customHeight="1">
+    <row r="54" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="24" t="s">
         <v>175</v>
       </c>
@@ -3805,7 +3810,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="24">
+    <row r="55" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A55" s="24" t="s">
         <v>175</v>
       </c>
@@ -3828,7 +3833,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="36">
+    <row r="56" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A56" s="24" t="s">
         <v>175</v>
       </c>
@@ -3851,7 +3856,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="53.25" customHeight="1">
+    <row r="57" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="24" t="s">
         <v>175</v>
       </c>
@@ -3874,7 +3879,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="72">
+    <row r="58" spans="1:7" ht="84" x14ac:dyDescent="0.2">
       <c r="A58" s="24" t="s">
         <v>175</v>
       </c>
@@ -3897,7 +3902,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="31.5" customHeight="1">
+    <row r="59" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="24" t="s">
         <v>175</v>
       </c>
@@ -3920,7 +3925,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="24">
+    <row r="60" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A60" s="24" t="s">
         <v>213</v>
       </c>
@@ -3943,7 +3948,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="24">
+    <row r="61" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A61" s="24" t="s">
         <v>213</v>
       </c>
@@ -3966,7 +3971,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="24">
+    <row r="62" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A62" s="24" t="s">
         <v>213</v>
       </c>
@@ -3989,7 +3994,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="24">
+    <row r="63" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A63" s="24" t="s">
         <v>213</v>
       </c>
@@ -4012,7 +4017,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="24">
+    <row r="64" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A64" s="24" t="s">
         <v>213</v>
       </c>
@@ -4035,7 +4040,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="24" t="s">
         <v>213</v>
       </c>
@@ -4058,7 +4063,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="24" t="s">
         <v>213</v>
       </c>
@@ -4081,7 +4086,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="42.75" customHeight="1">
+    <row r="67" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="24" t="s">
         <v>213</v>
       </c>
@@ -4104,7 +4109,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="24">
+    <row r="68" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A68" s="24" t="s">
         <v>213</v>
       </c>
@@ -4127,7 +4132,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="29.25" customHeight="1">
+    <row r="69" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="24" t="s">
         <v>213</v>
       </c>
@@ -4150,7 +4155,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="24">
+    <row r="70" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A70" s="24" t="s">
         <v>213</v>
       </c>
@@ -4173,7 +4178,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="24">
+    <row r="71" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A71" s="24" t="s">
         <v>213</v>
       </c>
@@ -4196,7 +4201,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="24">
+    <row r="72" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A72" s="24" t="s">
         <v>213</v>
       </c>
@@ -4219,7 +4224,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="24">
+    <row r="73" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A73" s="24" t="s">
         <v>213</v>
       </c>
@@ -4242,7 +4247,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="24">
+    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.2">
       <c r="A74" s="24" t="s">
         <v>213</v>
       </c>
@@ -4265,7 +4270,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="24">
+    <row r="75" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A75" s="24" t="s">
         <v>213</v>
       </c>
@@ -4288,7 +4293,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="24">
+    <row r="76" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A76" s="24" t="s">
         <v>213</v>
       </c>
@@ -4311,7 +4316,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="77" spans="1:7" s="9" customFormat="1" ht="24">
+    <row r="77" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.2">
       <c r="A77" s="17" t="s">
         <v>213</v>
       </c>
@@ -4334,7 +4339,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="24">
+    <row r="78" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A78" s="24" t="s">
         <v>213</v>
       </c>
@@ -4357,7 +4362,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="24">
+    <row r="79" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A79" s="24" t="s">
         <v>213</v>
       </c>
@@ -4380,7 +4385,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="24" t="s">
         <v>213</v>
       </c>
@@ -4403,7 +4408,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="24" t="s">
         <v>213</v>
       </c>
@@ -4426,7 +4431,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="24">
+    <row r="82" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A82" s="24" t="s">
         <v>213</v>
       </c>
@@ -4449,7 +4454,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="24">
+    <row r="83" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A83" s="24" t="s">
         <v>213</v>
       </c>
@@ -4472,7 +4477,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="36">
+    <row r="84" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A84" s="24" t="s">
         <v>213</v>
       </c>
@@ -4495,7 +4500,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="85" spans="1:7" ht="36">
+    <row r="85" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A85" s="24" t="s">
         <v>213</v>
       </c>
@@ -4518,7 +4523,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="24">
+    <row r="86" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A86" s="24" t="s">
         <v>213</v>
       </c>
@@ -4541,7 +4546,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="24">
+    <row r="87" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A87" s="24" t="s">
         <v>213</v>
       </c>
@@ -4564,7 +4569,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="24">
+    <row r="88" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A88" s="17" t="s">
         <v>38</v>
       </c>
@@ -4587,7 +4592,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="24">
+    <row r="89" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A89" s="17" t="s">
         <v>38</v>
       </c>
@@ -4610,7 +4615,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="24">
+    <row r="90" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A90" s="17" t="s">
         <v>38</v>
       </c>
@@ -4633,7 +4638,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="33" customHeight="1">
+    <row r="91" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="17" t="s">
         <v>38</v>
       </c>
@@ -4656,7 +4661,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="28.5" customHeight="1">
+    <row r="92" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="17" t="s">
         <v>38</v>
       </c>
@@ -4679,7 +4684,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="24">
+    <row r="93" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A93" s="17" t="s">
         <v>38</v>
       </c>
@@ -4702,7 +4707,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="94" spans="1:7" ht="24">
+    <row r="94" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A94" s="17" t="s">
         <v>38</v>
       </c>
@@ -4725,7 +4730,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="95" spans="1:7" ht="48">
+    <row r="95" spans="1:7" ht="56" x14ac:dyDescent="0.2">
       <c r="A95" s="17" t="s">
         <v>38</v>
       </c>
@@ -4748,7 +4753,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="96" spans="1:7" ht="24">
+    <row r="96" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A96" s="17" t="s">
         <v>38</v>
       </c>
@@ -4771,7 +4776,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="97" spans="1:7" ht="24">
+    <row r="97" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A97" s="17" t="s">
         <v>38</v>
       </c>
@@ -4794,7 +4799,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="98" spans="1:7" s="11" customFormat="1" ht="36" hidden="1">
+    <row r="98" spans="1:7" s="11" customFormat="1" ht="42" hidden="1" x14ac:dyDescent="0.2">
       <c r="A98" s="17" t="s">
         <v>38</v>
       </c>
@@ -4817,7 +4822,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="99" spans="1:7" ht="41.25" customHeight="1">
+    <row r="99" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="17" t="s">
         <v>38</v>
       </c>
@@ -4840,7 +4845,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="100" spans="1:7" ht="42" customHeight="1">
+    <row r="100" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="17" t="s">
         <v>38</v>
       </c>
@@ -4863,7 +4868,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="101" spans="1:7" ht="24">
+    <row r="101" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A101" s="24" t="s">
         <v>335</v>
       </c>
@@ -4886,7 +4891,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="24" t="s">
         <v>340</v>
       </c>
@@ -4909,7 +4914,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="24" t="s">
         <v>340</v>
       </c>
@@ -4932,7 +4937,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="104" spans="1:7" ht="24">
+    <row r="104" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A104" s="24" t="s">
         <v>340</v>
       </c>
@@ -4955,7 +4960,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="105" spans="1:7" ht="48">
+    <row r="105" spans="1:7" ht="56" x14ac:dyDescent="0.2">
       <c r="A105" s="24" t="s">
         <v>340</v>
       </c>
@@ -4978,7 +4983,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="106" spans="1:7" ht="36">
+    <row r="106" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A106" s="24" t="s">
         <v>353</v>
       </c>
@@ -5001,7 +5006,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="107" spans="1:7" ht="24">
+    <row r="107" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A107" s="24" t="s">
         <v>353</v>
       </c>
@@ -5024,7 +5029,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="108" spans="1:7" ht="24">
+    <row r="108" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A108" s="24" t="s">
         <v>353</v>
       </c>
@@ -5047,7 +5052,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="109" spans="1:7" ht="48">
+    <row r="109" spans="1:7" ht="42" x14ac:dyDescent="0.2">
       <c r="A109" s="24" t="s">
         <v>353</v>
       </c>
@@ -5070,7 +5075,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="110" spans="1:7" ht="24">
+    <row r="110" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A110" s="24" t="s">
         <v>353</v>
       </c>
@@ -5093,7 +5098,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="111" spans="1:7" ht="24">
+    <row r="111" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A111" s="24" t="s">
         <v>353</v>
       </c>
@@ -5116,7 +5121,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="112" spans="1:7" ht="108.75" customHeight="1">
+    <row r="112" spans="1:7" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="24" t="s">
         <v>353</v>
       </c>
@@ -5139,7 +5144,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="113" spans="1:7" ht="83.25" customHeight="1">
+    <row r="113" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="24" t="s">
         <v>375</v>
       </c>
@@ -5162,7 +5167,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="114" spans="1:7" ht="24">
+    <row r="114" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A114" s="24" t="s">
         <v>375</v>
       </c>
@@ -5185,7 +5190,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="115" spans="1:7" ht="24">
+    <row r="115" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A115" s="24" t="s">
         <v>375</v>
       </c>
@@ -5208,7 +5213,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="116" spans="1:7" ht="34.5" customHeight="1">
+    <row r="116" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="24" t="s">
         <v>375</v>
       </c>
@@ -5231,7 +5236,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="117" spans="1:7" ht="24">
+    <row r="117" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A117" s="24" t="s">
         <v>375</v>
       </c>
@@ -5254,7 +5259,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="24">
+    <row r="118" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A118" s="24" t="s">
         <v>375</v>
       </c>
@@ -5277,7 +5282,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="119" spans="1:7" ht="24">
+    <row r="119" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A119" s="24" t="s">
         <v>375</v>
       </c>
@@ -5300,7 +5305,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="24">
+    <row r="120" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A120" s="24" t="s">
         <v>375</v>
       </c>
@@ -5323,7 +5328,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="121" spans="1:7" s="10" customFormat="1" ht="36">
+    <row r="121" spans="1:7" s="10" customFormat="1" ht="43" x14ac:dyDescent="0.2">
       <c r="A121" s="17" t="s">
         <v>375</v>
       </c>
@@ -5346,7 +5351,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="122" spans="1:7" s="10" customFormat="1" ht="36">
+    <row r="122" spans="1:7" s="10" customFormat="1" ht="43" x14ac:dyDescent="0.2">
       <c r="A122" s="17" t="s">
         <v>375</v>
       </c>
@@ -5369,7 +5374,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="123" spans="1:7" ht="24">
+    <row r="123" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A123" s="24" t="s">
         <v>375</v>
       </c>
@@ -5392,7 +5397,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="124" spans="1:7" ht="24">
+    <row r="124" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A124" s="24" t="s">
         <v>375</v>
       </c>
@@ -5415,7 +5420,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="125" spans="1:7" ht="24">
+    <row r="125" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A125" s="24" t="s">
         <v>375</v>
       </c>
@@ -5438,7 +5443,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="126" spans="1:7" ht="24">
+    <row r="126" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A126" s="24" t="s">
         <v>375</v>
       </c>
@@ -5461,7 +5466,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="127" spans="1:7" ht="24">
+    <row r="127" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A127" s="24" t="s">
         <v>375</v>
       </c>
@@ -5484,7 +5489,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="128" spans="1:7" ht="24">
+    <row r="128" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A128" s="24" t="s">
         <v>375</v>
       </c>
@@ -5507,7 +5512,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="24">
+    <row r="129" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A129" s="24" t="s">
         <v>375</v>
       </c>
@@ -5530,7 +5535,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="24">
+    <row r="130" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A130" s="24" t="s">
         <v>375</v>
       </c>
@@ -5553,7 +5558,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="24">
+    <row r="131" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A131" s="24" t="s">
         <v>428</v>
       </c>
@@ -5576,7 +5581,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="24" t="s">
         <v>428</v>
       </c>
@@ -5599,7 +5604,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="24" t="s">
         <v>428</v>
       </c>
@@ -5622,7 +5627,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="134" spans="1:7" ht="48">
+    <row r="134" spans="1:7" ht="56" x14ac:dyDescent="0.2">
       <c r="A134" s="24" t="s">
         <v>428</v>
       </c>
@@ -5645,7 +5650,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="135" spans="1:7" ht="24">
+    <row r="135" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A135" s="24" t="s">
         <v>428</v>
       </c>
@@ -5668,7 +5673,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="136" spans="1:7" ht="24">
+    <row r="136" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A136" s="24" t="s">
         <v>428</v>
       </c>
@@ -5691,7 +5696,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="137" spans="1:7" ht="61.5" customHeight="1">
+    <row r="137" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="24" t="s">
         <v>447</v>
       </c>
@@ -5714,7 +5719,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="138" spans="1:7" ht="36">
+    <row r="138" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A138" s="24" t="s">
         <v>447</v>
       </c>
@@ -5737,7 +5742,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="139" spans="1:7" ht="24">
+    <row r="139" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A139" s="24" t="s">
         <v>447</v>
       </c>
@@ -5760,7 +5765,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="140" spans="1:7" ht="24">
+    <row r="140" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A140" s="24" t="s">
         <v>447</v>
       </c>
@@ -5783,7 +5788,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="141" spans="1:7" ht="24">
+    <row r="141" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A141" s="24" t="s">
         <v>447</v>
       </c>
@@ -5806,7 +5811,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="142" spans="1:7" ht="24">
+    <row r="142" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A142" s="24" t="s">
         <v>447</v>
       </c>
@@ -5829,7 +5834,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="143" spans="1:7" ht="24">
+    <row r="143" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A143" s="24" t="s">
         <v>447</v>
       </c>
@@ -5852,7 +5857,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="144" spans="1:7" ht="24">
+    <row r="144" spans="1:7" ht="28" x14ac:dyDescent="0.2">
       <c r="A144" s="24" t="s">
         <v>447</v>
       </c>
@@ -5875,7 +5880,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="24">
+    <row r="145" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A145" s="24" t="s">
         <v>447</v>
       </c>
@@ -5898,7 +5903,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="24">
+    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A146" s="24" t="s">
         <v>447</v>
       </c>
@@ -5921,7 +5926,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="24">
+    <row r="147" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A147" s="24" t="s">
         <v>447</v>
       </c>
@@ -5944,7 +5949,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="24">
+    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A148" s="24" t="s">
         <v>447</v>
       </c>
@@ -5967,7 +5972,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="24">
+    <row r="149" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A149" s="24" t="s">
         <v>447</v>
       </c>
@@ -5990,7 +5995,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="24">
+    <row r="150" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A150" s="24" t="s">
         <v>447</v>
       </c>
@@ -6013,7 +6018,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="24">
+    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.2">
       <c r="A151" s="24" t="s">
         <v>447</v>
       </c>
@@ -6036,7 +6041,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="152" spans="1:12">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="24" t="s">
         <v>447</v>
       </c>
@@ -6059,7 +6064,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="39" customHeight="1">
+    <row r="153" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="24" t="s">
         <v>483</v>
       </c>
@@ -6082,7 +6087,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="154" spans="1:12" s="12" customFormat="1" ht="24">
+    <row r="154" spans="1:12" s="12" customFormat="1" ht="28" x14ac:dyDescent="0.15">
       <c r="A154" s="63" t="s">
         <v>131</v>
       </c>
@@ -6105,7 +6110,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="155" spans="1:12">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="64" t="s">
         <v>483</v>
       </c>
@@ -6128,7 +6133,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="30.75">
+    <row r="156" spans="1:12" ht="280" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
         <v>483</v>
       </c>
@@ -6164,7 +6169,7 @@
       </c>
       <c r="L156" s="46"/>
     </row>
-    <row r="157" spans="1:12" ht="30.75">
+    <row r="157" spans="1:12" ht="280" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
         <v>483</v>
       </c>
@@ -6200,7 +6205,7 @@
       </c>
       <c r="L157" s="49"/>
     </row>
-    <row r="158" spans="1:12" ht="30.75">
+    <row r="158" spans="1:12" ht="280" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
         <v>483</v>
       </c>
@@ -6236,7 +6241,7 @@
       </c>
       <c r="L158" s="49"/>
     </row>
-    <row r="159" spans="1:12" ht="30.75">
+    <row r="159" spans="1:12" ht="280" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
         <v>483</v>
       </c>
@@ -6272,7 +6277,7 @@
       </c>
       <c r="L159" s="50"/>
     </row>
-    <row r="160" spans="1:12" ht="29.25">
+    <row r="160" spans="1:12" ht="280" x14ac:dyDescent="0.2">
       <c r="A160" s="69" t="s">
         <v>483</v>
       </c>
@@ -6308,7 +6313,7 @@
       </c>
       <c r="L160" s="53"/>
     </row>
-    <row r="161" spans="1:12" ht="29.25">
+    <row r="161" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A161" s="69" t="s">
         <v>483</v>
       </c>
@@ -6344,7 +6349,7 @@
       </c>
       <c r="L161" s="53"/>
     </row>
-    <row r="162" spans="1:12">
+    <row r="162" spans="1:12" ht="288" x14ac:dyDescent="0.2">
       <c r="A162" s="69" t="s">
         <v>483</v>
       </c>
@@ -6380,7 +6385,7 @@
       </c>
       <c r="L162" s="58"/>
     </row>
-    <row r="163" spans="1:12" ht="29.25">
+    <row r="163" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A163" s="69" t="s">
         <v>483</v>
       </c>
@@ -6416,7 +6421,7 @@
       </c>
       <c r="L163" s="58"/>
     </row>
-    <row r="164" spans="1:12" ht="24">
+    <row r="164" spans="1:12" ht="320" x14ac:dyDescent="0.2">
       <c r="A164" s="69" t="s">
         <v>483</v>
       </c>
@@ -6452,276 +6457,276 @@
       </c>
       <c r="L164" s="58"/>
     </row>
-    <row r="165" spans="1:12">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165" s="8"/>
       <c r="B165" s="8"/>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
       <c r="E165" s="8"/>
     </row>
-    <row r="166" spans="1:12">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166" s="8"/>
       <c r="B166" s="8"/>
       <c r="C166" s="8"/>
       <c r="D166" s="8"/>
       <c r="E166" s="8"/>
     </row>
-    <row r="167" spans="1:12">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167" s="8"/>
       <c r="B167" s="8"/>
       <c r="C167" s="8"/>
       <c r="D167" s="8"/>
       <c r="E167" s="8"/>
     </row>
-    <row r="168" spans="1:12">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168" s="8"/>
       <c r="B168" s="8"/>
       <c r="C168" s="8"/>
       <c r="D168" s="8"/>
       <c r="E168" s="8"/>
     </row>
-    <row r="169" spans="1:12">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169" s="8"/>
       <c r="B169" s="8"/>
       <c r="C169" s="8"/>
       <c r="D169" s="8"/>
       <c r="E169" s="8"/>
     </row>
-    <row r="170" spans="1:12">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170" s="8"/>
       <c r="B170" s="8"/>
       <c r="C170" s="8"/>
       <c r="D170" s="8"/>
       <c r="E170" s="8"/>
     </row>
-    <row r="171" spans="1:12">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171" s="8"/>
       <c r="B171" s="8"/>
       <c r="C171" s="8"/>
       <c r="D171" s="8"/>
       <c r="E171" s="8"/>
     </row>
-    <row r="172" spans="1:12">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172" s="8"/>
       <c r="B172" s="8"/>
       <c r="C172" s="8"/>
       <c r="D172" s="8"/>
       <c r="E172" s="8"/>
     </row>
-    <row r="173" spans="1:12">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173" s="8"/>
       <c r="B173" s="8"/>
       <c r="C173" s="8"/>
       <c r="D173" s="8"/>
       <c r="E173" s="8"/>
     </row>
-    <row r="174" spans="1:12">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174" s="8"/>
       <c r="B174" s="8"/>
       <c r="C174" s="8"/>
       <c r="D174" s="8"/>
       <c r="E174" s="8"/>
     </row>
-    <row r="175" spans="1:12">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175" s="8"/>
       <c r="B175" s="8"/>
       <c r="C175" s="8"/>
       <c r="D175" s="8"/>
       <c r="E175" s="8"/>
     </row>
-    <row r="176" spans="1:12">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176" s="8"/>
       <c r="B176" s="8"/>
       <c r="C176" s="8"/>
       <c r="D176" s="8"/>
       <c r="E176" s="8"/>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A177" s="8"/>
       <c r="B177" s="8"/>
       <c r="C177" s="8"/>
       <c r="D177" s="8"/>
       <c r="E177" s="8"/>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A178" s="8"/>
       <c r="B178" s="8"/>
       <c r="C178" s="8"/>
       <c r="D178" s="8"/>
       <c r="E178" s="8"/>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A179" s="8"/>
       <c r="B179" s="8"/>
       <c r="C179" s="8"/>
       <c r="D179" s="8"/>
       <c r="E179" s="8"/>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A180" s="8"/>
       <c r="B180" s="8"/>
       <c r="C180" s="8"/>
       <c r="D180" s="8"/>
       <c r="E180" s="8"/>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A181" s="8"/>
       <c r="B181" s="8"/>
       <c r="C181" s="8"/>
       <c r="D181" s="8"/>
       <c r="E181" s="8"/>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A182" s="8"/>
       <c r="B182" s="8"/>
       <c r="C182" s="8"/>
       <c r="D182" s="8"/>
       <c r="E182" s="8"/>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A183" s="8"/>
       <c r="B183" s="8"/>
       <c r="C183" s="8"/>
       <c r="D183" s="8"/>
       <c r="E183" s="8"/>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A184" s="8"/>
       <c r="B184" s="8"/>
       <c r="C184" s="8"/>
       <c r="D184" s="8"/>
       <c r="E184" s="8"/>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A185" s="8"/>
       <c r="B185" s="8"/>
       <c r="C185" s="8"/>
       <c r="D185" s="8"/>
       <c r="E185" s="8"/>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A186" s="8"/>
       <c r="B186" s="8"/>
       <c r="C186" s="8"/>
       <c r="D186" s="8"/>
       <c r="E186" s="8"/>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A187" s="8"/>
       <c r="B187" s="8"/>
       <c r="C187" s="8"/>
       <c r="D187" s="8"/>
       <c r="E187" s="8"/>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A188" s="8"/>
       <c r="B188" s="8"/>
       <c r="C188" s="8"/>
       <c r="D188" s="8"/>
       <c r="E188" s="8"/>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A189" s="8"/>
       <c r="B189" s="8"/>
       <c r="C189" s="8"/>
       <c r="D189" s="8"/>
       <c r="E189" s="8"/>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A190" s="8"/>
       <c r="B190" s="8"/>
       <c r="C190" s="8"/>
       <c r="D190" s="8"/>
       <c r="E190" s="8"/>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A191" s="8"/>
       <c r="B191" s="8"/>
       <c r="C191" s="8"/>
       <c r="D191" s="8"/>
       <c r="E191" s="8"/>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A192" s="8"/>
       <c r="B192" s="8"/>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
       <c r="E192" s="8"/>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A193" s="8"/>
       <c r="B193" s="8"/>
       <c r="C193" s="8"/>
       <c r="D193" s="8"/>
       <c r="E193" s="8"/>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A194" s="8"/>
       <c r="B194" s="8"/>
       <c r="C194" s="8"/>
       <c r="D194" s="8"/>
       <c r="E194" s="8"/>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A195" s="8"/>
       <c r="B195" s="8"/>
       <c r="C195" s="8"/>
       <c r="D195" s="8"/>
       <c r="E195" s="8"/>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A196" s="8"/>
       <c r="B196" s="8"/>
       <c r="C196" s="8"/>
       <c r="D196" s="8"/>
       <c r="E196" s="8"/>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A197" s="8"/>
       <c r="B197" s="8"/>
       <c r="C197" s="8"/>
       <c r="D197" s="8"/>
       <c r="E197" s="8"/>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A198" s="8"/>
       <c r="B198" s="8"/>
       <c r="C198" s="8"/>
       <c r="D198" s="8"/>
       <c r="E198" s="8"/>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A199" s="8"/>
       <c r="B199" s="8"/>
       <c r="C199" s="8"/>
       <c r="D199" s="8"/>
       <c r="E199" s="8"/>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A200" s="8"/>
       <c r="B200" s="8"/>
       <c r="C200" s="8"/>
       <c r="D200" s="8"/>
       <c r="E200" s="8"/>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A201" s="8"/>
       <c r="B201" s="8"/>
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
       <c r="E201" s="8"/>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A202" s="8"/>
       <c r="B202" s="8"/>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
       <c r="E202" s="8"/>
     </row>
-    <row r="269" spans="5:5">
+    <row r="269" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E269" s="13"/>
     </row>
-    <row r="271" spans="5:5">
+    <row r="271" spans="5:5" x14ac:dyDescent="0.2">
       <c r="E271" s="14"/>
     </row>
   </sheetData>
@@ -6908,39 +6913,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD006C89-1AA2-4301-A3E8-1AF42E12C555}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.7109375" customWidth="1"/>
-    <col min="2" max="2" width="8.42578125" style="40" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.6640625" customWidth="1"/>
+    <col min="2" max="2" width="8.5" style="40" customWidth="1"/>
+    <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.5703125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.5" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.1640625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30.75">
+    <row r="1" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="42" t="s">
         <v>525</v>
       </c>
@@ -6948,7 +6953,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
@@ -6956,7 +6961,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>340</v>
       </c>
@@ -6964,7 +6969,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>335</v>
       </c>
@@ -6972,7 +6977,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>483</v>
       </c>
@@ -6981,7 +6986,7 @@
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>101</v>
       </c>
@@ -6990,7 +6995,7 @@
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>7</v>
       </c>
@@ -6999,7 +7004,7 @@
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>353</v>
       </c>
@@ -7008,7 +7013,7 @@
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>375</v>
       </c>
@@ -7017,7 +7022,7 @@
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>527</v>
       </c>
@@ -7026,7 +7031,7 @@
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>131</v>
       </c>
@@ -7035,7 +7040,7 @@
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>428</v>
       </c>
@@ -7044,7 +7049,7 @@
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>528</v>
       </c>
@@ -7053,7 +7058,7 @@
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>447</v>
       </c>
@@ -7062,7 +7067,7 @@
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>213</v>
       </c>
@@ -7071,7 +7076,7 @@
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>529</v>
       </c>
@@ -7080,7 +7085,7 @@
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>530</v>
       </c>
@@ -7115,13 +7120,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F3854A-26D2-4B73-8883-41115D3B5C7C}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="30.42578125" customWidth="1"/>
+    <col min="1" max="1" width="30.5" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30.75">
+    <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>531</v>
       </c>
@@ -7129,7 +7134,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
         <v>47</v>
       </c>
@@ -7137,7 +7142,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
         <v>10</v>
       </c>
@@ -7145,7 +7150,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>110</v>
       </c>
@@ -7153,7 +7158,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>133</v>
       </c>
@@ -7161,7 +7166,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>19</v>
       </c>
@@ -7169,7 +7174,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>61</v>
       </c>
@@ -7177,7 +7182,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>167</v>
       </c>
@@ -7185,7 +7190,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>275</v>
       </c>
@@ -7193,7 +7198,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
         <v>142</v>
       </c>
@@ -7201,7 +7206,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>337</v>
       </c>
@@ -7209,7 +7214,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>103</v>
       </c>
@@ -7217,7 +7222,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>35</v>
       </c>
@@ -7225,7 +7230,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>51</v>
       </c>
@@ -7233,7 +7238,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
@@ -7241,7 +7246,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>15</v>
       </c>
@@ -7249,7 +7254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>28</v>
       </c>
@@ -7257,7 +7262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>530</v>
       </c>
@@ -7292,13 +7297,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20EE7BF-088B-4DBC-8B00-B4629CB74C85}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" style="40" customWidth="1"/>
-    <col min="2" max="2" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" style="40" customWidth="1"/>
+    <col min="2" max="2" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="30.75">
+    <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
         <v>532</v>
       </c>
@@ -7306,7 +7311,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="30.75">
+    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="40" t="s">
         <v>75</v>
       </c>
@@ -7314,7 +7319,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="30.75">
+    <row r="3" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="40" t="s">
         <v>68</v>
       </c>
@@ -7322,7 +7327,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
         <v>193</v>
       </c>
@@ -7330,7 +7335,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30.75">
+    <row r="5" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="40" t="s">
         <v>27</v>
       </c>
@@ -7338,7 +7343,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="30.75">
+    <row r="6" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="40" t="s">
         <v>9</v>
       </c>
@@ -7346,7 +7351,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="30.75">
+    <row r="7" spans="1:2" ht="32" x14ac:dyDescent="0.2">
       <c r="A7" s="40" t="s">
         <v>94</v>
       </c>
@@ -7354,7 +7359,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="40" t="s">
         <v>137</v>
       </c>
@@ -7362,7 +7367,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="40" t="s">
         <v>121</v>
       </c>
@@ -7370,7 +7375,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="41" t="s">
         <v>530</v>
       </c>
@@ -7385,6 +7390,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddf82700-9bfb-4fea-878c-7eefdbc7745a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A70658DA2082244F88130573F11D6B61" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="858aee249293fa9096085e62b28b992c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ddf82700-9bfb-4fea-878c-7eefdbc7745a" xmlns:ns3="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bb51cc068e630e42264d9068ea4c7f6" ns2:_="" ns3:_="">
     <xsd:import namespace="ddf82700-9bfb-4fea-878c-7eefdbc7745a"/>
@@ -7585,17 +7601,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddf82700-9bfb-4fea-878c-7eefdbc7745a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7606,13 +7611,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63105CD5-8CA5-4DAD-B85E-7A49F4224C26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11F60C-BEA5-4032-9DEF-D983207E1747}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="e1fe8cf4-797e-455f-bdfc-84f59ecaf273"/>
+    <ds:schemaRef ds:uri="ddf82700-9bfb-4fea-878c-7eefdbc7745a"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11F60C-BEA5-4032-9DEF-D983207E1747}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63105CD5-8CA5-4DAD-B85E-7A49F4224C26}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="ddf82700-9bfb-4fea-878c-7eefdbc7745a"/>
+    <ds:schemaRef ds:uri="e1fe8cf4-797e-455f-bdfc-84f59ecaf273"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1BDF07-269F-4A8A-929B-119FFB2E0C7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1BDF07-269F-4A8A-929B-119FFB2E0C7C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/data/oer-catalog-2024-2025.xlsx
+++ b/data/oer-catalog-2024-2025.xlsx
@@ -1,16 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elliotgalvis/Downloads/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72EF4B2B-B60A-3C49-8D0D-3A2CB405A5A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFB370E8-1C42-48A8-AC71-8C5258FE4D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="780" windowWidth="30200" windowHeight="20640" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="6" r:id="rId1"/>
@@ -87,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="533">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1281" uniqueCount="553">
   <si>
     <t>Campus </t>
   </si>
@@ -1729,6 +1724,66 @@
     <t>https://academicworks.cuny.edu/bc_oers/27</t>
   </si>
   <si>
+    <t>English 1012: English Composition II: Seminar in Expository Writing</t>
+  </si>
+  <si>
+    <t>Sophia Bamert</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/38/</t>
+  </si>
+  <si>
+    <t>CASD 2482 Introduction to Rehabilitative Audiology</t>
+  </si>
+  <si>
+    <t>Rosette Reisman</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/39/</t>
+  </si>
+  <si>
+    <t>Intro to Puerto Rican and Latinx Studies</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/40/</t>
+  </si>
+  <si>
+    <t>POLS 3014W Research Strategies in Public Policy</t>
+  </si>
+  <si>
+    <t>Sevdenur Koru</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/41/</t>
+  </si>
+  <si>
+    <t>PRLS 3316: Banned Books: Teaching Latinx Children and Youth Literature</t>
+  </si>
+  <si>
+    <t>Carla España</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/42/</t>
+  </si>
+  <si>
+    <t>HNSC 3314 Human Encounters with Death and Bereavement</t>
+  </si>
+  <si>
+    <t>Tracy Wong</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/43/</t>
+  </si>
+  <si>
+    <t>CISC 3130 Data Structures</t>
+  </si>
+  <si>
+    <t>Moshe Lach</t>
+  </si>
+  <si>
+    <t>https://academicworks.cuny.edu/bc_oers/36/</t>
+  </si>
+  <si>
     <t>CUNY Campus</t>
   </si>
   <si>
@@ -1757,7 +1812,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1835,19 +1890,37 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0F374F"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1901,53 +1974,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1969,21 +2001,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -1993,51 +2010,18 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
       <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </right>
       <top style="thin">
-        <color rgb="FF000000"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.14999847407452621"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -2045,170 +2029,137 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2243,9 +2194,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2283,7 +2234,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2389,7 +2340,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2531,7 +2482,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -2556,4178 +2507,4784 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2C78B0D9-715E-4EDD-989F-8CB33D4C8A77}">
-  <dimension ref="A1:L271"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="0" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L202"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="7" customWidth="1"/>
-    <col min="2" max="2" width="33.6640625" style="7" customWidth="1"/>
-    <col min="3" max="3" width="21.5" style="7" customWidth="1"/>
-    <col min="4" max="4" width="19.5" style="2" customWidth="1"/>
-    <col min="5" max="5" width="24.83203125" style="7" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" style="8" customWidth="1"/>
-    <col min="7" max="7" width="29.6640625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" style="55" customWidth="1"/>
+    <col min="2" max="2" width="33.7109375" style="55" customWidth="1"/>
+    <col min="3" max="3" width="21.42578125" style="55" customWidth="1"/>
+    <col min="4" max="4" width="19.5703125" style="56" customWidth="1"/>
+    <col min="5" max="6" width="24.85546875" style="55" customWidth="1"/>
+    <col min="7" max="7" width="29.7109375" style="55" customWidth="1"/>
+    <col min="8" max="16384" width="0" style="24" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="6" customFormat="1" ht="46.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:11" s="13" customFormat="1" ht="46.5" customHeight="1">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="15" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="16" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A2" s="17" t="s">
+      <c r="H1" s="12"/>
+      <c r="I1" s="12"/>
+      <c r="J1" s="12"/>
+      <c r="K1" s="12"/>
+    </row>
+    <row r="2" spans="1:11" s="18" customFormat="1" ht="24">
+      <c r="A2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="D2" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="36" t="s">
+      <c r="F2" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="16" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="17" t="s">
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+    </row>
+    <row r="3" spans="1:11" s="18" customFormat="1">
+      <c r="A3" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="17" t="s">
+      <c r="E3" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3" s="36" t="s">
+      <c r="F3" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="16" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A4" s="17" t="s">
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+    </row>
+    <row r="4" spans="1:11" s="18" customFormat="1" ht="24">
+      <c r="A4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="E4" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G4" s="36" t="s">
+      <c r="F4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="16" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" s="11" customFormat="1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A5" s="17" t="s">
+      <c r="H4" s="17"/>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+    </row>
+    <row r="5" spans="1:11" s="21" customFormat="1" ht="24">
+      <c r="A5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="17" t="s">
+      <c r="C5" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="18" t="s">
+      <c r="D5" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G5" s="36" t="s">
+      <c r="F5" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="16" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A6" s="17" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" spans="1:11" ht="24">
+      <c r="A6" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G6" s="36" t="s">
+      <c r="F6" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="16" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A7" s="17" t="s">
+      <c r="H6" s="23"/>
+      <c r="I6" s="23"/>
+      <c r="J6" s="23"/>
+      <c r="K6" s="23"/>
+    </row>
+    <row r="7" spans="1:11" ht="24">
+      <c r="A7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="18" t="s">
+      <c r="D7" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="17" t="s">
+      <c r="E7" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="36" t="s">
+      <c r="F7" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="234" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="17" t="s">
+      <c r="H7" s="23"/>
+      <c r="I7" s="23"/>
+      <c r="J7" s="23"/>
+      <c r="K7" s="23"/>
+    </row>
+    <row r="8" spans="1:11" ht="234" customHeight="1">
+      <c r="A8" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D8" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="17" t="s">
+      <c r="E8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G8" s="36" t="s">
+      <c r="F8" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="16" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="21" t="s">
+      <c r="H8" s="23"/>
+      <c r="I8" s="23"/>
+      <c r="J8" s="23"/>
+      <c r="K8" s="23"/>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="25" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9" s="23" t="s">
+      <c r="F9" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="27" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+      <c r="J9" s="23"/>
+      <c r="K9" s="23"/>
+    </row>
+    <row r="10" spans="1:11" ht="24">
+      <c r="A10" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="E10" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10" s="76" t="s">
+      <c r="F10" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10" s="28" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="29" x14ac:dyDescent="0.2">
-      <c r="A11" s="24" t="s">
+      <c r="H10" s="23"/>
+      <c r="I10" s="23"/>
+      <c r="J10" s="23"/>
+      <c r="K10" s="23"/>
+    </row>
+    <row r="11" spans="1:11" ht="24">
+      <c r="A11" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="24" t="s">
+      <c r="C11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11" s="26" t="s">
+      <c r="F11" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11" s="30" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="29" x14ac:dyDescent="0.2">
-      <c r="A12" s="24" t="s">
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+    </row>
+    <row r="12" spans="1:11" ht="24">
+      <c r="A12" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="24" t="s">
+      <c r="B12" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="C12" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="25" t="s">
+      <c r="E12" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G12" s="26" t="s">
+      <c r="F12" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12" s="30" t="s">
         <v>53</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A13" s="24" t="s">
+      <c r="H12" s="23"/>
+      <c r="I12" s="23"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+    </row>
+    <row r="13" spans="1:11" ht="24">
+      <c r="A13" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E13" s="24" t="s">
+      <c r="E13" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="27" t="s">
+      <c r="F13" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G13" s="31" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+      <c r="H13" s="23"/>
+      <c r="I13" s="23"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+    </row>
+    <row r="14" spans="1:11" ht="36">
+      <c r="A14" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B14" s="24" t="s">
+      <c r="B14" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C14" s="24" t="s">
+      <c r="C14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="F14" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G14" s="27" t="s">
+      <c r="F14" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G14" s="31" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A15" s="24" t="s">
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="23"/>
+    </row>
+    <row r="15" spans="1:11" ht="24">
+      <c r="A15" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B15" s="24" t="s">
+      <c r="B15" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C15" s="24" t="s">
+      <c r="C15" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E15" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="28" t="s">
+      <c r="F15" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G15" s="32" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A16" s="24" t="s">
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+    </row>
+    <row r="16" spans="1:11" ht="24">
+      <c r="A16" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B16" s="24" t="s">
+      <c r="B16" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="C16" s="24" t="s">
+      <c r="C16" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E16" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G16" s="27" t="s">
+      <c r="F16" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G16" s="31" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A17" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="23"/>
+      <c r="J16" s="23"/>
+      <c r="K16" s="23"/>
+    </row>
+    <row r="17" spans="1:11" ht="24">
+      <c r="A17" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="24" t="s">
+      <c r="B17" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="C17" s="24" t="s">
+      <c r="C17" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E17" s="24" t="s">
+      <c r="E17" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17" s="27" t="s">
+      <c r="F17" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G17" s="31" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="H17" s="23"/>
+      <c r="I17" s="23"/>
+      <c r="J17" s="23"/>
+      <c r="K17" s="23"/>
+    </row>
+    <row r="18" spans="1:11" ht="24">
+      <c r="A18" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="B18" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="C18" s="24" t="s">
+      <c r="C18" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D18" s="18" t="s">
+      <c r="D18" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="24" t="s">
+      <c r="E18" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18" s="27" t="s">
+      <c r="F18" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18" s="31" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A19" s="24" t="s">
+      <c r="H18" s="23"/>
+      <c r="I18" s="23"/>
+      <c r="J18" s="23"/>
+      <c r="K18" s="23"/>
+    </row>
+    <row r="19" spans="1:11" ht="24">
+      <c r="A19" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="24" t="s">
+      <c r="B19" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E19" s="24" t="s">
+      <c r="E19" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19" s="27" t="s">
+      <c r="F19" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19" s="31" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A20" s="24" t="s">
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+    </row>
+    <row r="20" spans="1:11" ht="24">
+      <c r="A20" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="24" t="s">
+      <c r="B20" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="C20" s="24" t="s">
+      <c r="C20" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F20" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20" s="27" t="s">
+      <c r="F20" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20" s="31" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A21" s="24" t="s">
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+      <c r="K20" s="23"/>
+    </row>
+    <row r="21" spans="1:11" ht="24">
+      <c r="A21" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="18" t="s">
+      <c r="D21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E21" s="24" t="s">
+      <c r="E21" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="F21" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21" s="27" t="s">
+      <c r="F21" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21" s="31" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
+      <c r="J21" s="23"/>
+      <c r="K21" s="23"/>
+    </row>
+    <row r="22" spans="1:11" ht="24">
+      <c r="A22" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="24" t="s">
+      <c r="B22" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="D22" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E22" s="24" t="s">
+      <c r="E22" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F22" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G22" s="27" t="s">
+      <c r="F22" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22" s="31" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A23" s="24" t="s">
+      <c r="H22" s="23"/>
+      <c r="I22" s="23"/>
+      <c r="J22" s="23"/>
+      <c r="K22" s="23"/>
+    </row>
+    <row r="23" spans="1:11" ht="36">
+      <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="18" t="s">
+      <c r="D23" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="24" t="s">
+      <c r="E23" s="19" t="s">
         <v>88</v>
       </c>
-      <c r="F23" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G23" s="27" t="s">
+      <c r="F23" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="31" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A24" s="24" t="s">
+      <c r="H23" s="23"/>
+      <c r="I23" s="23"/>
+      <c r="J23" s="23"/>
+      <c r="K23" s="23"/>
+    </row>
+    <row r="24" spans="1:11" ht="36">
+      <c r="A24" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="B24" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="C24" s="24" t="s">
+      <c r="C24" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="24" t="s">
+      <c r="E24" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F24" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G24" s="27" t="s">
+      <c r="F24" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G24" s="31" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A25" s="24" t="s">
+      <c r="H24" s="23"/>
+      <c r="I24" s="23"/>
+      <c r="J24" s="23"/>
+      <c r="K24" s="23"/>
+    </row>
+    <row r="25" spans="1:11" ht="24">
+      <c r="A25" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B25" s="24" t="s">
+      <c r="B25" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="C25" s="24" t="s">
+      <c r="C25" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D25" s="18" t="s">
+      <c r="D25" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="24" t="s">
+      <c r="E25" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F25" s="17" t="s">
+      <c r="F25" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G25" s="27" t="s">
+      <c r="G25" s="31" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A26" s="24" t="s">
+      <c r="H25" s="23"/>
+      <c r="I25" s="23"/>
+      <c r="J25" s="23"/>
+      <c r="K25" s="23"/>
+    </row>
+    <row r="26" spans="1:11" ht="24">
+      <c r="A26" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="B26" s="24" t="s">
+      <c r="B26" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C26" s="24" t="s">
+      <c r="C26" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D26" s="18" t="s">
+      <c r="D26" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E26" s="24" t="s">
+      <c r="E26" s="19" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G26" s="27" t="s">
+      <c r="F26" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G26" s="31" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27" s="24" t="s">
+      <c r="H26" s="23"/>
+      <c r="I26" s="23"/>
+      <c r="J26" s="23"/>
+      <c r="K26" s="23"/>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B27" s="24" t="s">
+      <c r="B27" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="C27" s="24" t="s">
+      <c r="C27" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D27" s="18" t="s">
+      <c r="D27" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E27" s="24" t="s">
+      <c r="E27" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="F27" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G27" s="27" t="s">
+      <c r="F27" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G27" s="31" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A28" s="24" t="s">
+      <c r="H27" s="23"/>
+      <c r="I27" s="23"/>
+      <c r="J27" s="23"/>
+      <c r="K27" s="23"/>
+    </row>
+    <row r="28" spans="1:11" ht="24">
+      <c r="A28" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B28" s="24" t="s">
+      <c r="B28" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="C28" s="24" t="s">
+      <c r="C28" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E28" s="24" t="s">
+      <c r="E28" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="F28" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G28" s="27" t="s">
+      <c r="F28" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G28" s="31" t="s">
         <v>108</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A29" s="24" t="s">
+      <c r="H28" s="23"/>
+      <c r="I28" s="23"/>
+      <c r="J28" s="23"/>
+      <c r="K28" s="23"/>
+    </row>
+    <row r="29" spans="1:11" ht="24">
+      <c r="A29" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="24" t="s">
+      <c r="B29" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="24" t="s">
+      <c r="C29" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D29" s="18" t="s">
+      <c r="D29" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="24" t="s">
+      <c r="E29" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G29" s="27" t="s">
+      <c r="F29" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G29" s="31" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="24" t="s">
+      <c r="H29" s="23"/>
+      <c r="I29" s="23"/>
+      <c r="J29" s="23"/>
+      <c r="K29" s="23"/>
+    </row>
+    <row r="30" spans="1:11" ht="42" customHeight="1">
+      <c r="A30" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B30" s="24" t="s">
+      <c r="B30" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="C30" s="24" t="s">
+      <c r="C30" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="18" t="s">
+      <c r="D30" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E30" s="24" t="s">
+      <c r="E30" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G30" s="27" t="s">
+      <c r="F30" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G30" s="31" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A31" s="24" t="s">
+      <c r="H30" s="23"/>
+      <c r="I30" s="23"/>
+      <c r="J30" s="23"/>
+      <c r="K30" s="23"/>
+    </row>
+    <row r="31" spans="1:11" ht="24">
+      <c r="A31" s="19" t="s">
         <v>101</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C31" s="24" t="s">
+      <c r="C31" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D31" s="18" t="s">
+      <c r="D31" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="24" t="s">
+      <c r="E31" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="F31" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G31" s="27" t="s">
+      <c r="F31" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G31" s="31" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A32" s="24" t="s">
+      <c r="H31" s="23"/>
+      <c r="I31" s="23"/>
+      <c r="J31" s="23"/>
+      <c r="K31" s="23"/>
+    </row>
+    <row r="32" spans="1:11" ht="24">
+      <c r="A32" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B32" s="24" t="s">
+      <c r="B32" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="24" t="s">
+      <c r="E32" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="F32" s="17" t="s">
+      <c r="F32" s="14" t="s">
         <v>123</v>
       </c>
-      <c r="G32" s="27" t="s">
+      <c r="G32" s="31" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A33" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="23"/>
+      <c r="J32" s="23"/>
+      <c r="K32" s="23"/>
+    </row>
+    <row r="33" spans="1:11" ht="24">
+      <c r="A33" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B33" s="24" t="s">
+      <c r="B33" s="19" t="s">
         <v>125</v>
       </c>
-      <c r="C33" s="24" t="s">
+      <c r="C33" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="G33" s="30" t="s">
+      <c r="G33" s="34" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
-      <c r="A34" s="24" t="s">
+      <c r="H33" s="23"/>
+      <c r="I33" s="23"/>
+      <c r="J33" s="23"/>
+      <c r="K33" s="23"/>
+    </row>
+    <row r="34" spans="1:11" s="18" customFormat="1" ht="36">
+      <c r="A34" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="B34" s="17" t="s">
+      <c r="B34" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D34" s="18" t="s">
+      <c r="D34" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E34" s="17" t="s">
+      <c r="E34" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F34" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G34" s="19" t="s">
+      <c r="F34" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G34" s="28" t="s">
         <v>130</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A35" s="24" t="s">
+      <c r="H34" s="17"/>
+      <c r="I34" s="17"/>
+      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
+    </row>
+    <row r="35" spans="1:11" ht="24">
+      <c r="A35" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B35" s="24" t="s">
+      <c r="B35" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="18" t="s">
+      <c r="D35" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="F35" s="17" t="s">
+      <c r="F35" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G35" s="27" t="s">
+      <c r="G35" s="31" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A36" s="24" t="s">
+      <c r="H35" s="23"/>
+      <c r="I35" s="23"/>
+      <c r="J35" s="23"/>
+      <c r="K35" s="23"/>
+    </row>
+    <row r="36" spans="1:11" ht="24">
+      <c r="A36" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B36" s="24" t="s">
+      <c r="B36" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="C36" s="24" t="s">
+      <c r="C36" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="F36" s="17" t="s">
+      <c r="F36" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G36" s="27" t="s">
+      <c r="G36" s="31" t="s">
         <v>140</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A37" s="24" t="s">
+      <c r="H36" s="23"/>
+      <c r="I36" s="23"/>
+      <c r="J36" s="23"/>
+      <c r="K36" s="23"/>
+    </row>
+    <row r="37" spans="1:11" ht="24">
+      <c r="A37" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B37" s="24" t="s">
+      <c r="B37" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D37" s="18" t="s">
+      <c r="D37" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="F37" s="17" t="s">
+      <c r="F37" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G37" s="27" t="s">
+      <c r="G37" s="31" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A38" s="24" t="s">
+      <c r="H37" s="23"/>
+      <c r="I37" s="23"/>
+      <c r="J37" s="23"/>
+      <c r="K37" s="23"/>
+    </row>
+    <row r="38" spans="1:11" ht="24">
+      <c r="A38" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C38" s="24" t="s">
+      <c r="C38" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D38" s="18" t="s">
+      <c r="D38" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="24" t="s">
+      <c r="E38" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="F38" s="17" t="s">
+      <c r="F38" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G38" s="27" t="s">
+      <c r="G38" s="31" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="24" t="s">
+      <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
+      <c r="J38" s="23"/>
+      <c r="K38" s="23"/>
+    </row>
+    <row r="39" spans="1:11" ht="33" customHeight="1">
+      <c r="A39" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B39" s="24" t="s">
+      <c r="B39" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C39" s="24" t="s">
+      <c r="C39" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D39" s="18" t="s">
+      <c r="D39" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E39" s="24" t="s">
+      <c r="E39" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="F39" s="17" t="s">
+      <c r="F39" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G39" s="27" t="s">
+      <c r="G39" s="31" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="104.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
+      <c r="H39" s="23"/>
+      <c r="I39" s="23"/>
+      <c r="J39" s="23"/>
+      <c r="K39" s="23"/>
+    </row>
+    <row r="40" spans="1:11" ht="104.25" customHeight="1">
+      <c r="A40" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B40" s="24" t="s">
+      <c r="B40" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="C40" s="24" t="s">
+      <c r="C40" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="18" t="s">
+      <c r="D40" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E40" s="24" t="s">
+      <c r="E40" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="F40" s="17" t="s">
+      <c r="F40" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G40" s="26" t="s">
+      <c r="G40" s="30" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="27" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="24" t="s">
+      <c r="H40" s="23"/>
+      <c r="I40" s="23"/>
+      <c r="J40" s="23"/>
+      <c r="K40" s="23"/>
+    </row>
+    <row r="41" spans="1:11" ht="27" customHeight="1">
+      <c r="A41" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B41" s="24" t="s">
+      <c r="B41" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="C41" s="24" t="s">
+      <c r="C41" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D41" s="18" t="s">
+      <c r="D41" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="25" t="s">
+      <c r="E41" s="29" t="s">
         <v>154</v>
       </c>
-      <c r="F41" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G41" s="26" t="s">
+      <c r="F41" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G41" s="30" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="24" t="s">
+      <c r="H41" s="23"/>
+      <c r="I41" s="23"/>
+      <c r="J41" s="23"/>
+      <c r="K41" s="23"/>
+    </row>
+    <row r="42" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A42" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="C42" s="24" t="s">
+      <c r="C42" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E42" s="24" t="s">
+      <c r="E42" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="F42" s="17" t="s">
+      <c r="F42" s="14" t="s">
         <v>158</v>
       </c>
-      <c r="G42" s="26" t="s">
+      <c r="G42" s="30" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="29" x14ac:dyDescent="0.2">
-      <c r="A43" s="24" t="s">
+      <c r="H42" s="23"/>
+      <c r="I42" s="23"/>
+      <c r="J42" s="23"/>
+      <c r="K42" s="23"/>
+    </row>
+    <row r="43" spans="1:11" ht="24">
+      <c r="A43" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B43" s="24" t="s">
+      <c r="B43" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C43" s="24" t="s">
+      <c r="C43" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D43" s="18" t="s">
+      <c r="D43" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E43" s="25" t="s">
+      <c r="E43" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="F43" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" s="26" t="s">
+      <c r="F43" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G43" s="30" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A44" s="24" t="s">
+      <c r="H43" s="23"/>
+      <c r="I43" s="23"/>
+      <c r="J43" s="23"/>
+      <c r="K43" s="23"/>
+    </row>
+    <row r="44" spans="1:11" ht="24">
+      <c r="A44" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B44" s="24" t="s">
+      <c r="B44" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="C44" s="24" t="s">
+      <c r="C44" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D44" s="18" t="s">
+      <c r="D44" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E44" s="25" t="s">
+      <c r="E44" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="F44" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G44" s="27" t="s">
+      <c r="F44" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G44" s="31" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="24" t="s">
+      <c r="H44" s="23"/>
+      <c r="I44" s="23"/>
+      <c r="J44" s="23"/>
+      <c r="K44" s="23"/>
+    </row>
+    <row r="45" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A45" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B45" s="24" t="s">
+      <c r="B45" s="19" t="s">
         <v>166</v>
       </c>
-      <c r="C45" s="24" t="s">
+      <c r="C45" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D45" s="18" t="s">
+      <c r="D45" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E45" s="25" t="s">
+      <c r="E45" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="F45" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G45" s="27" t="s">
+      <c r="F45" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G45" s="31" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="24" t="s">
+      <c r="H45" s="23"/>
+      <c r="I45" s="23"/>
+      <c r="J45" s="23"/>
+      <c r="K45" s="23"/>
+    </row>
+    <row r="46" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A46" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="19" t="s">
         <v>170</v>
       </c>
-      <c r="C46" s="24" t="s">
+      <c r="C46" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E46" s="25" t="s">
+      <c r="E46" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F46" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G46" s="27" t="s">
+      <c r="F46" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G46" s="31" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A47" s="24" t="s">
+      <c r="H46" s="23"/>
+      <c r="I46" s="23"/>
+      <c r="J46" s="23"/>
+      <c r="K46" s="23"/>
+    </row>
+    <row r="47" spans="1:11">
+      <c r="A47" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="B47" s="17" t="s">
+      <c r="B47" s="14" t="s">
         <v>173</v>
       </c>
-      <c r="C47" s="24" t="s">
+      <c r="C47" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D47" s="18" t="s">
+      <c r="D47" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="25" t="s">
+      <c r="E47" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="F47" s="17" t="s">
+      <c r="F47" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G47" s="27" t="s">
+      <c r="G47" s="31" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A48" s="24" t="s">
+      <c r="H47" s="23"/>
+      <c r="I47" s="23"/>
+      <c r="J47" s="23"/>
+      <c r="K47" s="23"/>
+    </row>
+    <row r="48" spans="1:11" ht="24">
+      <c r="A48" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B48" s="24" t="s">
+      <c r="B48" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="C48" s="24" t="s">
+      <c r="C48" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D48" s="18" t="s">
+      <c r="D48" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E48" s="24" t="s">
+      <c r="E48" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="F48" s="17" t="s">
+      <c r="F48" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="G48" s="27" t="s">
+      <c r="G48" s="31" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A49" s="24" t="s">
+      <c r="H48" s="23"/>
+      <c r="I48" s="23"/>
+      <c r="J48" s="23"/>
+      <c r="K48" s="23"/>
+    </row>
+    <row r="49" spans="1:11" ht="24">
+      <c r="A49" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B49" s="24" t="s">
+      <c r="B49" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="C49" s="24" t="s">
+      <c r="C49" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="18" t="s">
+      <c r="D49" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="24" t="s">
+      <c r="E49" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="F49" s="17" t="s">
+      <c r="F49" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G49" s="27" t="s">
+      <c r="G49" s="31" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
-      <c r="A50" s="17" t="s">
+      <c r="H49" s="23"/>
+      <c r="I49" s="23"/>
+      <c r="J49" s="23"/>
+      <c r="K49" s="23"/>
+    </row>
+    <row r="50" spans="1:11" s="18" customFormat="1" ht="36">
+      <c r="A50" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="39" t="s">
+      <c r="B50" s="35" t="s">
         <v>183</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="22" t="s">
         <v>184</v>
       </c>
-      <c r="F50" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G50" s="31" t="s">
+      <c r="F50" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G50" s="36" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A51" s="24" t="s">
+      <c r="H50" s="17"/>
+      <c r="I50" s="17"/>
+      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
+    </row>
+    <row r="51" spans="1:11" ht="24">
+      <c r="A51" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B51" s="24" t="s">
+      <c r="B51" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="C51" s="25" t="s">
+      <c r="C51" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="D51" s="18" t="s">
+      <c r="D51" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E51" s="25" t="s">
+      <c r="E51" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="F51" s="17" t="s">
+      <c r="F51" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G51" s="27" t="s">
+      <c r="G51" s="31" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A52" s="24" t="s">
+      <c r="H51" s="23"/>
+      <c r="I51" s="23"/>
+      <c r="J51" s="23"/>
+      <c r="K51" s="23"/>
+    </row>
+    <row r="52" spans="1:11" ht="24">
+      <c r="A52" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B52" s="24" t="s">
+      <c r="B52" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="C52" s="24" t="s">
+      <c r="C52" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D52" s="18" t="s">
+      <c r="D52" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E52" s="24" t="s">
+      <c r="E52" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="F52" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G52" s="27" t="s">
+      <c r="F52" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G52" s="31" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" s="9" customFormat="1" ht="42" x14ac:dyDescent="0.2">
-      <c r="A53" s="17" t="s">
+      <c r="H52" s="23"/>
+      <c r="I52" s="23"/>
+      <c r="J52" s="23"/>
+      <c r="K52" s="23"/>
+    </row>
+    <row r="53" spans="1:11" s="18" customFormat="1" ht="36">
+      <c r="A53" s="14" t="s">
         <v>175</v>
       </c>
-      <c r="B53" s="17" t="s">
+      <c r="B53" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="C53" s="17" t="s">
+      <c r="C53" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="D53" s="18" t="s">
+      <c r="D53" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="E53" s="17" t="s">
+      <c r="E53" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="F53" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G53" s="38" t="s">
+      <c r="F53" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G53" s="37" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="24" t="s">
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
+    </row>
+    <row r="54" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A54" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B54" s="24" t="s">
+      <c r="B54" s="19" t="s">
         <v>196</v>
       </c>
-      <c r="C54" s="24" t="s">
+      <c r="C54" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D54" s="18" t="s">
+      <c r="D54" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E54" s="24" t="s">
+      <c r="E54" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="F54" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G54" s="27" t="s">
+      <c r="F54" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G54" s="31" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A55" s="24" t="s">
+      <c r="H54" s="23"/>
+      <c r="I54" s="23"/>
+      <c r="J54" s="23"/>
+      <c r="K54" s="23"/>
+    </row>
+    <row r="55" spans="1:11" ht="24">
+      <c r="A55" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B55" s="24" t="s">
+      <c r="B55" s="19" t="s">
         <v>199</v>
       </c>
-      <c r="C55" s="24" t="s">
+      <c r="C55" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D55" s="18" t="s">
+      <c r="D55" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E55" s="24" t="s">
+      <c r="E55" s="19" t="s">
         <v>200</v>
       </c>
-      <c r="F55" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G55" s="27" t="s">
+      <c r="F55" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G55" s="31" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A56" s="24" t="s">
+      <c r="H55" s="23"/>
+      <c r="I55" s="23"/>
+      <c r="J55" s="23"/>
+      <c r="K55" s="23"/>
+    </row>
+    <row r="56" spans="1:11" ht="36">
+      <c r="A56" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B56" s="24" t="s">
+      <c r="B56" s="19" t="s">
         <v>202</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D56" s="18" t="s">
+      <c r="D56" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E56" s="24" t="s">
+      <c r="E56" s="19" t="s">
         <v>203</v>
       </c>
-      <c r="F56" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G56" s="27" t="s">
+      <c r="F56" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="31" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="24" t="s">
+      <c r="H56" s="23"/>
+      <c r="I56" s="23"/>
+      <c r="J56" s="23"/>
+      <c r="K56" s="23"/>
+    </row>
+    <row r="57" spans="1:11" ht="53.25" customHeight="1">
+      <c r="A57" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B57" s="24" t="s">
+      <c r="B57" s="19" t="s">
         <v>205</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D57" s="18" t="s">
+      <c r="D57" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E57" s="24" t="s">
+      <c r="E57" s="19" t="s">
         <v>206</v>
       </c>
-      <c r="F57" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G57" s="27" t="s">
+      <c r="F57" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57" s="31" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="84" x14ac:dyDescent="0.2">
-      <c r="A58" s="24" t="s">
+      <c r="H57" s="23"/>
+      <c r="I57" s="23"/>
+      <c r="J57" s="23"/>
+      <c r="K57" s="23"/>
+    </row>
+    <row r="58" spans="1:11" ht="72">
+      <c r="A58" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B58" s="24" t="s">
+      <c r="B58" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="C58" s="24" t="s">
+      <c r="C58" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D58" s="18" t="s">
+      <c r="D58" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E58" s="24" t="s">
+      <c r="E58" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="F58" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G58" s="27" t="s">
+      <c r="G58" s="31" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="24" t="s">
+      <c r="H58" s="23"/>
+      <c r="I58" s="23"/>
+      <c r="J58" s="23"/>
+      <c r="K58" s="23"/>
+    </row>
+    <row r="59" spans="1:11" ht="31.5" customHeight="1">
+      <c r="A59" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="B59" s="24" t="s">
+      <c r="B59" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="C59" s="24" t="s">
+      <c r="C59" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E59" s="24" t="s">
+      <c r="E59" s="19" t="s">
         <v>197</v>
       </c>
-      <c r="F59" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G59" s="27" t="s">
+      <c r="F59" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G59" s="31" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A60" s="24" t="s">
+      <c r="H59" s="23"/>
+      <c r="I59" s="23"/>
+      <c r="J59" s="23"/>
+      <c r="K59" s="23"/>
+    </row>
+    <row r="60" spans="1:11" ht="24">
+      <c r="A60" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B60" s="24" t="s">
+      <c r="B60" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="C60" s="24" t="s">
+      <c r="C60" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D60" s="18" t="s">
+      <c r="D60" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E60" s="24" t="s">
+      <c r="E60" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="F60" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G60" s="27" t="s">
+      <c r="F60" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G60" s="31" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A61" s="24" t="s">
+      <c r="H60" s="23"/>
+      <c r="I60" s="23"/>
+      <c r="J60" s="23"/>
+      <c r="K60" s="23"/>
+    </row>
+    <row r="61" spans="1:11" ht="24">
+      <c r="A61" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B61" s="24" t="s">
+      <c r="B61" s="19" t="s">
         <v>217</v>
       </c>
-      <c r="C61" s="24" t="s">
+      <c r="C61" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D61" s="18" t="s">
+      <c r="D61" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E61" s="24" t="s">
+      <c r="E61" s="19" t="s">
         <v>218</v>
       </c>
-      <c r="F61" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G61" s="27" t="s">
+      <c r="F61" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G61" s="31" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A62" s="24" t="s">
+      <c r="H61" s="23"/>
+      <c r="I61" s="23"/>
+      <c r="J61" s="23"/>
+      <c r="K61" s="23"/>
+    </row>
+    <row r="62" spans="1:11" ht="24">
+      <c r="A62" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B62" s="24" t="s">
+      <c r="B62" s="19" t="s">
         <v>220</v>
       </c>
-      <c r="C62" s="24" t="s">
+      <c r="C62" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D62" s="18" t="s">
+      <c r="D62" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E62" s="24" t="s">
+      <c r="E62" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="F62" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G62" s="27" t="s">
+      <c r="F62" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G62" s="31" t="s">
         <v>222</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A63" s="24" t="s">
+      <c r="H62" s="23"/>
+      <c r="I62" s="23"/>
+      <c r="J62" s="23"/>
+      <c r="K62" s="23"/>
+    </row>
+    <row r="63" spans="1:11" ht="24">
+      <c r="A63" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B63" s="24" t="s">
+      <c r="B63" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="C63" s="24" t="s">
+      <c r="C63" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D63" s="18" t="s">
+      <c r="D63" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="E63" s="24" t="s">
+      <c r="E63" s="19" t="s">
         <v>224</v>
       </c>
-      <c r="F63" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G63" s="27" t="s">
+      <c r="F63" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G63" s="31" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A64" s="24" t="s">
+      <c r="H63" s="23"/>
+      <c r="I63" s="23"/>
+      <c r="J63" s="23"/>
+      <c r="K63" s="23"/>
+    </row>
+    <row r="64" spans="1:11" ht="24">
+      <c r="A64" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B64" s="24" t="s">
+      <c r="B64" s="19" t="s">
         <v>226</v>
       </c>
-      <c r="C64" s="24" t="s">
+      <c r="C64" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D64" s="18" t="s">
+      <c r="D64" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="E64" s="24" t="s">
+      <c r="E64" s="19" t="s">
         <v>227</v>
       </c>
-      <c r="F64" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G64" s="27" t="s">
+      <c r="F64" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G64" s="31" t="s">
         <v>228</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A65" s="24" t="s">
+      <c r="H64" s="23"/>
+      <c r="I64" s="23"/>
+      <c r="J64" s="23"/>
+      <c r="K64" s="23"/>
+    </row>
+    <row r="65" spans="1:11">
+      <c r="A65" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B65" s="24" t="s">
+      <c r="B65" s="19" t="s">
         <v>229</v>
       </c>
-      <c r="C65" s="24" t="s">
+      <c r="C65" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D65" s="18" t="s">
+      <c r="D65" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E65" s="24" t="s">
+      <c r="E65" s="19" t="s">
         <v>230</v>
       </c>
-      <c r="F65" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G65" s="27" t="s">
+      <c r="F65" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G65" s="31" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A66" s="24" t="s">
+      <c r="H65" s="23"/>
+      <c r="I65" s="23"/>
+      <c r="J65" s="23"/>
+      <c r="K65" s="23"/>
+    </row>
+    <row r="66" spans="1:11">
+      <c r="A66" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B66" s="24" t="s">
+      <c r="B66" s="19" t="s">
         <v>232</v>
       </c>
-      <c r="C66" s="24" t="s">
+      <c r="C66" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E66" s="24" t="s">
+      <c r="E66" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="F66" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G66" s="27" t="s">
+      <c r="F66" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G66" s="31" t="s">
         <v>234</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="42.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="24" t="s">
+      <c r="H66" s="23"/>
+      <c r="I66" s="23"/>
+      <c r="J66" s="23"/>
+      <c r="K66" s="23"/>
+    </row>
+    <row r="67" spans="1:11" ht="42.75" customHeight="1">
+      <c r="A67" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B67" s="24" t="s">
+      <c r="B67" s="19" t="s">
         <v>235</v>
       </c>
-      <c r="C67" s="24" t="s">
+      <c r="C67" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D67" s="18" t="s">
+      <c r="D67" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E67" s="24" t="s">
+      <c r="E67" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="F67" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G67" s="26" t="s">
+      <c r="F67" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G67" s="30" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A68" s="24" t="s">
+      <c r="H67" s="23"/>
+      <c r="I67" s="23"/>
+      <c r="J67" s="23"/>
+      <c r="K67" s="23"/>
+    </row>
+    <row r="68" spans="1:11" ht="24">
+      <c r="A68" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B68" s="24" t="s">
+      <c r="B68" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="C68" s="24" t="s">
+      <c r="C68" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D68" s="18" t="s">
+      <c r="D68" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E68" s="24" t="s">
+      <c r="E68" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="F68" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G68" s="27" t="s">
+      <c r="F68" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G68" s="31" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="69" spans="1:7" ht="29.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="24" t="s">
+      <c r="H68" s="23"/>
+      <c r="I68" s="23"/>
+      <c r="J68" s="23"/>
+      <c r="K68" s="23"/>
+    </row>
+    <row r="69" spans="1:11" ht="29.25" customHeight="1">
+      <c r="A69" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B69" s="24" t="s">
+      <c r="B69" s="19" t="s">
         <v>241</v>
       </c>
-      <c r="C69" s="24" t="s">
+      <c r="C69" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D69" s="18" t="s">
+      <c r="D69" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E69" s="24" t="s">
+      <c r="E69" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="F69" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G69" s="27" t="s">
+      <c r="F69" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G69" s="31" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="70" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A70" s="24" t="s">
+      <c r="H69" s="23"/>
+      <c r="I69" s="23"/>
+      <c r="J69" s="23"/>
+      <c r="K69" s="23"/>
+    </row>
+    <row r="70" spans="1:11" ht="24">
+      <c r="A70" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B70" s="24" t="s">
+      <c r="B70" s="19" t="s">
         <v>244</v>
       </c>
-      <c r="C70" s="24" t="s">
+      <c r="C70" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="18" t="s">
+      <c r="D70" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E70" s="24" t="s">
+      <c r="E70" s="19" t="s">
         <v>245</v>
       </c>
-      <c r="F70" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G70" s="27" t="s">
+      <c r="F70" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G70" s="31" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="71" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A71" s="24" t="s">
+      <c r="H70" s="23"/>
+      <c r="I70" s="23"/>
+      <c r="J70" s="23"/>
+      <c r="K70" s="23"/>
+    </row>
+    <row r="71" spans="1:11" ht="24">
+      <c r="A71" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B71" s="24" t="s">
+      <c r="B71" s="19" t="s">
         <v>247</v>
       </c>
-      <c r="C71" s="24" t="s">
+      <c r="C71" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D71" s="18" t="s">
+      <c r="D71" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E71" s="24" t="s">
+      <c r="E71" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="F71" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G71" s="27" t="s">
+      <c r="F71" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G71" s="31" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="72" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A72" s="24" t="s">
+      <c r="H71" s="23"/>
+      <c r="I71" s="23"/>
+      <c r="J71" s="23"/>
+      <c r="K71" s="23"/>
+    </row>
+    <row r="72" spans="1:11" ht="24">
+      <c r="A72" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B72" s="24" t="s">
+      <c r="B72" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="C72" s="24" t="s">
+      <c r="C72" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D72" s="18" t="s">
+      <c r="D72" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="24" t="s">
+      <c r="E72" s="19" t="s">
         <v>251</v>
       </c>
-      <c r="F72" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G72" s="27" t="s">
+      <c r="F72" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G72" s="31" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A73" s="24" t="s">
+      <c r="H72" s="23"/>
+      <c r="I72" s="23"/>
+      <c r="J72" s="23"/>
+      <c r="K72" s="23"/>
+    </row>
+    <row r="73" spans="1:11" ht="24">
+      <c r="A73" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B73" s="24" t="s">
+      <c r="B73" s="19" t="s">
         <v>253</v>
       </c>
-      <c r="C73" s="24" t="s">
+      <c r="C73" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D73" s="18" t="s">
+      <c r="D73" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E73" s="24" t="s">
+      <c r="E73" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="F73" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G73" s="27" t="s">
+      <c r="F73" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G73" s="31" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="74" spans="1:7" ht="29" x14ac:dyDescent="0.2">
-      <c r="A74" s="24" t="s">
+      <c r="H73" s="23"/>
+      <c r="I73" s="23"/>
+      <c r="J73" s="23"/>
+      <c r="K73" s="23"/>
+    </row>
+    <row r="74" spans="1:11" ht="24">
+      <c r="A74" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B74" s="24" t="s">
+      <c r="B74" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="C74" s="24" t="s">
+      <c r="C74" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D74" s="18" t="s">
+      <c r="D74" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E74" s="24" t="s">
+      <c r="E74" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="F74" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G74" s="26" t="s">
+      <c r="F74" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G74" s="30" t="s">
         <v>258</v>
       </c>
-    </row>
-    <row r="75" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A75" s="24" t="s">
+      <c r="H74" s="23"/>
+      <c r="I74" s="23"/>
+      <c r="J74" s="23"/>
+      <c r="K74" s="23"/>
+    </row>
+    <row r="75" spans="1:11" ht="24">
+      <c r="A75" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B75" s="24" t="s">
+      <c r="B75" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="C75" s="25" t="s">
+      <c r="C75" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D75" s="18" t="s">
+      <c r="D75" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E75" s="24" t="s">
+      <c r="E75" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="F75" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G75" s="27" t="s">
+      <c r="F75" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G75" s="31" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="76" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A76" s="24" t="s">
+      <c r="H75" s="23"/>
+      <c r="I75" s="23"/>
+      <c r="J75" s="23"/>
+      <c r="K75" s="23"/>
+    </row>
+    <row r="76" spans="1:11" ht="24">
+      <c r="A76" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B76" s="24" t="s">
+      <c r="B76" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="C76" s="24" t="s">
+      <c r="C76" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D76" s="18" t="s">
+      <c r="D76" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E76" s="25" t="s">
+      <c r="E76" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="F76" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G76" s="27" t="s">
+      <c r="F76" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G76" s="31" t="s">
         <v>264</v>
       </c>
-    </row>
-    <row r="77" spans="1:7" s="9" customFormat="1" ht="28" x14ac:dyDescent="0.2">
-      <c r="A77" s="17" t="s">
+      <c r="H76" s="23"/>
+      <c r="I76" s="23"/>
+      <c r="J76" s="23"/>
+      <c r="K76" s="23"/>
+    </row>
+    <row r="77" spans="1:11" s="18" customFormat="1" ht="24">
+      <c r="A77" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="14" t="s">
         <v>265</v>
       </c>
-      <c r="C77" s="17" t="s">
+      <c r="C77" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="D77" s="18" t="s">
+      <c r="D77" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E77" s="17" t="s">
+      <c r="E77" s="14" t="s">
         <v>266</v>
       </c>
-      <c r="F77" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G77" s="19" t="s">
+      <c r="F77" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G77" s="28" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="78" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A78" s="24" t="s">
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
+      <c r="K77" s="17"/>
+    </row>
+    <row r="78" spans="1:11" ht="24">
+      <c r="A78" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B78" s="24" t="s">
+      <c r="B78" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="C78" s="24" t="s">
+      <c r="C78" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D78" s="18" t="s">
+      <c r="D78" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E78" s="25" t="s">
+      <c r="E78" s="29" t="s">
         <v>269</v>
       </c>
-      <c r="F78" s="17" t="s">
+      <c r="F78" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G78" s="27" t="s">
+      <c r="G78" s="31" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A79" s="24" t="s">
+      <c r="H78" s="23"/>
+      <c r="I78" s="23"/>
+      <c r="J78" s="23"/>
+      <c r="K78" s="23"/>
+    </row>
+    <row r="79" spans="1:11" ht="24">
+      <c r="A79" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B79" s="24" t="s">
+      <c r="B79" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="C79" s="24" t="s">
+      <c r="C79" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D79" s="18" t="s">
+      <c r="D79" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E79" s="25" t="s">
+      <c r="E79" s="29" t="s">
         <v>272</v>
       </c>
-      <c r="F79" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G79" s="27" t="s">
+      <c r="F79" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G79" s="31" t="s">
         <v>273</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A80" s="24" t="s">
+      <c r="H79" s="23"/>
+      <c r="I79" s="23"/>
+      <c r="J79" s="23"/>
+      <c r="K79" s="23"/>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B80" s="24" t="s">
+      <c r="B80" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="C80" s="24" t="s">
+      <c r="C80" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D80" s="18" t="s">
+      <c r="D80" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="E80" s="24" t="s">
+      <c r="E80" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F80" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G80" s="27" t="s">
+      <c r="F80" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G80" s="31" t="s">
         <v>277</v>
       </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A81" s="24" t="s">
+      <c r="H80" s="23"/>
+      <c r="I80" s="23"/>
+      <c r="J80" s="23"/>
+      <c r="K80" s="23"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B81" s="24" t="s">
+      <c r="B81" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="C81" s="24" t="s">
+      <c r="C81" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="D81" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="E81" s="24" t="s">
+      <c r="E81" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F81" s="17" t="s">
+      <c r="F81" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="G81" s="27" t="s">
+      <c r="G81" s="31" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="82" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A82" s="24" t="s">
+      <c r="H81" s="23"/>
+      <c r="I81" s="23"/>
+      <c r="J81" s="23"/>
+      <c r="K81" s="23"/>
+    </row>
+    <row r="82" spans="1:11" ht="24">
+      <c r="A82" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B82" s="24" t="s">
+      <c r="B82" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="C82" s="24" t="s">
+      <c r="C82" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D82" s="18" t="s">
+      <c r="D82" s="15" t="s">
         <v>275</v>
       </c>
-      <c r="E82" s="24" t="s">
+      <c r="E82" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="F82" s="17" t="s">
+      <c r="F82" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="G82" s="27" t="s">
+      <c r="G82" s="31" t="s">
         <v>281</v>
       </c>
-    </row>
-    <row r="83" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A83" s="24" t="s">
+      <c r="H82" s="23"/>
+      <c r="I82" s="23"/>
+      <c r="J82" s="23"/>
+      <c r="K82" s="23"/>
+    </row>
+    <row r="83" spans="1:11" ht="24">
+      <c r="A83" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B83" s="24" t="s">
+      <c r="B83" s="19" t="s">
         <v>282</v>
       </c>
-      <c r="C83" s="24" t="s">
+      <c r="C83" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="D83" s="18" t="s">
+      <c r="D83" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="E83" s="24" t="s">
+      <c r="E83" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="F83" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G83" s="27" t="s">
+      <c r="F83" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G83" s="31" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="84" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A84" s="24" t="s">
+      <c r="H83" s="23"/>
+      <c r="I83" s="23"/>
+      <c r="J83" s="23"/>
+      <c r="K83" s="23"/>
+    </row>
+    <row r="84" spans="1:11" ht="36">
+      <c r="A84" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B84" s="24" t="s">
+      <c r="B84" s="19" t="s">
         <v>285</v>
       </c>
-      <c r="C84" s="24" t="s">
+      <c r="C84" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D84" s="18" t="s">
+      <c r="D84" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="E84" s="24" t="s">
+      <c r="E84" s="19" t="s">
         <v>286</v>
       </c>
-      <c r="F84" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G84" s="27" t="s">
+      <c r="F84" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G84" s="31" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="85" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A85" s="24" t="s">
+      <c r="H84" s="23"/>
+      <c r="I84" s="23"/>
+      <c r="J84" s="23"/>
+      <c r="K84" s="23"/>
+    </row>
+    <row r="85" spans="1:11" ht="36">
+      <c r="A85" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B85" s="24" t="s">
+      <c r="B85" s="19" t="s">
         <v>288</v>
       </c>
-      <c r="C85" s="24" t="s">
+      <c r="C85" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D85" s="18" t="s">
+      <c r="D85" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E85" s="24" t="s">
+      <c r="E85" s="19" t="s">
         <v>289</v>
       </c>
-      <c r="F85" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G85" s="27" t="s">
+      <c r="F85" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G85" s="31" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="86" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A86" s="24" t="s">
+      <c r="H85" s="23"/>
+      <c r="I85" s="23"/>
+      <c r="J85" s="23"/>
+      <c r="K85" s="23"/>
+    </row>
+    <row r="86" spans="1:11" ht="24">
+      <c r="A86" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B86" s="24" t="s">
+      <c r="B86" s="19" t="s">
         <v>291</v>
       </c>
-      <c r="C86" s="24" t="s">
+      <c r="C86" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D86" s="18" t="s">
+      <c r="D86" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="E86" s="24" t="s">
+      <c r="E86" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="F86" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G86" s="27" t="s">
+      <c r="F86" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G86" s="31" t="s">
         <v>293</v>
       </c>
-    </row>
-    <row r="87" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A87" s="24" t="s">
+      <c r="H86" s="23"/>
+      <c r="I86" s="23"/>
+      <c r="J86" s="23"/>
+      <c r="K86" s="23"/>
+    </row>
+    <row r="87" spans="1:11" ht="24">
+      <c r="A87" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="B87" s="24" t="s">
+      <c r="B87" s="19" t="s">
         <v>294</v>
       </c>
-      <c r="C87" s="24" t="s">
+      <c r="C87" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D87" s="18" t="s">
+      <c r="D87" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E87" s="24" t="s">
+      <c r="E87" s="19" t="s">
         <v>295</v>
       </c>
-      <c r="F87" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G87" s="27" t="s">
+      <c r="F87" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G87" s="31" t="s">
         <v>296</v>
       </c>
-    </row>
-    <row r="88" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A88" s="17" t="s">
+      <c r="H87" s="23"/>
+      <c r="I87" s="23"/>
+      <c r="J87" s="23"/>
+      <c r="K87" s="23"/>
+    </row>
+    <row r="88" spans="1:11" ht="24">
+      <c r="A88" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B88" s="24" t="s">
+      <c r="B88" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="C88" s="24" t="s">
+      <c r="C88" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D88" s="18" t="s">
+      <c r="D88" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E88" s="24" t="s">
+      <c r="E88" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="F88" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G88" s="27" t="s">
+      <c r="F88" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G88" s="31" t="s">
         <v>299</v>
       </c>
-    </row>
-    <row r="89" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A89" s="17" t="s">
+      <c r="H88" s="23"/>
+      <c r="I88" s="23"/>
+      <c r="J88" s="23"/>
+      <c r="K88" s="23"/>
+    </row>
+    <row r="89" spans="1:11" ht="24">
+      <c r="A89" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B89" s="24" t="s">
+      <c r="B89" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="C89" s="24" t="s">
+      <c r="C89" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D89" s="18" t="s">
+      <c r="D89" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E89" s="24" t="s">
+      <c r="E89" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="F89" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G89" s="27" t="s">
+      <c r="F89" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G89" s="31" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="90" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A90" s="17" t="s">
+      <c r="H89" s="23"/>
+      <c r="I89" s="23"/>
+      <c r="J89" s="23"/>
+      <c r="K89" s="23"/>
+    </row>
+    <row r="90" spans="1:11" ht="24">
+      <c r="A90" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B90" s="24" t="s">
+      <c r="B90" s="19" t="s">
         <v>303</v>
       </c>
-      <c r="C90" s="24" t="s">
+      <c r="C90" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D90" s="18" t="s">
+      <c r="D90" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="E90" s="24" t="s">
+      <c r="E90" s="19" t="s">
         <v>304</v>
       </c>
-      <c r="F90" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G90" s="27" t="s">
+      <c r="F90" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G90" s="31" t="s">
         <v>305</v>
       </c>
-    </row>
-    <row r="91" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="17" t="s">
+      <c r="H90" s="23"/>
+      <c r="I90" s="23"/>
+      <c r="J90" s="23"/>
+      <c r="K90" s="23"/>
+    </row>
+    <row r="91" spans="1:11" ht="33" customHeight="1">
+      <c r="A91" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B91" s="24" t="s">
+      <c r="B91" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="C91" s="24" t="s">
+      <c r="C91" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D91" s="18" t="s">
+      <c r="D91" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E91" s="24" t="s">
+      <c r="E91" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="F91" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G91" s="27" t="s">
+      <c r="F91" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G91" s="31" t="s">
         <v>308</v>
       </c>
-    </row>
-    <row r="92" spans="1:7" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="17" t="s">
+      <c r="H91" s="23"/>
+      <c r="I91" s="23"/>
+      <c r="J91" s="23"/>
+      <c r="K91" s="23"/>
+    </row>
+    <row r="92" spans="1:11" ht="28.5" customHeight="1">
+      <c r="A92" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B92" s="24" t="s">
+      <c r="B92" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="C92" s="24" t="s">
+      <c r="C92" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D92" s="18" t="s">
+      <c r="D92" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E92" s="24" t="s">
+      <c r="E92" s="19" t="s">
         <v>310</v>
       </c>
-      <c r="F92" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G92" s="27" t="s">
+      <c r="F92" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G92" s="31" t="s">
         <v>311</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A93" s="17" t="s">
+      <c r="H92" s="23"/>
+      <c r="I92" s="23"/>
+      <c r="J92" s="23"/>
+      <c r="K92" s="23"/>
+    </row>
+    <row r="93" spans="1:11" ht="24">
+      <c r="A93" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B93" s="24" t="s">
+      <c r="B93" s="19" t="s">
         <v>312</v>
       </c>
-      <c r="C93" s="24" t="s">
+      <c r="C93" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D93" s="18" t="s">
+      <c r="D93" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E93" s="24" t="s">
+      <c r="E93" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="F93" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G93" s="27" t="s">
+      <c r="F93" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G93" s="31" t="s">
         <v>314</v>
       </c>
-    </row>
-    <row r="94" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A94" s="17" t="s">
+      <c r="H93" s="23"/>
+      <c r="I93" s="23"/>
+      <c r="J93" s="23"/>
+      <c r="K93" s="23"/>
+    </row>
+    <row r="94" spans="1:11" ht="24">
+      <c r="A94" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B94" s="24" t="s">
+      <c r="B94" s="19" t="s">
         <v>315</v>
       </c>
-      <c r="C94" s="24" t="s">
+      <c r="C94" s="19" t="s">
         <v>68</v>
       </c>
-      <c r="D94" s="29" t="s">
+      <c r="D94" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="E94" s="24" t="s">
+      <c r="E94" s="19" t="s">
         <v>316</v>
       </c>
-      <c r="F94" s="24" t="s">
+      <c r="F94" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="G94" s="45" t="s">
+      <c r="G94" s="38" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="95" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A95" s="17" t="s">
+      <c r="H94" s="23"/>
+      <c r="I94" s="23"/>
+      <c r="J94" s="23"/>
+      <c r="K94" s="23"/>
+    </row>
+    <row r="95" spans="1:11" ht="48">
+      <c r="A95" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B95" s="24" t="s">
+      <c r="B95" s="19" t="s">
         <v>318</v>
       </c>
-      <c r="C95" s="24" t="s">
+      <c r="C95" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D95" s="18" t="s">
+      <c r="D95" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="E95" s="24" t="s">
+      <c r="E95" s="19" t="s">
         <v>319</v>
       </c>
-      <c r="F95" s="17" t="s">
+      <c r="F95" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G95" s="27" t="s">
+      <c r="G95" s="31" t="s">
         <v>320</v>
       </c>
-    </row>
-    <row r="96" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A96" s="17" t="s">
+      <c r="H95" s="23"/>
+      <c r="I95" s="23"/>
+      <c r="J95" s="23"/>
+      <c r="K95" s="23"/>
+    </row>
+    <row r="96" spans="1:11" ht="24">
+      <c r="A96" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B96" s="24" t="s">
+      <c r="B96" s="19" t="s">
         <v>321</v>
       </c>
-      <c r="C96" s="24" t="s">
+      <c r="C96" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D96" s="18" t="s">
+      <c r="D96" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="E96" s="24" t="s">
+      <c r="E96" s="19" t="s">
         <v>322</v>
       </c>
-      <c r="F96" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G96" s="27" t="s">
+      <c r="F96" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G96" s="31" t="s">
         <v>323</v>
       </c>
-    </row>
-    <row r="97" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A97" s="17" t="s">
+      <c r="H96" s="23"/>
+      <c r="I96" s="23"/>
+      <c r="J96" s="23"/>
+      <c r="K96" s="23"/>
+    </row>
+    <row r="97" spans="1:11" ht="24">
+      <c r="A97" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B97" s="24" t="s">
+      <c r="B97" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="C97" s="24" t="s">
+      <c r="C97" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D97" s="18" t="s">
+      <c r="D97" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E97" s="24" t="s">
+      <c r="E97" s="19" t="s">
         <v>325</v>
       </c>
-      <c r="F97" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G97" s="27" t="s">
+      <c r="F97" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G97" s="31" t="s">
         <v>326</v>
       </c>
-    </row>
-    <row r="98" spans="1:7" s="11" customFormat="1" ht="42" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="17" t="s">
+      <c r="H97" s="23"/>
+      <c r="I97" s="23"/>
+      <c r="J97" s="23"/>
+      <c r="K97" s="23"/>
+    </row>
+    <row r="98" spans="1:11" s="21" customFormat="1" ht="36">
+      <c r="A98" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B98" s="32" t="s">
+      <c r="B98" s="39" t="s">
         <v>327</v>
       </c>
-      <c r="C98" s="32" t="s">
+      <c r="C98" s="39" t="s">
         <v>75</v>
       </c>
-      <c r="D98" s="33" t="s">
+      <c r="D98" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="E98" s="32" t="s">
+      <c r="E98" s="39" t="s">
         <v>328</v>
       </c>
-      <c r="F98" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="G98" s="34" t="s">
+      <c r="F98" s="39" t="s">
+        <v>12</v>
+      </c>
+      <c r="G98" s="41" t="s">
         <v>329</v>
       </c>
-    </row>
-    <row r="99" spans="1:7" ht="41.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="17" t="s">
+      <c r="H98" s="20"/>
+      <c r="I98" s="20"/>
+      <c r="J98" s="20"/>
+      <c r="K98" s="20"/>
+    </row>
+    <row r="99" spans="1:11" ht="41.25" customHeight="1">
+      <c r="A99" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B99" s="24" t="s">
+      <c r="B99" s="19" t="s">
         <v>330</v>
       </c>
-      <c r="C99" s="24" t="s">
+      <c r="C99" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="D99" s="18" t="s">
+      <c r="D99" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="E99" s="24" t="s">
+      <c r="E99" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="F99" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G99" s="27" t="s">
+      <c r="F99" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G99" s="31" t="s">
         <v>331</v>
       </c>
-    </row>
-    <row r="100" spans="1:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="17" t="s">
+      <c r="H99" s="23"/>
+      <c r="I99" s="23"/>
+      <c r="J99" s="23"/>
+      <c r="K99" s="23"/>
+    </row>
+    <row r="100" spans="1:11" ht="42" customHeight="1">
+      <c r="A100" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B100" s="24" t="s">
+      <c r="B100" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="C100" s="24" t="s">
+      <c r="C100" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D100" s="18" t="s">
+      <c r="D100" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="E100" s="24" t="s">
+      <c r="E100" s="19" t="s">
         <v>333</v>
       </c>
-      <c r="F100" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G100" s="27" t="s">
+      <c r="F100" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G100" s="31" t="s">
         <v>334</v>
       </c>
-    </row>
-    <row r="101" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A101" s="24" t="s">
+      <c r="H100" s="23"/>
+      <c r="I100" s="23"/>
+      <c r="J100" s="23"/>
+      <c r="K100" s="23"/>
+    </row>
+    <row r="101" spans="1:11" ht="24">
+      <c r="A101" s="19" t="s">
         <v>335</v>
       </c>
-      <c r="B101" s="24" t="s">
+      <c r="B101" s="19" t="s">
         <v>336</v>
       </c>
-      <c r="C101" s="24" t="s">
+      <c r="C101" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D101" s="18" t="s">
+      <c r="D101" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="E101" s="24" t="s">
+      <c r="E101" s="19" t="s">
         <v>338</v>
       </c>
-      <c r="F101" s="17" t="s">
+      <c r="F101" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="G101" s="27" t="s">
+      <c r="G101" s="31" t="s">
         <v>339</v>
       </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A102" s="24" t="s">
+      <c r="H101" s="23"/>
+      <c r="I101" s="23"/>
+      <c r="J101" s="23"/>
+      <c r="K101" s="23"/>
+    </row>
+    <row r="102" spans="1:11" ht="24">
+      <c r="A102" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="B102" s="24" t="s">
+      <c r="B102" s="19" t="s">
         <v>341</v>
       </c>
-      <c r="C102" s="24" t="s">
+      <c r="C102" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D102" s="18" t="s">
+      <c r="D102" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E102" s="19" t="s">
+        <v>342</v>
+      </c>
+      <c r="F102" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G102" s="31" t="s">
+        <v>343</v>
+      </c>
+      <c r="H102" s="23"/>
+      <c r="I102" s="23"/>
+      <c r="J102" s="23"/>
+      <c r="K102" s="23"/>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" s="19" t="s">
+        <v>340</v>
+      </c>
+      <c r="B103" s="19" t="s">
+        <v>344</v>
+      </c>
+      <c r="C103" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D103" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E102" s="24" t="s">
-        <v>342</v>
-      </c>
-      <c r="F102" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G102" s="27" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A103" s="24" t="s">
+      <c r="E103" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="F103" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G103" s="31" t="s">
+        <v>346</v>
+      </c>
+      <c r="H103" s="23"/>
+      <c r="I103" s="23"/>
+      <c r="J103" s="23"/>
+      <c r="K103" s="23"/>
+    </row>
+    <row r="104" spans="1:11" ht="24">
+      <c r="A104" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="B103" s="24" t="s">
-        <v>344</v>
-      </c>
-      <c r="C103" s="24" t="s">
+      <c r="B104" s="19" t="s">
+        <v>347</v>
+      </c>
+      <c r="C104" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D103" s="18" t="s">
+      <c r="D104" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E103" s="24" t="s">
-        <v>345</v>
-      </c>
-      <c r="F103" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G103" s="27" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A104" s="24" t="s">
+      <c r="E104" s="19" t="s">
+        <v>348</v>
+      </c>
+      <c r="F104" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G104" s="31" t="s">
+        <v>349</v>
+      </c>
+      <c r="H104" s="23"/>
+      <c r="I104" s="23"/>
+      <c r="J104" s="23"/>
+      <c r="K104" s="23"/>
+    </row>
+    <row r="105" spans="1:11" ht="48">
+      <c r="A105" s="19" t="s">
         <v>340</v>
       </c>
-      <c r="B104" s="24" t="s">
-        <v>347</v>
-      </c>
-      <c r="C104" s="24" t="s">
+      <c r="B105" s="19" t="s">
+        <v>350</v>
+      </c>
+      <c r="C105" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D105" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105" s="19" t="s">
+        <v>351</v>
+      </c>
+      <c r="F105" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G105" s="31" t="s">
+        <v>352</v>
+      </c>
+      <c r="H105" s="23"/>
+      <c r="I105" s="23"/>
+      <c r="J105" s="23"/>
+      <c r="K105" s="23"/>
+    </row>
+    <row r="106" spans="1:11" ht="36">
+      <c r="A106" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B106" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C106" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D106" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E106" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="F106" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G106" s="31" t="s">
+        <v>356</v>
+      </c>
+      <c r="H106" s="23"/>
+      <c r="I106" s="23"/>
+      <c r="J106" s="23"/>
+      <c r="K106" s="23"/>
+    </row>
+    <row r="107" spans="1:11" ht="24">
+      <c r="A107" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B107" s="19" t="s">
+        <v>357</v>
+      </c>
+      <c r="C107" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D107" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E107" s="19" t="s">
+        <v>358</v>
+      </c>
+      <c r="F107" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G107" s="31" t="s">
+        <v>359</v>
+      </c>
+      <c r="H107" s="23"/>
+      <c r="I107" s="23"/>
+      <c r="J107" s="23"/>
+      <c r="K107" s="23"/>
+    </row>
+    <row r="108" spans="1:11" ht="24">
+      <c r="A108" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B108" s="19" t="s">
+        <v>360</v>
+      </c>
+      <c r="C108" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D108" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" s="19" t="s">
+        <v>361</v>
+      </c>
+      <c r="F108" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G108" s="31" t="s">
+        <v>362</v>
+      </c>
+      <c r="H108" s="23"/>
+      <c r="I108" s="23"/>
+      <c r="J108" s="23"/>
+      <c r="K108" s="23"/>
+    </row>
+    <row r="109" spans="1:11" ht="48">
+      <c r="A109" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B109" s="19" t="s">
+        <v>363</v>
+      </c>
+      <c r="C109" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D109" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E109" s="19" t="s">
+        <v>364</v>
+      </c>
+      <c r="F109" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G109" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="H109" s="23"/>
+      <c r="I109" s="23"/>
+      <c r="J109" s="23"/>
+      <c r="K109" s="23"/>
+    </row>
+    <row r="110" spans="1:11" ht="24">
+      <c r="A110" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B110" s="19" t="s">
+        <v>366</v>
+      </c>
+      <c r="C110" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="D110" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E110" s="19" t="s">
+        <v>367</v>
+      </c>
+      <c r="F110" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G110" s="31" t="s">
+        <v>368</v>
+      </c>
+      <c r="H110" s="23"/>
+      <c r="I110" s="23"/>
+      <c r="J110" s="23"/>
+      <c r="K110" s="23"/>
+    </row>
+    <row r="111" spans="1:11" ht="24">
+      <c r="A111" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B111" s="19" t="s">
+        <v>369</v>
+      </c>
+      <c r="C111" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D111" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="E111" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="F111" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" s="31" t="s">
+        <v>371</v>
+      </c>
+      <c r="H111" s="23"/>
+      <c r="I111" s="23"/>
+      <c r="J111" s="23"/>
+      <c r="K111" s="23"/>
+    </row>
+    <row r="112" spans="1:11" ht="108.75" customHeight="1">
+      <c r="A112" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B112" s="19" t="s">
+        <v>372</v>
+      </c>
+      <c r="C112" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D112" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E112" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="F112" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="G112" s="31" t="s">
+        <v>374</v>
+      </c>
+      <c r="H112" s="23"/>
+      <c r="I112" s="23"/>
+      <c r="J112" s="23"/>
+      <c r="K112" s="23"/>
+    </row>
+    <row r="113" spans="1:11" ht="83.25" customHeight="1">
+      <c r="A113" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B113" s="19" t="s">
+        <v>376</v>
+      </c>
+      <c r="C113" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D113" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E113" s="19" t="s">
+        <v>377</v>
+      </c>
+      <c r="F113" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G113" s="31" t="s">
+        <v>378</v>
+      </c>
+      <c r="H113" s="23"/>
+      <c r="I113" s="23"/>
+      <c r="J113" s="23"/>
+      <c r="K113" s="23"/>
+    </row>
+    <row r="114" spans="1:11" ht="24">
+      <c r="A114" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B114" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="C114" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D114" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E114" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="F114" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G114" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="H114" s="23"/>
+      <c r="I114" s="23"/>
+      <c r="J114" s="23"/>
+      <c r="K114" s="23"/>
+    </row>
+    <row r="115" spans="1:11" ht="24">
+      <c r="A115" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B115" s="19" t="s">
+        <v>382</v>
+      </c>
+      <c r="C115" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D115" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="E115" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="F115" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G115" s="31" t="s">
+        <v>384</v>
+      </c>
+      <c r="H115" s="23"/>
+      <c r="I115" s="23"/>
+      <c r="J115" s="23"/>
+      <c r="K115" s="23"/>
+    </row>
+    <row r="116" spans="1:11" ht="34.5" customHeight="1">
+      <c r="A116" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B116" s="19" t="s">
+        <v>385</v>
+      </c>
+      <c r="C116" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D116" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E116" s="19" t="s">
+        <v>386</v>
+      </c>
+      <c r="F116" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G116" s="31" t="s">
+        <v>387</v>
+      </c>
+      <c r="H116" s="23"/>
+      <c r="I116" s="23"/>
+      <c r="J116" s="23"/>
+      <c r="K116" s="23"/>
+    </row>
+    <row r="117" spans="1:11" ht="24">
+      <c r="A117" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B117" s="19" t="s">
+        <v>388</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D117" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="E117" s="19" t="s">
+        <v>389</v>
+      </c>
+      <c r="F117" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G117" s="31" t="s">
+        <v>390</v>
+      </c>
+      <c r="H117" s="23"/>
+      <c r="I117" s="23"/>
+      <c r="J117" s="23"/>
+      <c r="K117" s="23"/>
+    </row>
+    <row r="118" spans="1:11" ht="24">
+      <c r="A118" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B118" s="19" t="s">
+        <v>391</v>
+      </c>
+      <c r="C118" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="D118" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E118" s="19" t="s">
+        <v>392</v>
+      </c>
+      <c r="F118" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G118" s="31" t="s">
+        <v>393</v>
+      </c>
+      <c r="H118" s="23"/>
+      <c r="I118" s="23"/>
+      <c r="J118" s="23"/>
+      <c r="K118" s="23"/>
+    </row>
+    <row r="119" spans="1:11" ht="24">
+      <c r="A119" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B119" s="19" t="s">
+        <v>394</v>
+      </c>
+      <c r="C119" s="19" t="s">
+        <v>193</v>
+      </c>
+      <c r="D119" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E119" s="19" t="s">
+        <v>395</v>
+      </c>
+      <c r="F119" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G119" s="31" t="s">
+        <v>396</v>
+      </c>
+      <c r="H119" s="23"/>
+      <c r="I119" s="23"/>
+      <c r="J119" s="23"/>
+      <c r="K119" s="23"/>
+    </row>
+    <row r="120" spans="1:11" ht="24">
+      <c r="A120" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B120" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="C120" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D120" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" s="19" t="s">
+        <v>398</v>
+      </c>
+      <c r="F120" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G120" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="H120" s="23"/>
+      <c r="I120" s="23"/>
+      <c r="J120" s="23"/>
+      <c r="K120" s="23"/>
+    </row>
+    <row r="121" spans="1:11" s="44" customFormat="1" ht="36">
+      <c r="A121" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B121" s="14" t="s">
+        <v>400</v>
+      </c>
+      <c r="C121" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D121" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E121" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="F121" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G121" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="H121" s="43"/>
+      <c r="I121" s="43"/>
+      <c r="J121" s="43"/>
+      <c r="K121" s="43"/>
+    </row>
+    <row r="122" spans="1:11" s="44" customFormat="1" ht="36">
+      <c r="A122" s="14" t="s">
+        <v>375</v>
+      </c>
+      <c r="B122" s="14" t="s">
+        <v>403</v>
+      </c>
+      <c r="C122" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D122" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E122" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="F122" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G122" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="H122" s="43"/>
+      <c r="I122" s="43"/>
+      <c r="J122" s="43"/>
+      <c r="K122" s="43"/>
+    </row>
+    <row r="123" spans="1:11" ht="24">
+      <c r="A123" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B123" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="C123" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D123" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="E123" s="19" t="s">
+        <v>406</v>
+      </c>
+      <c r="F123" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G123" s="31" t="s">
+        <v>407</v>
+      </c>
+      <c r="H123" s="23"/>
+      <c r="I123" s="23"/>
+      <c r="J123" s="23"/>
+      <c r="K123" s="23"/>
+    </row>
+    <row r="124" spans="1:11" ht="24">
+      <c r="A124" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B124" s="19" t="s">
+        <v>408</v>
+      </c>
+      <c r="C124" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D124" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E124" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="F124" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G124" s="31" t="s">
+        <v>410</v>
+      </c>
+      <c r="H124" s="23"/>
+      <c r="I124" s="23"/>
+      <c r="J124" s="23"/>
+      <c r="K124" s="23"/>
+    </row>
+    <row r="125" spans="1:11" ht="24">
+      <c r="A125" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B125" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="C125" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D125" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E125" s="19" t="s">
+        <v>412</v>
+      </c>
+      <c r="F125" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G125" s="31" t="s">
+        <v>413</v>
+      </c>
+      <c r="H125" s="23"/>
+      <c r="I125" s="23"/>
+      <c r="J125" s="23"/>
+      <c r="K125" s="23"/>
+    </row>
+    <row r="126" spans="1:11" ht="24">
+      <c r="A126" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B126" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="C126" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D126" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E126" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="F126" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G126" s="31" t="s">
+        <v>416</v>
+      </c>
+      <c r="H126" s="23"/>
+      <c r="I126" s="23"/>
+      <c r="J126" s="23"/>
+      <c r="K126" s="23"/>
+    </row>
+    <row r="127" spans="1:11" ht="24">
+      <c r="A127" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B127" s="19" t="s">
+        <v>417</v>
+      </c>
+      <c r="C127" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D127" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="E127" s="19" t="s">
+        <v>418</v>
+      </c>
+      <c r="F127" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G127" s="31" t="s">
+        <v>419</v>
+      </c>
+      <c r="H127" s="23"/>
+      <c r="I127" s="23"/>
+      <c r="J127" s="23"/>
+      <c r="K127" s="23"/>
+    </row>
+    <row r="128" spans="1:11" ht="24">
+      <c r="A128" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B128" s="19" t="s">
+        <v>420</v>
+      </c>
+      <c r="C128" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D128" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E128" s="19" t="s">
+        <v>421</v>
+      </c>
+      <c r="F128" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G128" s="31" t="s">
+        <v>422</v>
+      </c>
+      <c r="H128" s="23"/>
+      <c r="I128" s="23"/>
+      <c r="J128" s="23"/>
+      <c r="K128" s="23"/>
+    </row>
+    <row r="129" spans="1:11" ht="24">
+      <c r="A129" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B129" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="C129" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D129" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E129" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="F129" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G129" s="31" t="s">
+        <v>424</v>
+      </c>
+      <c r="H129" s="23"/>
+      <c r="I129" s="23"/>
+      <c r="J129" s="23"/>
+      <c r="K129" s="23"/>
+    </row>
+    <row r="130" spans="1:11" ht="24">
+      <c r="A130" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B130" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="C130" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D130" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="F130" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G130" s="31" t="s">
+        <v>427</v>
+      </c>
+      <c r="H130" s="23"/>
+      <c r="I130" s="23"/>
+      <c r="J130" s="23"/>
+      <c r="K130" s="23"/>
+    </row>
+    <row r="131" spans="1:11" ht="24">
+      <c r="A131" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="B131" s="19" t="s">
+        <v>429</v>
+      </c>
+      <c r="C131" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="D104" s="18" t="s">
+      <c r="D131" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E131" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="F131" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G131" s="31" t="s">
+        <v>431</v>
+      </c>
+      <c r="H131" s="23"/>
+      <c r="I131" s="23"/>
+      <c r="J131" s="23"/>
+      <c r="K131" s="23"/>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="B132" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="C132" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D132" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="E132" s="29" t="s">
+        <v>433</v>
+      </c>
+      <c r="F132" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G132" s="31" t="s">
+        <v>434</v>
+      </c>
+      <c r="H132" s="23"/>
+      <c r="I132" s="23"/>
+      <c r="J132" s="23"/>
+      <c r="K132" s="23"/>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="B133" s="19" t="s">
+        <v>435</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D133" s="15" t="s">
+        <v>51</v>
+      </c>
+      <c r="E133" s="19" t="s">
+        <v>436</v>
+      </c>
+      <c r="F133" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G133" s="31" t="s">
+        <v>437</v>
+      </c>
+      <c r="H133" s="23"/>
+      <c r="I133" s="23"/>
+      <c r="J133" s="23"/>
+      <c r="K133" s="23"/>
+    </row>
+    <row r="134" spans="1:11" ht="48">
+      <c r="A134" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="B134" s="19" t="s">
+        <v>438</v>
+      </c>
+      <c r="C134" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D134" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E134" s="29" t="s">
+        <v>439</v>
+      </c>
+      <c r="F134" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G134" s="31" t="s">
+        <v>440</v>
+      </c>
+      <c r="H134" s="23"/>
+      <c r="I134" s="23"/>
+      <c r="J134" s="23"/>
+      <c r="K134" s="23"/>
+    </row>
+    <row r="135" spans="1:11" ht="24">
+      <c r="A135" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="B135" s="19" t="s">
+        <v>441</v>
+      </c>
+      <c r="C135" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D135" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E135" s="29" t="s">
+        <v>442</v>
+      </c>
+      <c r="F135" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G135" s="31" t="s">
+        <v>443</v>
+      </c>
+      <c r="H135" s="23"/>
+      <c r="I135" s="23"/>
+      <c r="J135" s="23"/>
+      <c r="K135" s="23"/>
+    </row>
+    <row r="136" spans="1:11" ht="24">
+      <c r="A136" s="19" t="s">
+        <v>428</v>
+      </c>
+      <c r="B136" s="19" t="s">
+        <v>444</v>
+      </c>
+      <c r="C136" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D136" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E104" s="24" t="s">
-        <v>348</v>
-      </c>
-      <c r="F104" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G104" s="27" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A105" s="24" t="s">
-        <v>340</v>
-      </c>
-      <c r="B105" s="24" t="s">
-        <v>350</v>
-      </c>
-      <c r="C105" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="D105" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E105" s="24" t="s">
-        <v>351</v>
-      </c>
-      <c r="F105" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G105" s="27" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A106" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B106" s="24" t="s">
-        <v>354</v>
-      </c>
-      <c r="C106" s="24" t="s">
+      <c r="E136" s="29" t="s">
+        <v>445</v>
+      </c>
+      <c r="F136" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G136" s="31" t="s">
+        <v>446</v>
+      </c>
+      <c r="H136" s="23"/>
+      <c r="I136" s="23"/>
+      <c r="J136" s="23"/>
+      <c r="K136" s="23"/>
+    </row>
+    <row r="137" spans="1:11" ht="61.5" customHeight="1">
+      <c r="A137" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B137" s="19" t="s">
+        <v>448</v>
+      </c>
+      <c r="C137" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D106" s="18" t="s">
+      <c r="D137" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="E137" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="F137" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G137" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="H137" s="23"/>
+      <c r="I137" s="23"/>
+      <c r="J137" s="23"/>
+      <c r="K137" s="23"/>
+    </row>
+    <row r="138" spans="1:11" ht="36">
+      <c r="A138" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B138" s="19" t="s">
+        <v>451</v>
+      </c>
+      <c r="C138" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D138" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E138" s="19" t="s">
+        <v>452</v>
+      </c>
+      <c r="F138" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G138" s="31" t="s">
+        <v>453</v>
+      </c>
+      <c r="H138" s="23"/>
+      <c r="I138" s="23"/>
+      <c r="J138" s="23"/>
+      <c r="K138" s="23"/>
+    </row>
+    <row r="139" spans="1:11" ht="24">
+      <c r="A139" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B139" s="19" t="s">
+        <v>454</v>
+      </c>
+      <c r="C139" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D139" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="E106" s="24" t="s">
-        <v>355</v>
-      </c>
-      <c r="F106" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G106" s="27" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A107" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B107" s="24" t="s">
-        <v>357</v>
-      </c>
-      <c r="C107" s="24" t="s">
+      <c r="E139" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F139" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G139" s="31" t="s">
+        <v>456</v>
+      </c>
+      <c r="H139" s="23"/>
+      <c r="I139" s="23"/>
+      <c r="J139" s="23"/>
+      <c r="K139" s="23"/>
+    </row>
+    <row r="140" spans="1:11" ht="24">
+      <c r="A140" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B140" s="19" t="s">
+        <v>457</v>
+      </c>
+      <c r="C140" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D107" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E107" s="24" t="s">
-        <v>358</v>
-      </c>
-      <c r="F107" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G107" s="27" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A108" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B108" s="24" t="s">
-        <v>360</v>
-      </c>
-      <c r="C108" s="24" t="s">
+      <c r="D140" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E140" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F140" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G140" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="H140" s="23"/>
+      <c r="I140" s="23"/>
+      <c r="J140" s="23"/>
+      <c r="K140" s="23"/>
+    </row>
+    <row r="141" spans="1:11" ht="24">
+      <c r="A141" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B141" s="19" t="s">
+        <v>459</v>
+      </c>
+      <c r="C141" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D108" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="E108" s="24" t="s">
-        <v>361</v>
-      </c>
-      <c r="F108" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G108" s="27" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" ht="42" x14ac:dyDescent="0.2">
-      <c r="A109" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B109" s="24" t="s">
-        <v>363</v>
-      </c>
-      <c r="C109" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D109" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E109" s="24" t="s">
-        <v>364</v>
-      </c>
-      <c r="F109" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G109" s="27" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A110" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B110" s="24" t="s">
-        <v>366</v>
-      </c>
-      <c r="C110" s="24" t="s">
-        <v>68</v>
-      </c>
-      <c r="D110" s="18" t="s">
+      <c r="D141" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E141" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F141" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G141" s="31" t="s">
+        <v>460</v>
+      </c>
+      <c r="H141" s="23"/>
+      <c r="I141" s="23"/>
+      <c r="J141" s="23"/>
+      <c r="K141" s="23"/>
+    </row>
+    <row r="142" spans="1:11" ht="24">
+      <c r="A142" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B142" s="19" t="s">
+        <v>461</v>
+      </c>
+      <c r="C142" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D142" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E142" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F142" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G142" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="H142" s="23"/>
+      <c r="I142" s="23"/>
+      <c r="J142" s="23"/>
+      <c r="K142" s="23"/>
+    </row>
+    <row r="143" spans="1:11" ht="24">
+      <c r="A143" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B143" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="C143" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D143" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E143" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F143" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G143" s="31" t="s">
+        <v>464</v>
+      </c>
+      <c r="H143" s="23"/>
+      <c r="I143" s="23"/>
+      <c r="J143" s="23"/>
+      <c r="K143" s="23"/>
+    </row>
+    <row r="144" spans="1:11" ht="24">
+      <c r="A144" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B144" s="19" t="s">
+        <v>465</v>
+      </c>
+      <c r="C144" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D144" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E144" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F144" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G144" s="31" t="s">
+        <v>466</v>
+      </c>
+      <c r="H144" s="23"/>
+      <c r="I144" s="23"/>
+      <c r="J144" s="23"/>
+      <c r="K144" s="23"/>
+    </row>
+    <row r="145" spans="1:12" ht="24">
+      <c r="A145" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B145" s="19" t="s">
+        <v>467</v>
+      </c>
+      <c r="C145" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D145" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E145" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F145" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G145" s="31" t="s">
+        <v>468</v>
+      </c>
+      <c r="H145" s="23"/>
+      <c r="I145" s="23"/>
+      <c r="J145" s="23"/>
+      <c r="K145" s="23"/>
+    </row>
+    <row r="146" spans="1:12" ht="24">
+      <c r="A146" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B146" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="C146" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D146" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E146" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F146" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G146" s="31" t="s">
+        <v>470</v>
+      </c>
+      <c r="H146" s="23"/>
+      <c r="I146" s="23"/>
+      <c r="J146" s="23"/>
+      <c r="K146" s="23"/>
+    </row>
+    <row r="147" spans="1:12" ht="24">
+      <c r="A147" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B147" s="19" t="s">
+        <v>471</v>
+      </c>
+      <c r="C147" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D147" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E147" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F147" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G147" s="31" t="s">
+        <v>472</v>
+      </c>
+      <c r="H147" s="23"/>
+      <c r="I147" s="23"/>
+      <c r="J147" s="23"/>
+      <c r="K147" s="23"/>
+    </row>
+    <row r="148" spans="1:12" ht="24">
+      <c r="A148" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B148" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="C148" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D148" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E148" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F148" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G148" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="H148" s="23"/>
+      <c r="I148" s="23"/>
+      <c r="J148" s="23"/>
+      <c r="K148" s="23"/>
+    </row>
+    <row r="149" spans="1:12" ht="24">
+      <c r="A149" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B149" s="19" t="s">
+        <v>475</v>
+      </c>
+      <c r="C149" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D149" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E149" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F149" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G149" s="31" t="s">
+        <v>476</v>
+      </c>
+      <c r="H149" s="23"/>
+      <c r="I149" s="23"/>
+      <c r="J149" s="23"/>
+      <c r="K149" s="23"/>
+    </row>
+    <row r="150" spans="1:12" ht="24">
+      <c r="A150" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B150" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="C150" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D150" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E150" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F150" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G150" s="31" t="s">
+        <v>478</v>
+      </c>
+      <c r="H150" s="23"/>
+      <c r="I150" s="23"/>
+      <c r="J150" s="23"/>
+      <c r="K150" s="23"/>
+    </row>
+    <row r="151" spans="1:12" ht="24">
+      <c r="A151" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B151" s="19" t="s">
+        <v>479</v>
+      </c>
+      <c r="C151" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D151" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E151" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F151" s="14" t="s">
+        <v>12</v>
+      </c>
+      <c r="G151" s="31" t="s">
+        <v>480</v>
+      </c>
+      <c r="H151" s="23"/>
+      <c r="I151" s="23"/>
+      <c r="J151" s="23"/>
+      <c r="K151" s="23"/>
+    </row>
+    <row r="152" spans="1:12">
+      <c r="A152" s="19" t="s">
+        <v>447</v>
+      </c>
+      <c r="B152" s="19" t="s">
+        <v>481</v>
+      </c>
+      <c r="C152" s="19" t="s">
+        <v>137</v>
+      </c>
+      <c r="D152" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E152" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="F152" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G152" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="H152" s="23"/>
+      <c r="I152" s="23"/>
+      <c r="J152" s="23"/>
+      <c r="K152" s="23"/>
+    </row>
+    <row r="153" spans="1:12" ht="39" customHeight="1">
+      <c r="A153" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B153" s="45" t="s">
+        <v>484</v>
+      </c>
+      <c r="C153" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D153" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E153" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="F153" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G153" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="H153" s="23"/>
+      <c r="I153" s="23"/>
+      <c r="J153" s="23"/>
+      <c r="K153" s="23"/>
+    </row>
+    <row r="154" spans="1:12" s="46" customFormat="1" ht="24">
+      <c r="A154" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="B154" s="29" t="s">
+        <v>487</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D154" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E154" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="F154" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="G154" s="31" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12">
+      <c r="A155" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B155" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="C155" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D155" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="E155" s="47" t="s">
+        <v>491</v>
+      </c>
+      <c r="F155" s="19" t="s">
+        <v>280</v>
+      </c>
+      <c r="G155" s="48" t="s">
+        <v>492</v>
+      </c>
+      <c r="H155" s="23"/>
+      <c r="I155" s="23"/>
+      <c r="J155" s="23"/>
+      <c r="K155" s="23"/>
+    </row>
+    <row r="156" spans="1:12" ht="24">
+      <c r="A156" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="B156" s="46" t="s">
+        <v>493</v>
+      </c>
+      <c r="C156" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D156" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E156" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="F156" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G156" s="31" t="s">
+        <v>495</v>
+      </c>
+      <c r="H156" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="I156" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J156" s="23" t="s">
+        <v>497</v>
+      </c>
+      <c r="K156" s="32" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" ht="24">
+      <c r="A157" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="B157" s="46" t="s">
+        <v>498</v>
+      </c>
+      <c r="C157" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D157" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E157" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="F157" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G157" s="31" t="s">
+        <v>499</v>
+      </c>
+      <c r="H157" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="I157" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J157" s="23" t="s">
+        <v>500</v>
+      </c>
+      <c r="K157" s="32" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" ht="24">
+      <c r="A158" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="B158" s="46" t="s">
+        <v>501</v>
+      </c>
+      <c r="C158" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D158" s="49" t="s">
+        <v>10</v>
+      </c>
+      <c r="E158" s="46" t="s">
+        <v>494</v>
+      </c>
+      <c r="F158" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G158" s="31" t="s">
+        <v>502</v>
+      </c>
+      <c r="H158" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="I158" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J158" s="23" t="s">
+        <v>503</v>
+      </c>
+      <c r="K158" s="32" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" ht="24">
+      <c r="A159" s="46" t="s">
+        <v>483</v>
+      </c>
+      <c r="B159" s="46" t="s">
+        <v>504</v>
+      </c>
+      <c r="C159" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D159" s="49" t="s">
+        <v>47</v>
+      </c>
+      <c r="E159" s="46" t="s">
+        <v>505</v>
+      </c>
+      <c r="F159" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G159" s="31" t="s">
+        <v>506</v>
+      </c>
+      <c r="H159" s="23" t="s">
+        <v>496</v>
+      </c>
+      <c r="I159" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="J159" s="23" t="s">
+        <v>507</v>
+      </c>
+      <c r="K159" s="32" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" ht="24">
+      <c r="A160" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="B160" s="42" t="s">
+        <v>508</v>
+      </c>
+      <c r="C160" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D160" s="42" t="s">
+        <v>142</v>
+      </c>
+      <c r="E160" s="47" t="s">
+        <v>509</v>
+      </c>
+      <c r="F160" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G160" s="16" t="s">
+        <v>510</v>
+      </c>
+      <c r="H160" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="I160" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J160" s="51" t="s">
+        <v>511</v>
+      </c>
+      <c r="K160" s="28" t="s">
+        <v>510</v>
+      </c>
+      <c r="L160" s="52"/>
+    </row>
+    <row r="161" spans="1:12" ht="24">
+      <c r="A161" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="B161" s="42" t="s">
+        <v>512</v>
+      </c>
+      <c r="C161" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D161" s="42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E161" s="47" t="s">
+        <v>513</v>
+      </c>
+      <c r="F161" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G161" s="16" t="s">
+        <v>514</v>
+      </c>
+      <c r="H161" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="I161" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J161" s="53" t="s">
+        <v>515</v>
+      </c>
+      <c r="K161" s="28" t="s">
+        <v>514</v>
+      </c>
+      <c r="L161" s="52"/>
+    </row>
+    <row r="162" spans="1:12">
+      <c r="A162" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="B162" s="42" t="s">
+        <v>516</v>
+      </c>
+      <c r="C162" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D162" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E162" s="47" t="s">
+        <v>517</v>
+      </c>
+      <c r="F162" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G162" s="16" t="s">
+        <v>518</v>
+      </c>
+      <c r="H162" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="I162" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J162" s="50" t="s">
+        <v>516</v>
+      </c>
+      <c r="K162" s="28" t="s">
+        <v>518</v>
+      </c>
+      <c r="L162" s="54"/>
+    </row>
+    <row r="163" spans="1:12">
+      <c r="A163" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="B163" s="42" t="s">
+        <v>519</v>
+      </c>
+      <c r="C163" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D163" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="E163" s="47" t="s">
+        <v>520</v>
+      </c>
+      <c r="F163" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G163" s="16" t="s">
+        <v>521</v>
+      </c>
+      <c r="H163" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="I163" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J163" s="50" t="s">
+        <v>519</v>
+      </c>
+      <c r="K163" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="L163" s="54"/>
+    </row>
+    <row r="164" spans="1:12" ht="24">
+      <c r="A164" s="42" t="s">
+        <v>483</v>
+      </c>
+      <c r="B164" s="42" t="s">
+        <v>522</v>
+      </c>
+      <c r="C164" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D164" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E164" s="47" t="s">
+        <v>523</v>
+      </c>
+      <c r="F164" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G164" s="16" t="s">
+        <v>524</v>
+      </c>
+      <c r="H164" s="50" t="s">
+        <v>496</v>
+      </c>
+      <c r="I164" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="J164" s="50" t="s">
+        <v>522</v>
+      </c>
+      <c r="K164" s="28" t="s">
+        <v>524</v>
+      </c>
+      <c r="L164" s="54"/>
+    </row>
+    <row r="165" spans="1:12" s="57" customFormat="1" ht="24">
+      <c r="A165" s="14" t="s">
+        <v>483</v>
+      </c>
+      <c r="B165" s="19" t="s">
+        <v>525</v>
+      </c>
+      <c r="C165" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D165" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E165" s="19" t="s">
+        <v>526</v>
+      </c>
+      <c r="F165" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G165" s="58" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" s="57" customFormat="1" ht="27">
+      <c r="A166" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B166" s="19" t="s">
+        <v>528</v>
+      </c>
+      <c r="C166" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D166" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="E110" s="24" t="s">
-        <v>367</v>
-      </c>
-      <c r="F110" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G110" s="27" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A111" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B111" s="24" t="s">
-        <v>369</v>
-      </c>
-      <c r="C111" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D111" s="18" t="s">
-        <v>103</v>
-      </c>
-      <c r="E111" s="24" t="s">
-        <v>370</v>
-      </c>
-      <c r="F111" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G111" s="27" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" ht="108.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="24" t="s">
-        <v>353</v>
-      </c>
-      <c r="B112" s="24" t="s">
-        <v>372</v>
-      </c>
-      <c r="C112" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D112" s="18" t="s">
+      <c r="E166" s="19" t="s">
+        <v>529</v>
+      </c>
+      <c r="F166" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G166" s="59" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" s="57" customFormat="1" ht="27">
+      <c r="A167" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B167" s="19" t="s">
+        <v>531</v>
+      </c>
+      <c r="C167" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D167" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E167" s="19" t="s">
+        <v>513</v>
+      </c>
+      <c r="F167" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G167" s="59" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" s="57" customFormat="1" ht="27">
+      <c r="A168" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B168" s="19" t="s">
+        <v>533</v>
+      </c>
+      <c r="C168" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D168" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="E112" s="24" t="s">
-        <v>373</v>
-      </c>
-      <c r="F112" s="17" t="s">
-        <v>158</v>
-      </c>
-      <c r="G112" s="27" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" ht="83.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B113" s="24" t="s">
-        <v>376</v>
-      </c>
-      <c r="C113" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="D113" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E113" s="24" t="s">
-        <v>377</v>
-      </c>
-      <c r="F113" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G113" s="27" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A114" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B114" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="C114" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D114" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E114" s="24" t="s">
-        <v>380</v>
-      </c>
-      <c r="F114" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G114" s="27" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A115" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B115" s="24" t="s">
-        <v>382</v>
-      </c>
-      <c r="C115" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="D115" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="E115" s="24" t="s">
-        <v>383</v>
-      </c>
-      <c r="F115" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G115" s="27" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B116" s="24" t="s">
-        <v>385</v>
-      </c>
-      <c r="C116" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D116" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E116" s="24" t="s">
-        <v>386</v>
-      </c>
-      <c r="F116" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G116" s="27" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A117" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B117" s="24" t="s">
-        <v>388</v>
-      </c>
-      <c r="C117" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D117" s="18" t="s">
-        <v>35</v>
-      </c>
-      <c r="E117" s="24" t="s">
-        <v>389</v>
-      </c>
-      <c r="F117" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G117" s="27" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A118" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B118" s="24" t="s">
-        <v>391</v>
-      </c>
-      <c r="C118" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="D118" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E118" s="24" t="s">
-        <v>392</v>
-      </c>
-      <c r="F118" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G118" s="27" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A119" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B119" s="24" t="s">
-        <v>394</v>
-      </c>
-      <c r="C119" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="D119" s="18" t="s">
+      <c r="E168" s="19" t="s">
+        <v>534</v>
+      </c>
+      <c r="F168" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G168" s="59" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" s="57" customFormat="1" ht="27">
+      <c r="A169" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B169" s="19" t="s">
+        <v>536</v>
+      </c>
+      <c r="C169" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D169" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="E169" s="19" t="s">
+        <v>537</v>
+      </c>
+      <c r="F169" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G169" s="59" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" s="57" customFormat="1" ht="27">
+      <c r="A170" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B170" s="19" t="s">
+        <v>539</v>
+      </c>
+      <c r="C170" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D170" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="E170" s="19" t="s">
+        <v>540</v>
+      </c>
+      <c r="F170" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G170" s="59" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" s="57" customFormat="1" ht="27">
+      <c r="A171" s="19" t="s">
+        <v>483</v>
+      </c>
+      <c r="B171" s="19" t="s">
+        <v>542</v>
+      </c>
+      <c r="C171" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="D171" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="E119" s="24" t="s">
-        <v>395</v>
-      </c>
-      <c r="F119" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G119" s="27" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A120" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B120" s="24" t="s">
-        <v>397</v>
-      </c>
-      <c r="C120" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D120" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E120" s="24" t="s">
-        <v>398</v>
-      </c>
-      <c r="F120" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G120" s="27" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" s="10" customFormat="1" ht="43" x14ac:dyDescent="0.2">
-      <c r="A121" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="C121" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D121" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E121" s="35" t="s">
-        <v>401</v>
-      </c>
-      <c r="F121" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G121" s="36" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" s="10" customFormat="1" ht="43" x14ac:dyDescent="0.2">
-      <c r="A122" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>403</v>
-      </c>
-      <c r="C122" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="D122" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E122" s="35" t="s">
-        <v>401</v>
-      </c>
-      <c r="F122" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G122" s="36" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A123" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B123" s="24" t="s">
-        <v>405</v>
-      </c>
-      <c r="C123" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D123" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="E123" s="24" t="s">
-        <v>406</v>
-      </c>
-      <c r="F123" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G123" s="27" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A124" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B124" s="24" t="s">
-        <v>408</v>
-      </c>
-      <c r="C124" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D124" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="E124" s="24" t="s">
-        <v>409</v>
-      </c>
-      <c r="F124" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G124" s="27" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A125" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B125" s="24" t="s">
-        <v>411</v>
-      </c>
-      <c r="C125" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D125" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E125" s="24" t="s">
-        <v>412</v>
-      </c>
-      <c r="F125" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G125" s="27" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A126" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B126" s="24" t="s">
-        <v>414</v>
-      </c>
-      <c r="C126" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D126" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E126" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="F126" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G126" s="27" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A127" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B127" s="24" t="s">
-        <v>417</v>
-      </c>
-      <c r="C127" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D127" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="E127" s="24" t="s">
-        <v>418</v>
-      </c>
-      <c r="F127" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G127" s="27" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A128" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B128" s="24" t="s">
-        <v>420</v>
-      </c>
-      <c r="C128" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E128" s="24" t="s">
-        <v>421</v>
-      </c>
-      <c r="F128" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G128" s="27" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A129" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B129" s="24" t="s">
-        <v>423</v>
-      </c>
-      <c r="C129" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D129" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E129" s="24" t="s">
-        <v>415</v>
-      </c>
-      <c r="F129" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G129" s="27" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A130" s="24" t="s">
-        <v>375</v>
-      </c>
-      <c r="B130" s="24" t="s">
-        <v>425</v>
-      </c>
-      <c r="C130" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D130" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E130" s="24" t="s">
-        <v>426</v>
-      </c>
-      <c r="F130" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G130" s="27" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A131" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="B131" s="24" t="s">
-        <v>429</v>
-      </c>
-      <c r="C131" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D131" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E131" s="25" t="s">
-        <v>430</v>
-      </c>
-      <c r="F131" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G131" s="27" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A132" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="B132" s="24" t="s">
-        <v>432</v>
-      </c>
-      <c r="C132" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D132" s="18" t="s">
-        <v>337</v>
-      </c>
-      <c r="E132" s="25" t="s">
-        <v>433</v>
-      </c>
-      <c r="F132" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G132" s="27" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A133" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="B133" s="24" t="s">
-        <v>435</v>
-      </c>
-      <c r="C133" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D133" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="E133" s="24" t="s">
-        <v>436</v>
-      </c>
-      <c r="F133" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G133" s="27" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" ht="56" x14ac:dyDescent="0.2">
-      <c r="A134" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="B134" s="24" t="s">
-        <v>438</v>
-      </c>
-      <c r="C134" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D134" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E134" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="F134" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G134" s="27" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A135" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="B135" s="24" t="s">
-        <v>441</v>
-      </c>
-      <c r="C135" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D135" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="E135" s="25" t="s">
-        <v>442</v>
-      </c>
-      <c r="F135" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G135" s="27" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A136" s="24" t="s">
-        <v>428</v>
-      </c>
-      <c r="B136" s="24" t="s">
-        <v>444</v>
-      </c>
-      <c r="C136" s="24" t="s">
-        <v>9</v>
-      </c>
-      <c r="D136" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E136" s="25" t="s">
-        <v>445</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G136" s="27" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B137" s="24" t="s">
-        <v>448</v>
-      </c>
-      <c r="C137" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D137" s="18" t="s">
-        <v>275</v>
-      </c>
-      <c r="E137" s="24" t="s">
-        <v>449</v>
-      </c>
-      <c r="F137" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G137" s="27" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A138" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B138" s="24" t="s">
-        <v>451</v>
-      </c>
-      <c r="C138" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D138" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E138" s="24" t="s">
-        <v>452</v>
-      </c>
-      <c r="F138" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G138" s="27" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A139" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B139" s="24" t="s">
-        <v>454</v>
-      </c>
-      <c r="C139" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D139" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E139" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F139" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G139" s="27" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A140" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B140" s="24" t="s">
-        <v>457</v>
-      </c>
-      <c r="C140" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D140" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E140" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F140" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G140" s="27" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A141" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B141" s="24" t="s">
-        <v>459</v>
-      </c>
-      <c r="C141" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D141" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E141" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F141" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G141" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A142" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B142" s="24" t="s">
-        <v>461</v>
-      </c>
-      <c r="C142" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D142" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E142" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F142" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G142" s="27" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A143" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B143" s="24" t="s">
-        <v>463</v>
-      </c>
-      <c r="C143" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D143" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E143" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F143" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G143" s="27" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" ht="28" x14ac:dyDescent="0.2">
-      <c r="A144" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B144" s="24" t="s">
-        <v>465</v>
-      </c>
-      <c r="C144" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D144" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E144" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F144" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G144" s="27" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A145" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B145" s="24" t="s">
-        <v>467</v>
-      </c>
-      <c r="C145" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D145" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E145" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F145" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G145" s="27" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A146" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B146" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="C146" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D146" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E146" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F146" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G146" s="27" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A147" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B147" s="24" t="s">
-        <v>471</v>
-      </c>
-      <c r="C147" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D147" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E147" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F147" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G147" s="27" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A148" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B148" s="24" t="s">
-        <v>473</v>
-      </c>
-      <c r="C148" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D148" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E148" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F148" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G148" s="27" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A149" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B149" s="24" t="s">
-        <v>475</v>
-      </c>
-      <c r="C149" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D149" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E149" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F149" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G149" s="27" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A150" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B150" s="24" t="s">
-        <v>477</v>
-      </c>
-      <c r="C150" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D150" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E150" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F150" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G150" s="27" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" ht="28" x14ac:dyDescent="0.2">
-      <c r="A151" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B151" s="24" t="s">
-        <v>479</v>
-      </c>
-      <c r="C151" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D151" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="E151" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F151" s="17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G151" s="27" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A152" s="24" t="s">
-        <v>447</v>
-      </c>
-      <c r="B152" s="24" t="s">
-        <v>481</v>
-      </c>
-      <c r="C152" s="24" t="s">
-        <v>137</v>
-      </c>
-      <c r="D152" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="E152" s="24" t="s">
-        <v>455</v>
-      </c>
-      <c r="F152" s="24" t="s">
-        <v>12</v>
-      </c>
-      <c r="G152" s="30" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" ht="39" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="24" t="s">
-        <v>483</v>
-      </c>
-      <c r="B153" s="37" t="s">
-        <v>484</v>
-      </c>
-      <c r="C153" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="D153" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="E153" s="24" t="s">
-        <v>485</v>
-      </c>
-      <c r="F153" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G153" s="27" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" s="12" customFormat="1" ht="28" x14ac:dyDescent="0.15">
-      <c r="A154" s="63" t="s">
-        <v>131</v>
-      </c>
-      <c r="B154" s="72" t="s">
-        <v>487</v>
-      </c>
-      <c r="C154" s="63" t="s">
-        <v>94</v>
-      </c>
-      <c r="D154" s="73" t="s">
-        <v>61</v>
-      </c>
-      <c r="E154" s="63" t="s">
-        <v>488</v>
-      </c>
-      <c r="F154" s="63" t="s">
-        <v>96</v>
-      </c>
-      <c r="G154" s="74" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A155" s="64" t="s">
-        <v>483</v>
-      </c>
-      <c r="B155" s="64" t="s">
-        <v>490</v>
-      </c>
-      <c r="C155" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D155" s="65" t="s">
-        <v>275</v>
-      </c>
-      <c r="E155" s="66" t="s">
-        <v>491</v>
-      </c>
-      <c r="F155" s="64" t="s">
-        <v>280</v>
-      </c>
-      <c r="G155" s="67" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" ht="280" x14ac:dyDescent="0.2">
-      <c r="A156" t="s">
-        <v>483</v>
-      </c>
-      <c r="B156" t="s">
-        <v>493</v>
-      </c>
-      <c r="C156" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D156" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E156" t="s">
-        <v>494</v>
-      </c>
-      <c r="F156" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G156" s="68" t="s">
-        <v>495</v>
-      </c>
-      <c r="H156" s="59" t="s">
-        <v>496</v>
-      </c>
-      <c r="I156" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="J156" s="46" t="s">
-        <v>497</v>
-      </c>
-      <c r="K156" s="48" t="s">
-        <v>495</v>
-      </c>
-      <c r="L156" s="46"/>
-    </row>
-    <row r="157" spans="1:12" ht="280" x14ac:dyDescent="0.2">
-      <c r="A157" t="s">
-        <v>483</v>
-      </c>
-      <c r="B157" t="s">
-        <v>498</v>
-      </c>
-      <c r="C157" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D157" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E157" t="s">
-        <v>494</v>
-      </c>
-      <c r="F157" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G157" s="68" t="s">
-        <v>499</v>
-      </c>
-      <c r="H157" s="60" t="s">
-        <v>496</v>
-      </c>
-      <c r="I157" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="J157" s="49" t="s">
-        <v>500</v>
-      </c>
-      <c r="K157" s="48" t="s">
-        <v>499</v>
-      </c>
-      <c r="L157" s="49"/>
-    </row>
-    <row r="158" spans="1:12" ht="280" x14ac:dyDescent="0.2">
-      <c r="A158" t="s">
-        <v>483</v>
-      </c>
-      <c r="B158" t="s">
-        <v>501</v>
-      </c>
-      <c r="C158" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D158" s="40" t="s">
-        <v>10</v>
-      </c>
-      <c r="E158" t="s">
-        <v>494</v>
-      </c>
-      <c r="F158" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G158" s="68" t="s">
-        <v>502</v>
-      </c>
-      <c r="H158" s="60" t="s">
-        <v>496</v>
-      </c>
-      <c r="I158" s="47" t="s">
-        <v>9</v>
-      </c>
-      <c r="J158" s="49" t="s">
-        <v>503</v>
-      </c>
-      <c r="K158" s="48" t="s">
-        <v>502</v>
-      </c>
-      <c r="L158" s="49"/>
-    </row>
-    <row r="159" spans="1:12" ht="280" x14ac:dyDescent="0.2">
-      <c r="A159" t="s">
-        <v>483</v>
-      </c>
-      <c r="B159" t="s">
-        <v>504</v>
-      </c>
-      <c r="C159" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D159" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E159" t="s">
-        <v>505</v>
-      </c>
-      <c r="F159" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G159" s="68" t="s">
-        <v>506</v>
-      </c>
-      <c r="H159" s="61" t="s">
-        <v>496</v>
-      </c>
-      <c r="I159" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="J159" s="50" t="s">
-        <v>507</v>
-      </c>
-      <c r="K159" s="52" t="s">
-        <v>506</v>
-      </c>
-      <c r="L159" s="50"/>
-    </row>
-    <row r="160" spans="1:12" ht="280" x14ac:dyDescent="0.2">
-      <c r="A160" s="69" t="s">
-        <v>483</v>
-      </c>
-      <c r="B160" s="69" t="s">
-        <v>508</v>
-      </c>
-      <c r="C160" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D160" s="69" t="s">
-        <v>142</v>
-      </c>
-      <c r="E160" s="70" t="s">
-        <v>509</v>
-      </c>
-      <c r="F160" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G160" s="71" t="s">
-        <v>510</v>
-      </c>
-      <c r="H160" s="62" t="s">
-        <v>496</v>
-      </c>
-      <c r="I160" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J160" s="55" t="s">
-        <v>511</v>
-      </c>
-      <c r="K160" s="56" t="s">
-        <v>510</v>
-      </c>
-      <c r="L160" s="53"/>
-    </row>
-    <row r="161" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A161" s="69" t="s">
-        <v>483</v>
-      </c>
-      <c r="B161" s="69" t="s">
-        <v>512</v>
-      </c>
-      <c r="C161" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D161" s="69" t="s">
-        <v>61</v>
-      </c>
-      <c r="E161" s="70" t="s">
-        <v>513</v>
-      </c>
-      <c r="F161" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G161" s="71" t="s">
-        <v>514</v>
-      </c>
-      <c r="H161" s="62" t="s">
-        <v>496</v>
-      </c>
-      <c r="I161" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J161" s="57" t="s">
-        <v>515</v>
-      </c>
-      <c r="K161" s="56" t="s">
-        <v>514</v>
-      </c>
-      <c r="L161" s="53"/>
-    </row>
-    <row r="162" spans="1:12" ht="288" x14ac:dyDescent="0.2">
-      <c r="A162" s="69" t="s">
-        <v>483</v>
-      </c>
-      <c r="B162" s="69" t="s">
-        <v>516</v>
-      </c>
-      <c r="C162" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D162" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="E162" s="70" t="s">
-        <v>517</v>
-      </c>
-      <c r="F162" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G162" s="71" t="s">
-        <v>518</v>
-      </c>
-      <c r="H162" s="62" t="s">
-        <v>496</v>
-      </c>
-      <c r="I162" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J162" s="53" t="s">
-        <v>516</v>
-      </c>
-      <c r="K162" s="56" t="s">
-        <v>518</v>
-      </c>
-      <c r="L162" s="58"/>
-    </row>
-    <row r="163" spans="1:12" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A163" s="69" t="s">
-        <v>483</v>
-      </c>
-      <c r="B163" s="69" t="s">
-        <v>519</v>
-      </c>
-      <c r="C163" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D163" s="69" t="s">
-        <v>23</v>
-      </c>
-      <c r="E163" s="70" t="s">
-        <v>520</v>
-      </c>
-      <c r="F163" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G163" s="71" t="s">
-        <v>521</v>
-      </c>
-      <c r="H163" s="62" t="s">
-        <v>496</v>
-      </c>
-      <c r="I163" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J163" s="53" t="s">
-        <v>519</v>
-      </c>
-      <c r="K163" s="56" t="s">
-        <v>521</v>
-      </c>
-      <c r="L163" s="58"/>
-    </row>
-    <row r="164" spans="1:12" ht="320" x14ac:dyDescent="0.2">
-      <c r="A164" s="69" t="s">
-        <v>483</v>
-      </c>
-      <c r="B164" s="69" t="s">
-        <v>522</v>
-      </c>
-      <c r="C164" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="D164" s="75" t="s">
-        <v>61</v>
-      </c>
-      <c r="E164" s="70" t="s">
-        <v>523</v>
-      </c>
-      <c r="F164" s="64" t="s">
-        <v>12</v>
-      </c>
-      <c r="G164" s="71" t="s">
-        <v>524</v>
-      </c>
-      <c r="H164" s="62" t="s">
-        <v>496</v>
-      </c>
-      <c r="I164" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="J164" s="53" t="s">
-        <v>522</v>
-      </c>
-      <c r="K164" s="56" t="s">
-        <v>524</v>
-      </c>
-      <c r="L164" s="58"/>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A165" s="8"/>
-      <c r="B165" s="8"/>
-      <c r="C165" s="8"/>
-      <c r="D165" s="8"/>
-      <c r="E165" s="8"/>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A166" s="8"/>
-      <c r="B166" s="8"/>
-      <c r="C166" s="8"/>
-      <c r="D166" s="8"/>
-      <c r="E166" s="8"/>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A167" s="8"/>
-      <c r="B167" s="8"/>
-      <c r="C167" s="8"/>
-      <c r="D167" s="8"/>
-      <c r="E167" s="8"/>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A168" s="8"/>
-      <c r="B168" s="8"/>
-      <c r="C168" s="8"/>
-      <c r="D168" s="8"/>
-      <c r="E168" s="8"/>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A169" s="8"/>
-      <c r="B169" s="8"/>
-      <c r="C169" s="8"/>
-      <c r="D169" s="8"/>
-      <c r="E169" s="8"/>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A170" s="8"/>
-      <c r="B170" s="8"/>
-      <c r="C170" s="8"/>
-      <c r="D170" s="8"/>
-      <c r="E170" s="8"/>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A171" s="8"/>
-      <c r="B171" s="8"/>
-      <c r="C171" s="8"/>
-      <c r="D171" s="8"/>
-      <c r="E171" s="8"/>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A172" s="8"/>
-      <c r="B172" s="8"/>
-      <c r="C172" s="8"/>
-      <c r="D172" s="8"/>
-      <c r="E172" s="8"/>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A173" s="8"/>
-      <c r="B173" s="8"/>
-      <c r="C173" s="8"/>
-      <c r="D173" s="8"/>
-      <c r="E173" s="8"/>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A174" s="8"/>
-      <c r="B174" s="8"/>
-      <c r="C174" s="8"/>
-      <c r="D174" s="8"/>
-      <c r="E174" s="8"/>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A175" s="8"/>
-      <c r="B175" s="8"/>
-      <c r="C175" s="8"/>
-      <c r="D175" s="8"/>
-      <c r="E175" s="8"/>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A176" s="8"/>
-      <c r="B176" s="8"/>
-      <c r="C176" s="8"/>
-      <c r="D176" s="8"/>
-      <c r="E176" s="8"/>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A177" s="8"/>
-      <c r="B177" s="8"/>
-      <c r="C177" s="8"/>
-      <c r="D177" s="8"/>
-      <c r="E177" s="8"/>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A178" s="8"/>
-      <c r="B178" s="8"/>
-      <c r="C178" s="8"/>
-      <c r="D178" s="8"/>
-      <c r="E178" s="8"/>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A179" s="8"/>
-      <c r="B179" s="8"/>
-      <c r="C179" s="8"/>
-      <c r="D179" s="8"/>
-      <c r="E179" s="8"/>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A180" s="8"/>
-      <c r="B180" s="8"/>
-      <c r="C180" s="8"/>
-      <c r="D180" s="8"/>
-      <c r="E180" s="8"/>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A181" s="8"/>
-      <c r="B181" s="8"/>
-      <c r="C181" s="8"/>
-      <c r="D181" s="8"/>
-      <c r="E181" s="8"/>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A182" s="8"/>
-      <c r="B182" s="8"/>
-      <c r="C182" s="8"/>
-      <c r="D182" s="8"/>
-      <c r="E182" s="8"/>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A183" s="8"/>
-      <c r="B183" s="8"/>
-      <c r="C183" s="8"/>
-      <c r="D183" s="8"/>
-      <c r="E183" s="8"/>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A184" s="8"/>
-      <c r="B184" s="8"/>
-      <c r="C184" s="8"/>
-      <c r="D184" s="8"/>
-      <c r="E184" s="8"/>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A185" s="8"/>
-      <c r="B185" s="8"/>
-      <c r="C185" s="8"/>
-      <c r="D185" s="8"/>
-      <c r="E185" s="8"/>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A186" s="8"/>
-      <c r="B186" s="8"/>
-      <c r="C186" s="8"/>
-      <c r="D186" s="8"/>
-      <c r="E186" s="8"/>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A187" s="8"/>
-      <c r="B187" s="8"/>
-      <c r="C187" s="8"/>
-      <c r="D187" s="8"/>
-      <c r="E187" s="8"/>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A188" s="8"/>
-      <c r="B188" s="8"/>
-      <c r="C188" s="8"/>
-      <c r="D188" s="8"/>
-      <c r="E188" s="8"/>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A189" s="8"/>
-      <c r="B189" s="8"/>
-      <c r="C189" s="8"/>
-      <c r="D189" s="8"/>
-      <c r="E189" s="8"/>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A190" s="8"/>
-      <c r="B190" s="8"/>
-      <c r="C190" s="8"/>
-      <c r="D190" s="8"/>
-      <c r="E190" s="8"/>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A191" s="8"/>
-      <c r="B191" s="8"/>
-      <c r="C191" s="8"/>
-      <c r="D191" s="8"/>
-      <c r="E191" s="8"/>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A192" s="8"/>
-      <c r="B192" s="8"/>
-      <c r="C192" s="8"/>
-      <c r="D192" s="8"/>
-      <c r="E192" s="8"/>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A193" s="8"/>
-      <c r="B193" s="8"/>
-      <c r="C193" s="8"/>
-      <c r="D193" s="8"/>
-      <c r="E193" s="8"/>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A194" s="8"/>
-      <c r="B194" s="8"/>
-      <c r="C194" s="8"/>
-      <c r="D194" s="8"/>
-      <c r="E194" s="8"/>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A195" s="8"/>
-      <c r="B195" s="8"/>
-      <c r="C195" s="8"/>
-      <c r="D195" s="8"/>
-      <c r="E195" s="8"/>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A196" s="8"/>
-      <c r="B196" s="8"/>
-      <c r="C196" s="8"/>
-      <c r="D196" s="8"/>
-      <c r="E196" s="8"/>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A197" s="8"/>
-      <c r="B197" s="8"/>
-      <c r="C197" s="8"/>
-      <c r="D197" s="8"/>
-      <c r="E197" s="8"/>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A198" s="8"/>
-      <c r="B198" s="8"/>
-      <c r="C198" s="8"/>
-      <c r="D198" s="8"/>
-      <c r="E198" s="8"/>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A199" s="8"/>
-      <c r="B199" s="8"/>
-      <c r="C199" s="8"/>
-      <c r="D199" s="8"/>
-      <c r="E199" s="8"/>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A200" s="8"/>
-      <c r="B200" s="8"/>
-      <c r="C200" s="8"/>
-      <c r="D200" s="8"/>
-      <c r="E200" s="8"/>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A201" s="8"/>
-      <c r="B201" s="8"/>
-      <c r="C201" s="8"/>
-      <c r="D201" s="8"/>
-      <c r="E201" s="8"/>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A202" s="8"/>
-      <c r="B202" s="8"/>
-      <c r="C202" s="8"/>
-      <c r="D202" s="8"/>
-      <c r="E202" s="8"/>
-    </row>
-    <row r="269" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E269" s="13"/>
-    </row>
-    <row r="271" spans="5:5" x14ac:dyDescent="0.2">
-      <c r="E271" s="14"/>
+      <c r="E171" s="19" t="s">
+        <v>543</v>
+      </c>
+      <c r="F171" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G171" s="59" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" s="57" customFormat="1" ht="14.25">
+      <c r="A172" s="19"/>
+      <c r="B172" s="19"/>
+      <c r="C172" s="19"/>
+      <c r="D172" s="19"/>
+      <c r="E172" s="19"/>
+      <c r="F172" s="19"/>
+      <c r="G172" s="19"/>
+    </row>
+    <row r="173" spans="1:12" s="57" customFormat="1" ht="14.25">
+      <c r="A173" s="19"/>
+      <c r="B173" s="19"/>
+      <c r="C173" s="19"/>
+      <c r="D173" s="19"/>
+      <c r="E173" s="19"/>
+      <c r="F173" s="19"/>
+      <c r="G173" s="19"/>
+    </row>
+    <row r="174" spans="1:12">
+      <c r="D174" s="55"/>
+    </row>
+    <row r="175" spans="1:12">
+      <c r="D175" s="55"/>
+    </row>
+    <row r="176" spans="1:12">
+      <c r="D176" s="55"/>
+    </row>
+    <row r="177" spans="4:4">
+      <c r="D177" s="55"/>
+    </row>
+    <row r="178" spans="4:4">
+      <c r="D178" s="55"/>
+    </row>
+    <row r="179" spans="4:4">
+      <c r="D179" s="55"/>
+    </row>
+    <row r="180" spans="4:4">
+      <c r="D180" s="55"/>
+    </row>
+    <row r="181" spans="4:4">
+      <c r="D181" s="55"/>
+    </row>
+    <row r="182" spans="4:4">
+      <c r="D182" s="55"/>
+    </row>
+    <row r="183" spans="4:4">
+      <c r="D183" s="55"/>
+    </row>
+    <row r="184" spans="4:4">
+      <c r="D184" s="55"/>
+    </row>
+    <row r="185" spans="4:4">
+      <c r="D185" s="55"/>
+    </row>
+    <row r="186" spans="4:4">
+      <c r="D186" s="55"/>
+    </row>
+    <row r="187" spans="4:4">
+      <c r="D187" s="55"/>
+    </row>
+    <row r="188" spans="4:4">
+      <c r="D188" s="55"/>
+    </row>
+    <row r="189" spans="4:4">
+      <c r="D189" s="55"/>
+    </row>
+    <row r="190" spans="4:4">
+      <c r="D190" s="55"/>
+    </row>
+    <row r="191" spans="4:4">
+      <c r="D191" s="55"/>
+    </row>
+    <row r="192" spans="4:4">
+      <c r="D192" s="55"/>
+    </row>
+    <row r="193" spans="4:4">
+      <c r="D193" s="55"/>
+    </row>
+    <row r="194" spans="4:4">
+      <c r="D194" s="55"/>
+    </row>
+    <row r="195" spans="4:4">
+      <c r="D195" s="55"/>
+    </row>
+    <row r="196" spans="4:4">
+      <c r="D196" s="55"/>
+    </row>
+    <row r="197" spans="4:4">
+      <c r="D197" s="55"/>
+    </row>
+    <row r="198" spans="4:4">
+      <c r="D198" s="55"/>
+    </row>
+    <row r="199" spans="4:4">
+      <c r="D199" s="55"/>
+    </row>
+    <row r="200" spans="4:4">
+      <c r="D200" s="55"/>
+    </row>
+    <row r="201" spans="4:4">
+      <c r="D201" s="55"/>
+    </row>
+    <row r="202" spans="4:4">
+      <c r="D202" s="55"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F270" xr:uid="{2C78B0D9-715E-4EDD-989F-8CB33D4C8A77}"/>
@@ -6904,194 +7461,201 @@
     <hyperlink ref="G164" r:id="rId170" xr:uid="{66B90635-FA20-4B3A-95B5-E735EACBBB93}"/>
     <hyperlink ref="G161" r:id="rId171" xr:uid="{058563C7-3039-464C-AAAA-5E8C55B5966B}"/>
     <hyperlink ref="G160" r:id="rId172" xr:uid="{DCCD4AB1-6174-4770-B88D-6D9A55AC89E9}"/>
+    <hyperlink ref="G166" r:id="rId173" xr:uid="{2BB85477-8B07-453A-943A-AB8D833D765C}"/>
+    <hyperlink ref="G167" r:id="rId174" xr:uid="{78A91A81-A712-4FC3-9541-7844350E958F}"/>
+    <hyperlink ref="G168" r:id="rId175" xr:uid="{BCC63CFD-5AC4-4F9B-BC3B-A78BEFB931B2}"/>
+    <hyperlink ref="G169" r:id="rId176" xr:uid="{68402901-A3D7-42F9-B1C5-1D5E49E4124D}"/>
+    <hyperlink ref="G170" r:id="rId177" xr:uid="{633A13CF-BFA3-48CB-9016-D6746BB2C07F}"/>
+    <hyperlink ref="G171" r:id="rId178" xr:uid="{60098ECC-6534-4FDC-957D-3160571C5520}"/>
+    <hyperlink ref="G165" r:id="rId179" xr:uid="{F34643C8-C444-4D62-95B0-60C8D08644AC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId173"/>
+  <legacyDrawing r:id="rId180"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD006C89-1AA2-4301-A3E8-1AF42E12C555}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" customWidth="1"/>
-    <col min="2" max="2" width="8.5" style="40" customWidth="1"/>
-    <col min="3" max="3" width="16.1640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="8.42578125" style="5" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="9" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.83203125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.85546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.140625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.42578125" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="17" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="7.1640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="42" t="s">
-        <v>525</v>
-      </c>
-      <c r="B1" s="43" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:5" ht="30.75">
+      <c r="A1" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="B2" s="40">
+      <c r="B2" s="5">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="B3" s="40">
+      <c r="B3" s="5">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:5">
+      <c r="A4" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B4" s="40">
+      <c r="B4" s="5">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:5">
+      <c r="A5" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="B5" s="40">
-        <v>11</v>
+      <c r="B5" s="5">
+        <v>18</v>
       </c>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:5">
+      <c r="A6" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B6" s="40">
+      <c r="B6" s="5">
         <v>5</v>
       </c>
       <c r="E6" s="1"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:5">
+      <c r="A7" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="40">
+      <c r="B7" s="5">
         <v>7</v>
       </c>
       <c r="E7" s="1"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:5">
+      <c r="A8" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="B8" s="40">
+      <c r="B8" s="5">
         <v>7</v>
       </c>
       <c r="E8" s="1"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:5">
+      <c r="A9" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="B9" s="40">
+      <c r="B9" s="5">
         <v>18</v>
       </c>
       <c r="E9" s="1"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
-        <v>527</v>
-      </c>
-      <c r="B10" s="40">
+    <row r="10" spans="1:5">
+      <c r="A10" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="B10" s="5">
         <v>15</v>
       </c>
       <c r="E10" s="1"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:5">
+      <c r="A11" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="40">
+      <c r="B11" s="5">
         <v>14</v>
       </c>
       <c r="E11" s="1"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:5">
+      <c r="A12" s="4" t="s">
         <v>428</v>
       </c>
-      <c r="B12" s="40">
+      <c r="B12" s="5">
         <v>6</v>
       </c>
       <c r="E12" s="1"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
-        <v>528</v>
-      </c>
-      <c r="B13" s="40">
+    <row r="13" spans="1:5">
+      <c r="A13" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="B13" s="5">
         <v>12</v>
       </c>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:5">
+      <c r="A14" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="B14" s="40">
+      <c r="B14" s="5">
         <v>16</v>
       </c>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:5">
+      <c r="A15" s="4" t="s">
         <v>213</v>
       </c>
-      <c r="B15" s="40">
+      <c r="B15" s="5">
         <v>28</v>
       </c>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
-        <v>529</v>
-      </c>
-      <c r="B16" s="40">
+    <row r="16" spans="1:5">
+      <c r="A16" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="B16" s="5">
         <v>3</v>
       </c>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="B17" s="41">
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B17" s="6">
         <f>SUM(B2:B16)</f>
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="E17" s="1"/>
     </row>
@@ -7120,155 +7684,155 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F3854A-26D2-4B73-8883-41115D3B5C7C}">
   <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.5" customWidth="1"/>
+    <col min="1" max="1" width="30.42578125" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="3" t="s">
-        <v>531</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="1" spans="1:2" ht="30.75">
+      <c r="A1" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="4" t="s">
         <v>47</v>
       </c>
       <c r="B2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="4" t="s">
         <v>110</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:2">
+      <c r="A5" s="4" t="s">
         <v>133</v>
       </c>
       <c r="B5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="B6">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:2">
+      <c r="A7" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="B7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="5" t="s">
+      <c r="B7" s="5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="4" t="s">
         <v>167</v>
       </c>
       <c r="B8">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="4" t="s">
         <v>275</v>
       </c>
       <c r="B9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="5" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" s="4" t="s">
         <v>142</v>
       </c>
       <c r="B10">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:2">
+      <c r="A11" s="4" t="s">
         <v>337</v>
       </c>
       <c r="B11">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:2">
+      <c r="A12" s="4" t="s">
         <v>103</v>
       </c>
       <c r="B12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:2">
+      <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
       <c r="B13">
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:2">
+      <c r="A14" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B14">
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:2">
+      <c r="A15" s="4" t="s">
         <v>23</v>
       </c>
       <c r="B15">
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:2">
+      <c r="A16" s="4" t="s">
         <v>15</v>
       </c>
       <c r="B16">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:2">
+      <c r="A17" s="4" t="s">
         <v>28</v>
       </c>
       <c r="B17">
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="B18" s="4">
+    <row r="18" spans="1:2">
+      <c r="A18" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B18" s="3">
         <f>SUM(B2:B17)</f>
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7297,91 +7861,91 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A20EE7BF-088B-4DBC-8B00-B4629CB74C85}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.33203125" style="40" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="18.28515625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A1" s="44" t="s">
-        <v>532</v>
-      </c>
-      <c r="B1" s="44" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A2" s="40" t="s">
+    <row r="1" spans="1:2" ht="30.75">
+      <c r="A1" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="B1" s="9" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="30.75">
+      <c r="A2" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B2">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A3" s="40" t="s">
+    <row r="3" spans="1:2" ht="30.75">
+      <c r="A3" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B3">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:2" ht="15.75" customHeight="1">
+      <c r="A4" s="5" t="s">
         <v>193</v>
       </c>
       <c r="B4">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
+    <row r="5" spans="1:2" ht="30.75">
+      <c r="A5" s="5" t="s">
         <v>27</v>
       </c>
       <c r="B5">
         <v>12</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A6" s="40" t="s">
+    <row r="6" spans="1:2" ht="30.75">
+      <c r="A6" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B6">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="30.75">
+      <c r="A7" s="5" t="s">
         <v>94</v>
       </c>
       <c r="B7">
         <v>45</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A8" s="40" t="s">
+    <row r="8" spans="1:2">
+      <c r="A8" s="5" t="s">
         <v>137</v>
       </c>
       <c r="B8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A9" s="40" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" s="5" t="s">
         <v>121</v>
       </c>
       <c r="B9">
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="16" x14ac:dyDescent="0.2">
-      <c r="A10" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="B10" s="4">
+    <row r="10" spans="1:2">
+      <c r="A10" s="6" t="s">
+        <v>550</v>
+      </c>
+      <c r="B10" s="3">
         <f>SUM(B2:B9)</f>
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7390,17 +7954,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddf82700-9bfb-4fea-878c-7eefdbc7745a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A70658DA2082244F88130573F11D6B61" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="858aee249293fa9096085e62b28b992c">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="ddf82700-9bfb-4fea-878c-7eefdbc7745a" xmlns:ns3="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0bb51cc068e630e42264d9068ea4c7f6" ns2:_="" ns3:_="">
     <xsd:import namespace="ddf82700-9bfb-4fea-878c-7eefdbc7745a"/>
@@ -7601,7 +8154,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -7610,40 +8163,25 @@
 </FormTemplates>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="ddf82700-9bfb-4fea-878c-7eefdbc7745a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11F60C-BEA5-4032-9DEF-D983207E1747}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="e1fe8cf4-797e-455f-bdfc-84f59ecaf273"/>
-    <ds:schemaRef ds:uri="ddf82700-9bfb-4fea-878c-7eefdbc7745a"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63105CD5-8CA5-4DAD-B85E-7A49F4224C26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63105CD5-8CA5-4DAD-B85E-7A49F4224C26}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="ddf82700-9bfb-4fea-878c-7eefdbc7745a"/>
-    <ds:schemaRef ds:uri="e1fe8cf4-797e-455f-bdfc-84f59ecaf273"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1BDF07-269F-4A8A-929B-119FFB2E0C7C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1BDF07-269F-4A8A-929B-119FFB2E0C7C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11F60C-BEA5-4032-9DEF-D983207E1747}"/>
 </file>
--- a/data/oer-catalog-2024-2025.xlsx
+++ b/data/oer-catalog-2024-2025.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30006"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FFB370E8-1C42-48A8-AC71-8C5258FE4D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{04B679C5-3F15-440A-AC92-05BD516AA9CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Catalog" sheetId="6" r:id="rId1"/>
@@ -42,6 +42,8 @@
     <author>tc={EF2E148D-555A-4E50-8DD5-A09F00C654B8}</author>
     <author>tc={AAE805E9-9988-450C-8A0E-4FC2EB2FEDE2}</author>
     <author>tc={316FD03D-FBA8-46BE-9B13-BDBF824B02A3}</author>
+    <author>tc={EF16F86B-C910-43A7-9C3D-8C92CAAE6A05}</author>
+    <author>tc={0000AA95-7943-4B6E-A38B-5B549A02C6DC}</author>
     <author>tc={AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}</author>
   </authors>
   <commentList>
@@ -69,7 +71,25 @@
     Links to a Google Form that isn't open</t>
       </text>
     </comment>
-    <comment ref="E121" authorId="3" shapeId="0" xr:uid="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
+    <comment ref="B109" authorId="3" shapeId="0" xr:uid="{EF16F86B-C910-43A7-9C3D-8C92CAAE6A05}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    the "Authors" at the end of this tab seems to be a typo
+Reply:
+    Thanks for catching! I'll fix the live version now</t>
+      </text>
+    </comment>
+    <comment ref="D111" authorId="4" shapeId="0" xr:uid="{0000AA95-7943-4B6E-A38B-5B549A02C6DC}">
+      <text>
+        <t>[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Assignment for ethnography course; social sciences is probably most accurate</t>
+      </text>
+    </comment>
+    <comment ref="E121" authorId="5" shapeId="0" xr:uid="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -1215,7 +1235,7 @@
     <t>https://academicworks.cuny.edu/nc_oers/33/</t>
   </si>
   <si>
-    <t xml:space="preserve">Estimating the amount of carbon dioxide gas removed from the atmosphere by the Bryant Park tree population Authors  </t>
+    <t>Estimating the amount of carbon dioxide gas removed from the atmosphere by the Bryant Park tree population</t>
   </si>
   <si>
     <t>Edimarlyn Gonzalez</t>
@@ -2499,6 +2519,15 @@
   <threadedComment ref="G98" dT="2026-03-19T14:52:17.13" personId="{657B7818-16BF-47BC-A894-BA53C86E21EC}" id="{316FD03D-FBA8-46BE-9B13-BDBF824B02A3}">
     <text>Links to a Google Form that isn't open</text>
   </threadedComment>
+  <threadedComment ref="B109" dT="2026-05-20T18:51:43.15" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{EF16F86B-C910-43A7-9C3D-8C92CAAE6A05}">
+    <text>the "Authors" at the end of this tab seems to be a typo</text>
+  </threadedComment>
+  <threadedComment ref="B109" dT="2026-05-20T19:12:31.01" personId="{657B7818-16BF-47BC-A894-BA53C86E21EC}" id="{A3F1CFF1-670E-4A2A-963F-635B9DF5E15A}" parentId="{EF16F86B-C910-43A7-9C3D-8C92CAAE6A05}">
+    <text>Thanks for catching! I'll fix the live version now</text>
+  </threadedComment>
+  <threadedComment ref="D111" dT="2026-04-23T17:14:32.58" personId="{C2DA5350-6A68-476C-B8B8-C22CFA092D41}" id="{0000AA95-7943-4B6E-A38B-5B549A02C6DC}">
+    <text>Assignment for ethnography course; social sciences is probably most accurate</text>
+  </threadedComment>
   <threadedComment ref="E121" dT="2026-03-19T21:24:38.22" personId="{ABB89055-104B-4067-BC1F-C93E3E956FFD}" id="{AC5944AF-50DA-47F9-A3C1-21E9FAE213F4}">
     <text>for group authored works -- cite the authoring entity described in the work</text>
   </threadedComment>
@@ -5489,32 +5518,32 @@
       <c r="J110" s="23"/>
       <c r="K110" s="23"/>
     </row>
-    <row r="111" spans="1:11" ht="24">
-      <c r="A111" s="19" t="s">
+    <row r="111" spans="1:11" s="18" customFormat="1" ht="24">
+      <c r="A111" s="25" t="s">
         <v>353</v>
       </c>
-      <c r="B111" s="19" t="s">
+      <c r="B111" s="25" t="s">
         <v>369</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="D111" s="15" t="s">
+      <c r="D111" s="26" t="s">
         <v>103</v>
       </c>
-      <c r="E111" s="19" t="s">
+      <c r="E111" s="25" t="s">
         <v>370</v>
       </c>
-      <c r="F111" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G111" s="31" t="s">
+      <c r="F111" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="G111" s="27" t="s">
         <v>371</v>
       </c>
-      <c r="H111" s="23"/>
-      <c r="I111" s="23"/>
-      <c r="J111" s="23"/>
-      <c r="K111" s="23"/>
+      <c r="H111" s="17"/>
+      <c r="I111" s="17"/>
+      <c r="J111" s="17"/>
+      <c r="K111" s="17"/>
     </row>
     <row r="112" spans="1:11" ht="108.75" customHeight="1">
       <c r="A112" s="19" t="s">
@@ -8155,15 +8184,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="e1fe8cf4-797e-455f-bdfc-84f59ecaf273" xsi:nil="true"/>
@@ -8174,14 +8194,23 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63105CD5-8CA5-4DAD-B85E-7A49F4224C26}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1BDF07-269F-4A8A-929B-119FFB2E0C7C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11F60C-BEA5-4032-9DEF-D983207E1747}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB11F60C-BEA5-4032-9DEF-D983207E1747}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2C1BDF07-269F-4A8A-929B-119FFB2E0C7C}"/>
 </file>